--- a/youzi/牛散唐汉若/index.xlsx
+++ b/youzi/牛散唐汉若/index.xlsx
@@ -39,13 +39,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF7AC88C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -57,25 +105,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,25 +201,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
+        <fgColor rgb="FFD7EEDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -117,19 +261,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D5D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,67 +351,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF56BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
+        <fgColor rgb="FFC42A39"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -213,43 +405,229 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56974"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0EBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -261,25 +639,499 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -291,115 +1143,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D5D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -411,55 +1299,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -471,37 +1395,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -513,205 +1491,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56974"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAF202E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707B"/>
+        <fgColor rgb="FFAF202E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -723,799 +1569,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1527,61 +1587,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE35F6C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CE"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1606,24 +1624,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -4730,7 +4730,7 @@
       <c r="C2" t="str">
         <v>603300</v>
       </c>
-      <c r="D2" s="8" t="str">
+      <c r="D2" s="9" t="str">
         <v>净买: 7263.08万</v>
       </c>
       <c r="E2">
@@ -4745,37 +4745,37 @@
       <c r="H2">
         <v>5.49</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="1">
         <v>4.31</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="2">
         <v>-6.1</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="11">
         <v>-0.65</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="3">
         <v>1.06</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="5">
         <v>-3.09</v>
       </c>
       <c r="N2" s="10">
         <v>-1.14</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="6">
         <v>-3.25</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="7">
         <v>-6.02</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="8">
         <v>-3.58</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="4">
         <v>-6.59</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S2" s="12">
         <v>-13.01</v>
       </c>
       <c r="T2" s="13">
@@ -4792,7 +4792,7 @@
       <c r="C3" t="str">
         <v>002093</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="20" t="str">
         <v>净卖: -871.26万</v>
       </c>
       <c r="E3">
@@ -4807,40 +4807,40 @@
       <c r="H3">
         <v>10.06</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="26">
         <v>0</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="21">
         <v>10.04</v>
       </c>
       <c r="K3" s="22">
         <v>14.06</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="23">
         <v>21.08</v>
       </c>
       <c r="M3" s="15">
         <v>33.23</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="18">
         <v>46.59</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="19">
         <v>41.16</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="16">
         <v>31.83</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="17">
         <v>44.98</v>
       </c>
-      <c r="R3" s="25">
+      <c r="R3" s="24">
         <v>59.44</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="25">
         <v>43.47</v>
       </c>
-      <c r="T3" s="26">
+      <c r="T3" s="14">
         <v>-2.61</v>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       <c r="C4" t="str">
         <v>603300</v>
       </c>
-      <c r="D4" s="30" t="str">
+      <c r="D4" s="27" t="str">
         <v>净买: 227.62万</v>
       </c>
       <c r="E4">
@@ -4869,28 +4869,28 @@
       <c r="H4">
         <v>-6.24</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="31">
         <v>-3.99</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="33">
         <v>1.58</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="38">
         <v>3.33</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="28">
         <v>-0.91</v>
       </c>
-      <c r="M4" s="39">
+      <c r="M4" s="32">
         <v>1.08</v>
       </c>
-      <c r="N4" s="33">
+      <c r="N4" s="29">
         <v>-1.08</v>
       </c>
-      <c r="O4" s="27">
+      <c r="O4" s="34">
         <v>-3.91</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="35">
         <v>-1.41</v>
       </c>
       <c r="Q4" s="36">
@@ -4899,10 +4899,10 @@
       <c r="R4" s="37">
         <v>-11.06</v>
       </c>
-      <c r="S4" s="38">
+      <c r="S4" s="30">
         <v>-8.56</v>
       </c>
-      <c r="T4" s="29">
+      <c r="T4" s="39">
         <v>-40.4</v>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       <c r="C5" t="str">
         <v>603300</v>
       </c>
-      <c r="D5" s="50" t="str">
+      <c r="D5" s="52" t="str">
         <v>净卖: -6041.68万</v>
       </c>
       <c r="E5">
@@ -4931,40 +4931,40 @@
       <c r="H5">
         <v>2.16</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="48">
         <v>3.56</v>
       </c>
-      <c r="J5" s="46">
+      <c r="J5" s="49">
         <v>5.34</v>
       </c>
-      <c r="K5" s="51">
+      <c r="K5" s="45">
         <v>1.02</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="46">
         <v>3.05</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="40">
         <v>0.85</v>
       </c>
-      <c r="N5" s="45">
+      <c r="N5" s="47">
         <v>-2.03</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="41">
         <v>0.51</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="42">
         <v>-2.63</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="50">
         <v>-9.32</v>
       </c>
-      <c r="R5" s="41">
+      <c r="R5" s="51">
         <v>-6.78</v>
       </c>
-      <c r="S5" s="49">
+      <c r="S5" s="43">
         <v>-13.73</v>
       </c>
-      <c r="T5" s="42">
+      <c r="T5" s="44">
         <v>-39.24</v>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       <c r="C6" t="str">
         <v>603985</v>
       </c>
-      <c r="D6" s="62" t="str">
+      <c r="D6" s="58" t="str">
         <v>净卖: -484.50万</v>
       </c>
       <c r="E6">
@@ -4993,40 +4993,40 @@
       <c r="H6">
         <v>10.01</v>
       </c>
-      <c r="I6" s="63">
+      <c r="I6" s="59">
         <v>0</v>
       </c>
-      <c r="J6" s="58">
+      <c r="J6" s="53">
         <v>10.01</v>
       </c>
-      <c r="K6" s="64">
+      <c r="K6" s="60">
         <v>7.17</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="57">
         <v>-3.55</v>
       </c>
-      <c r="M6" s="59">
+      <c r="M6" s="61">
         <v>-10.59</v>
       </c>
-      <c r="N6" s="65">
+      <c r="N6" s="54">
         <v>-1.61</v>
       </c>
-      <c r="O6" s="56">
+      <c r="O6" s="62">
         <v>2.32</v>
       </c>
-      <c r="P6" s="60">
+      <c r="P6" s="63">
         <v>3.87</v>
       </c>
-      <c r="Q6" s="61">
+      <c r="Q6" s="64">
         <v>6.33</v>
       </c>
-      <c r="R6" s="57">
+      <c r="R6" s="55">
         <v>4.33</v>
       </c>
-      <c r="S6" s="53">
+      <c r="S6" s="56">
         <v>5.68</v>
       </c>
-      <c r="T6" s="54">
+      <c r="T6" s="65">
         <v>58.81</v>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       <c r="C7" t="str">
         <v>600744</v>
       </c>
-      <c r="D7" s="72" t="str">
+      <c r="D7" s="73" t="str">
         <v>净卖: -165.95万</v>
       </c>
       <c r="E7">
@@ -5058,31 +5058,31 @@
       <c r="I7" s="78">
         <v>0</v>
       </c>
-      <c r="J7" s="73">
+      <c r="J7" s="74">
         <v>9.91</v>
       </c>
       <c r="K7" s="69">
         <v>15.8</v>
       </c>
-      <c r="L7" s="74">
+      <c r="L7" s="75">
         <v>4.25</v>
       </c>
-      <c r="M7" s="66">
+      <c r="M7" s="70">
         <v>14.62</v>
       </c>
-      <c r="N7" s="67">
+      <c r="N7" s="76">
         <v>19.34</v>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="71">
         <v>27.36</v>
       </c>
-      <c r="P7" s="71">
+      <c r="P7" s="66">
         <v>27.36</v>
       </c>
-      <c r="Q7" s="75">
+      <c r="Q7" s="72">
         <v>25.24</v>
       </c>
-      <c r="R7" s="76">
+      <c r="R7" s="67">
         <v>24.53</v>
       </c>
       <c r="S7" s="77">
@@ -5102,7 +5102,7 @@
       <c r="C8" t="str">
         <v>603042</v>
       </c>
-      <c r="D8" s="79" t="str">
+      <c r="D8" s="89" t="str">
         <v>净买: 1056.82万</v>
       </c>
       <c r="E8">
@@ -5120,37 +5120,37 @@
       <c r="I8" s="85">
         <v>6.28</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="82">
         <v>7.66</v>
       </c>
       <c r="K8" s="90">
         <v>9.48</v>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="81">
         <v>12.44</v>
       </c>
-      <c r="M8" s="86">
+      <c r="M8" s="83">
         <v>11.93</v>
       </c>
-      <c r="N8" s="83">
+      <c r="N8" s="86">
         <v>9.99</v>
       </c>
-      <c r="O8" s="84">
+      <c r="O8" s="91">
         <v>8.73</v>
       </c>
-      <c r="P8" s="80">
+      <c r="P8" s="84">
         <v>12.5</v>
       </c>
-      <c r="Q8" s="87">
+      <c r="Q8" s="79">
         <v>9.86</v>
       </c>
-      <c r="R8" s="88">
+      <c r="R8" s="87">
         <v>3.71</v>
       </c>
-      <c r="S8" s="81">
+      <c r="S8" s="88">
         <v>5.21</v>
       </c>
-      <c r="T8" s="91">
+      <c r="T8" s="80">
         <v>36.24</v>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       <c r="C9" t="str">
         <v>603300</v>
       </c>
-      <c r="D9" s="97" t="str">
+      <c r="D9" s="101" t="str">
         <v>净卖: -5853.95万</v>
       </c>
       <c r="E9">
@@ -5179,40 +5179,40 @@
       <c r="H9">
         <v>-0.29</v>
       </c>
-      <c r="I9" s="98">
+      <c r="I9" s="102">
         <v>7.44</v>
       </c>
-      <c r="J9" s="94">
+      <c r="J9" s="97">
         <v>8.23</v>
       </c>
       <c r="K9" s="103">
         <v>9.21</v>
       </c>
-      <c r="L9" s="104">
+      <c r="L9" s="98">
         <v>4.8</v>
       </c>
-      <c r="M9" s="99">
+      <c r="M9" s="104">
         <v>2.06</v>
       </c>
-      <c r="N9" s="95">
+      <c r="N9" s="94">
         <v>1.37</v>
       </c>
-      <c r="O9" s="96">
+      <c r="O9" s="92">
         <v>0.78</v>
       </c>
-      <c r="P9" s="92">
+      <c r="P9" s="95">
         <v>4.41</v>
       </c>
-      <c r="Q9" s="100">
+      <c r="Q9" s="99">
         <v>7.05</v>
       </c>
-      <c r="R9" s="101">
+      <c r="R9" s="93">
         <v>4.21</v>
       </c>
-      <c r="S9" s="93">
+      <c r="S9" s="96">
         <v>2.45</v>
       </c>
-      <c r="T9" s="102">
+      <c r="T9" s="100">
         <v>-29.77</v>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       <c r="C10" t="str">
         <v>002028</v>
       </c>
-      <c r="D10" s="109" t="str">
+      <c r="D10" s="116" t="str">
         <v>净卖: -3647.56万</v>
       </c>
       <c r="E10">
@@ -5241,37 +5241,37 @@
       <c r="H10">
         <v>7.27</v>
       </c>
-      <c r="I10" s="116">
+      <c r="I10" s="108">
         <v>2.54</v>
       </c>
-      <c r="J10" s="110">
+      <c r="J10" s="109">
         <v>9.99</v>
       </c>
-      <c r="K10" s="107">
+      <c r="K10" s="110">
         <v>6.69</v>
       </c>
-      <c r="L10" s="108">
+      <c r="L10" s="105">
         <v>5.58</v>
       </c>
       <c r="M10" s="111">
         <v>1.57</v>
       </c>
-      <c r="N10" s="117">
+      <c r="N10" s="112">
         <v>3.49</v>
       </c>
-      <c r="O10" s="105">
+      <c r="O10" s="117">
         <v>5.22</v>
       </c>
-      <c r="P10" s="112">
+      <c r="P10" s="113">
         <v>4.9</v>
       </c>
-      <c r="Q10" s="113">
+      <c r="Q10" s="106">
         <v>3.53</v>
       </c>
       <c r="R10" s="114">
         <v>6.54</v>
       </c>
-      <c r="S10" s="106">
+      <c r="S10" s="107">
         <v>8.07</v>
       </c>
       <c r="T10" s="115">
@@ -5303,40 +5303,40 @@
       <c r="H11">
         <v>0.04</v>
       </c>
-      <c r="I11" s="118">
+      <c r="I11" s="128">
         <v>3.45</v>
       </c>
-      <c r="J11" s="119">
+      <c r="J11" s="118">
         <v>3.45</v>
       </c>
       <c r="K11" s="124">
         <v>4.99</v>
       </c>
-      <c r="L11" s="120">
+      <c r="L11" s="119">
         <v>3.55</v>
       </c>
-      <c r="M11" s="125">
+      <c r="M11" s="122">
         <v>9.31</v>
       </c>
-      <c r="N11" s="129">
+      <c r="N11" s="120">
         <v>6.44</v>
       </c>
-      <c r="O11" s="121">
+      <c r="O11" s="123">
         <v>5.49</v>
       </c>
-      <c r="P11" s="126">
+      <c r="P11" s="121">
         <v>4.71</v>
       </c>
-      <c r="Q11" s="122">
+      <c r="Q11" s="125">
         <v>3.2</v>
       </c>
-      <c r="R11" s="127">
+      <c r="R11" s="129">
         <v>3.82</v>
       </c>
-      <c r="S11" s="128">
+      <c r="S11" s="126">
         <v>3.18</v>
       </c>
-      <c r="T11" s="123">
+      <c r="T11" s="127">
         <v>15.42</v>
       </c>
     </row>
@@ -5350,7 +5350,7 @@
       <c r="C12" t="str">
         <v>603280</v>
       </c>
-      <c r="D12" s="143" t="str">
+      <c r="D12" s="133" t="str">
         <v>净卖: -740.40万</v>
       </c>
       <c r="E12">
@@ -5365,40 +5365,40 @@
       <c r="H12">
         <v>3.37</v>
       </c>
-      <c r="I12" s="134">
+      <c r="I12" s="137">
         <v>6.41</v>
       </c>
-      <c r="J12" s="138">
+      <c r="J12" s="141">
         <v>17.04</v>
       </c>
-      <c r="K12" s="139">
+      <c r="K12" s="138">
         <v>28.75</v>
       </c>
-      <c r="L12" s="135">
+      <c r="L12" s="134">
         <v>41.65</v>
       </c>
-      <c r="M12" s="131">
+      <c r="M12" s="143">
         <v>38.83</v>
       </c>
-      <c r="N12" s="140">
+      <c r="N12" s="131">
         <v>52.72</v>
       </c>
-      <c r="O12" s="136">
+      <c r="O12" s="135">
         <v>67.99</v>
       </c>
-      <c r="P12" s="137">
+      <c r="P12" s="142">
         <v>84.77</v>
       </c>
-      <c r="Q12" s="132">
+      <c r="Q12" s="139">
         <v>103.26</v>
       </c>
-      <c r="R12" s="141">
+      <c r="R12" s="140">
         <v>112.93</v>
       </c>
-      <c r="S12" s="133">
+      <c r="S12" s="136">
         <v>122.68</v>
       </c>
-      <c r="T12" s="142">
+      <c r="T12" s="132">
         <v>28.97</v>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       <c r="C13" t="str">
         <v>603280</v>
       </c>
-      <c r="D13" s="152" t="str">
+      <c r="D13" s="144" t="str">
         <v>净卖: -1064.89万</v>
       </c>
       <c r="E13">
@@ -5427,40 +5427,40 @@
       <c r="H13">
         <v>4.74</v>
       </c>
-      <c r="I13" s="153">
+      <c r="I13" s="145">
         <v>5.02</v>
       </c>
-      <c r="J13" s="144">
+      <c r="J13" s="150">
         <v>15.53</v>
       </c>
-      <c r="K13" s="145">
+      <c r="K13" s="155">
         <v>27.09</v>
       </c>
-      <c r="L13" s="154">
+      <c r="L13" s="153">
         <v>24.57</v>
       </c>
-      <c r="M13" s="146">
+      <c r="M13" s="154">
         <v>37.03</v>
       </c>
-      <c r="N13" s="155">
+      <c r="N13" s="156">
         <v>50.73</v>
       </c>
-      <c r="O13" s="147">
+      <c r="O13" s="146">
         <v>65.79</v>
       </c>
-      <c r="P13" s="148">
+      <c r="P13" s="151">
         <v>82.38</v>
       </c>
-      <c r="Q13" s="149">
+      <c r="Q13" s="147">
         <v>91.06</v>
       </c>
-      <c r="R13" s="150">
+      <c r="R13" s="148">
         <v>99.8</v>
       </c>
-      <c r="S13" s="151">
+      <c r="S13" s="152">
         <v>90.16</v>
       </c>
-      <c r="T13" s="156">
+      <c r="T13" s="149">
         <v>15.72</v>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       <c r="C14" t="str">
         <v>600113</v>
       </c>
-      <c r="D14" s="157" t="str">
+      <c r="D14" s="166" t="str">
         <v>净卖: -1621.26万</v>
       </c>
       <c r="E14">
@@ -5489,40 +5489,40 @@
       <c r="H14">
         <v>2.49</v>
       </c>
-      <c r="I14" s="165">
+      <c r="I14" s="163">
         <v>7.32</v>
       </c>
-      <c r="J14" s="162">
+      <c r="J14" s="167">
         <v>18.05</v>
       </c>
-      <c r="K14" s="158">
+      <c r="K14" s="168">
         <v>25.05</v>
       </c>
-      <c r="L14" s="163">
+      <c r="L14" s="158">
         <v>37.57</v>
       </c>
-      <c r="M14" s="159">
+      <c r="M14" s="169">
         <v>35.41</v>
       </c>
-      <c r="N14" s="166">
+      <c r="N14" s="164">
         <v>38.35</v>
       </c>
-      <c r="O14" s="164">
+      <c r="O14" s="160">
         <v>38.24</v>
       </c>
-      <c r="P14" s="160">
+      <c r="P14" s="165">
         <v>39.05</v>
       </c>
-      <c r="Q14" s="167">
+      <c r="Q14" s="161">
         <v>33.92</v>
       </c>
-      <c r="R14" s="161">
+      <c r="R14" s="159">
         <v>47.32</v>
       </c>
-      <c r="S14" s="169">
+      <c r="S14" s="162">
         <v>62.05</v>
       </c>
-      <c r="T14" s="168">
+      <c r="T14" s="157">
         <v>27.54</v>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       <c r="C15" t="str">
         <v>600113</v>
       </c>
-      <c r="D15" s="182" t="str">
+      <c r="D15" s="181" t="str">
         <v>净卖: -2870.19万</v>
       </c>
       <c r="E15">
@@ -5551,40 +5551,40 @@
       <c r="H15">
         <v>-0.58</v>
       </c>
-      <c r="I15" s="170">
+      <c r="I15" s="176">
         <v>10.65</v>
       </c>
-      <c r="J15" s="178">
+      <c r="J15" s="177">
         <v>8.91</v>
       </c>
-      <c r="K15" s="174">
+      <c r="K15" s="171">
         <v>11.28</v>
       </c>
-      <c r="L15" s="171">
+      <c r="L15" s="172">
         <v>11.2</v>
       </c>
-      <c r="M15" s="175">
+      <c r="M15" s="173">
         <v>11.85</v>
       </c>
-      <c r="N15" s="179">
+      <c r="N15" s="182">
         <v>7.72</v>
       </c>
-      <c r="O15" s="180">
+      <c r="O15" s="174">
         <v>18.5</v>
       </c>
-      <c r="P15" s="172">
+      <c r="P15" s="179">
         <v>30.35</v>
       </c>
-      <c r="Q15" s="176">
+      <c r="Q15" s="180">
         <v>33.04</v>
       </c>
-      <c r="R15" s="177">
+      <c r="R15" s="170">
         <v>22.78</v>
       </c>
-      <c r="S15" s="173">
+      <c r="S15" s="178">
         <v>28.54</v>
       </c>
-      <c r="T15" s="181">
+      <c r="T15" s="175">
         <v>2.59</v>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       <c r="C16" t="str">
         <v>000014</v>
       </c>
-      <c r="D16" s="184" t="str">
+      <c r="D16" s="183" t="str">
         <v>净卖: -962.87万</v>
       </c>
       <c r="E16">
@@ -5613,40 +5613,40 @@
       <c r="H16">
         <v>9.96</v>
       </c>
-      <c r="I16" s="194">
+      <c r="I16" s="188">
         <v>-12.33</v>
       </c>
-      <c r="J16" s="185">
+      <c r="J16" s="184">
         <v>-15.5</v>
       </c>
-      <c r="K16" s="189">
+      <c r="K16" s="192">
         <v>-14.75</v>
       </c>
-      <c r="L16" s="186">
+      <c r="L16" s="193">
         <v>-14.05</v>
       </c>
-      <c r="M16" s="190">
+      <c r="M16" s="185">
         <v>-12.8</v>
       </c>
       <c r="N16" s="195">
         <v>-18.7</v>
       </c>
-      <c r="O16" s="187">
+      <c r="O16" s="186">
         <v>-26.81</v>
       </c>
-      <c r="P16" s="191">
+      <c r="P16" s="187">
         <v>-26.39</v>
       </c>
-      <c r="Q16" s="183">
+      <c r="Q16" s="194">
         <v>-31.3</v>
       </c>
-      <c r="R16" s="192">
+      <c r="R16" s="189">
         <v>-29.12</v>
       </c>
-      <c r="S16" s="193">
+      <c r="S16" s="190">
         <v>-29.2</v>
       </c>
-      <c r="T16" s="188">
+      <c r="T16" s="191">
         <v>-47.66</v>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       <c r="C17" t="str">
         <v>688577</v>
       </c>
-      <c r="D17" s="198" t="str">
+      <c r="D17" s="207" t="str">
         <v>净卖: -1039.47万</v>
       </c>
       <c r="E17">
@@ -5675,40 +5675,40 @@
       <c r="H17">
         <v>-0.04</v>
       </c>
-      <c r="I17" s="197">
+      <c r="I17" s="200">
         <v>-19.96</v>
       </c>
-      <c r="J17" s="199">
+      <c r="J17" s="208">
         <v>-18.66</v>
       </c>
-      <c r="K17" s="200">
+      <c r="K17" s="204">
         <v>-15.24</v>
       </c>
       <c r="L17" s="201">
         <v>-16.26</v>
       </c>
-      <c r="M17" s="202">
+      <c r="M17" s="205">
         <v>-17.76</v>
       </c>
-      <c r="N17" s="203">
+      <c r="N17" s="202">
         <v>-16.4</v>
       </c>
-      <c r="O17" s="207">
+      <c r="O17" s="196">
         <v>-18.64</v>
       </c>
-      <c r="P17" s="208">
+      <c r="P17" s="197">
         <v>-19.41</v>
       </c>
-      <c r="Q17" s="196">
+      <c r="Q17" s="198">
         <v>-10.36</v>
       </c>
-      <c r="R17" s="204">
+      <c r="R17" s="206">
         <v>-13.75</v>
       </c>
-      <c r="S17" s="205">
+      <c r="S17" s="203">
         <v>-14.11</v>
       </c>
-      <c r="T17" s="206">
+      <c r="T17" s="199">
         <v>-38.74</v>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       <c r="C18" t="str">
         <v>603757</v>
       </c>
-      <c r="D18" s="211" t="str">
+      <c r="D18" s="210" t="str">
         <v>净卖: -7133.87万</v>
       </c>
       <c r="E18">
@@ -5737,40 +5737,40 @@
       <c r="H18">
         <v>-1.84</v>
       </c>
-      <c r="I18" s="213">
+      <c r="I18" s="216">
         <v>12.06</v>
       </c>
-      <c r="J18" s="212">
+      <c r="J18" s="209">
         <v>13.86</v>
       </c>
-      <c r="K18" s="220">
+      <c r="K18" s="211">
         <v>17.77</v>
       </c>
-      <c r="L18" s="215">
+      <c r="L18" s="219">
         <v>14.57</v>
       </c>
-      <c r="M18" s="216">
+      <c r="M18" s="212">
         <v>16.9</v>
       </c>
       <c r="N18" s="217">
         <v>11.61</v>
       </c>
-      <c r="O18" s="221">
+      <c r="O18" s="213">
         <v>9.48</v>
       </c>
-      <c r="P18" s="218">
+      <c r="P18" s="214">
         <v>12.23</v>
       </c>
-      <c r="Q18" s="214">
+      <c r="Q18" s="220">
         <v>5.19</v>
       </c>
-      <c r="R18" s="219">
+      <c r="R18" s="215">
         <v>8.18</v>
       </c>
-      <c r="S18" s="209">
+      <c r="S18" s="218">
         <v>6.47</v>
       </c>
-      <c r="T18" s="210">
+      <c r="T18" s="221">
         <v>32.37</v>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       <c r="C19" t="str">
         <v>002117</v>
       </c>
-      <c r="D19" s="223" t="str">
+      <c r="D19" s="226" t="str">
         <v>净卖: -1144.93万</v>
       </c>
       <c r="E19">
@@ -5799,37 +5799,37 @@
       <c r="H19">
         <v>0.29</v>
       </c>
-      <c r="I19" s="224">
+      <c r="I19" s="223">
         <v>-10.25</v>
       </c>
-      <c r="J19" s="234">
+      <c r="J19" s="232">
         <v>-10.69</v>
       </c>
-      <c r="K19" s="222">
+      <c r="K19" s="224">
         <v>-13.72</v>
       </c>
       <c r="L19" s="225">
         <v>-12.78</v>
       </c>
-      <c r="M19" s="226">
+      <c r="M19" s="228">
         <v>-12.64</v>
       </c>
-      <c r="N19" s="227">
+      <c r="N19" s="229">
         <v>-8.52</v>
       </c>
-      <c r="O19" s="232">
+      <c r="O19" s="233">
         <v>-12.27</v>
       </c>
-      <c r="P19" s="233">
+      <c r="P19" s="230">
         <v>-11.26</v>
       </c>
-      <c r="Q19" s="228">
+      <c r="Q19" s="234">
         <v>-12.13</v>
       </c>
-      <c r="R19" s="230">
+      <c r="R19" s="222">
         <v>-12.78</v>
       </c>
-      <c r="S19" s="229">
+      <c r="S19" s="227">
         <v>-12.56</v>
       </c>
       <c r="T19" s="231">
@@ -5846,7 +5846,7 @@
       <c r="C20" t="str">
         <v>600246</v>
       </c>
-      <c r="D20" s="246" t="str">
+      <c r="D20" s="242" t="str">
         <v>净买: 1107.56万</v>
       </c>
       <c r="E20">
@@ -5864,37 +5864,37 @@
       <c r="I20" s="243">
         <v>-10.98</v>
       </c>
-      <c r="J20" s="237">
+      <c r="J20" s="244">
         <v>-11.79</v>
       </c>
-      <c r="K20" s="247">
+      <c r="K20" s="245">
         <v>-11.87</v>
       </c>
-      <c r="L20" s="238">
+      <c r="L20" s="246">
         <v>-11.54</v>
       </c>
-      <c r="M20" s="239">
+      <c r="M20" s="238">
         <v>-10.08</v>
       </c>
-      <c r="N20" s="240">
+      <c r="N20" s="247">
         <v>-10.08</v>
       </c>
-      <c r="O20" s="244">
+      <c r="O20" s="235">
         <v>-11.71</v>
       </c>
-      <c r="P20" s="236">
+      <c r="P20" s="239">
         <v>-12.52</v>
       </c>
-      <c r="Q20" s="241">
+      <c r="Q20" s="236">
         <v>-11.95</v>
       </c>
-      <c r="R20" s="242">
+      <c r="R20" s="237">
         <v>-12.44</v>
       </c>
-      <c r="S20" s="235">
+      <c r="S20" s="240">
         <v>-14.15</v>
       </c>
-      <c r="T20" s="245">
+      <c r="T20" s="241">
         <v>-21.22</v>
       </c>
     </row>
@@ -5957,40 +5957,40 @@
       <c r="F22" t="str"/>
       <c r="G22" t="str"/>
       <c r="H22" t="str"/>
-      <c r="I22" s="254">
+      <c r="I22" s="248">
         <v>57.89</v>
       </c>
-      <c r="J22" s="259">
+      <c r="J22" s="252">
         <v>73.68</v>
       </c>
-      <c r="K22" s="253">
+      <c r="K22" s="249">
         <v>73.68</v>
       </c>
-      <c r="L22" s="248">
+      <c r="L22" s="258">
         <v>68.42</v>
       </c>
-      <c r="M22" s="249">
+      <c r="M22" s="254">
         <v>68.42</v>
       </c>
-      <c r="N22" s="255">
+      <c r="N22" s="259">
         <v>57.89</v>
       </c>
-      <c r="O22" s="256">
+      <c r="O22" s="253">
         <v>68.42</v>
       </c>
-      <c r="P22" s="252">
+      <c r="P22" s="250">
         <v>63.16</v>
       </c>
-      <c r="Q22" s="257">
+      <c r="Q22" s="255">
         <v>63.16</v>
       </c>
-      <c r="R22" s="250">
+      <c r="R22" s="256">
         <v>63.16</v>
       </c>
-      <c r="S22" s="251">
+      <c r="S22" s="257">
         <v>63.16</v>
       </c>
-      <c r="T22" s="258">
+      <c r="T22" s="251">
         <v>52.63</v>
       </c>
     </row>
@@ -6005,40 +6005,40 @@
       <c r="F23" t="str"/>
       <c r="G23" t="str"/>
       <c r="H23" t="str"/>
-      <c r="I23" s="262">
+      <c r="I23" s="265">
         <v>0.61</v>
       </c>
-      <c r="J23" s="264">
+      <c r="J23" s="267">
         <v>4.05</v>
       </c>
-      <c r="K23" s="267">
+      <c r="K23" s="268">
         <v>6.6</v>
       </c>
-      <c r="L23" s="265">
+      <c r="L23" s="269">
         <v>6.65</v>
       </c>
-      <c r="M23" s="271">
+      <c r="M23" s="270">
         <v>7.77</v>
       </c>
-      <c r="N23" s="263">
+      <c r="N23" s="262">
         <v>9.94</v>
       </c>
-      <c r="O23" s="268">
+      <c r="O23" s="266">
         <v>11.31</v>
       </c>
-      <c r="P23" s="260">
+      <c r="P23" s="271">
         <v>13.62</v>
       </c>
-      <c r="Q23" s="266">
+      <c r="Q23" s="260">
         <v>14.92</v>
       </c>
       <c r="R23" s="261">
         <v>16.06</v>
       </c>
-      <c r="S23" s="269">
+      <c r="S23" s="264">
         <v>15.55</v>
       </c>
-      <c r="T23" s="270">
+      <c r="T23" s="263">
         <v>10.05</v>
       </c>
     </row>

--- a/youzi/牛散唐汉若/index.xlsx
+++ b/youzi/牛散唐汉若/index.xlsx
@@ -39,49 +39,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE0505E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF249A3F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF7D4D7"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,13 +213,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,43 +237,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D5D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -159,31 +345,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -195,61 +363,277 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0EBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF56BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56974"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -261,7 +645,487 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -273,24 +1137,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -303,43 +1149,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D5D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -351,31 +1179,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -387,85 +1233,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -483,85 +1353,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56974"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -573,79 +1521,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -657,61 +1563,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
+        <fgColor rgb="FFAF202E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -723,828 +1575,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCB2D3C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -1557,37 +1593,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1624,12 +1630,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -4730,7 +4730,7 @@
       <c r="C2" t="str">
         <v>603300</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="2" t="str">
         <v>净买: 7263.08万</v>
       </c>
       <c r="E2">
@@ -4745,40 +4745,40 @@
       <c r="H2">
         <v>5.49</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="3">
         <v>4.31</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="9">
         <v>-6.1</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="4">
         <v>-0.65</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="13">
         <v>1.06</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="10">
         <v>-3.09</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="1">
         <v>-1.14</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="5">
         <v>-3.25</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="6">
         <v>-6.02</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="11">
         <v>-3.58</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="7">
         <v>-6.59</v>
       </c>
       <c r="S2" s="12">
         <v>-13.01</v>
       </c>
-      <c r="T2" s="13">
+      <c r="T2" s="8">
         <v>-41.71</v>
       </c>
     </row>
@@ -4792,7 +4792,7 @@
       <c r="C3" t="str">
         <v>002093</v>
       </c>
-      <c r="D3" s="20" t="str">
+      <c r="D3" s="23" t="str">
         <v>净卖: -871.26万</v>
       </c>
       <c r="E3">
@@ -4807,40 +4807,40 @@
       <c r="H3">
         <v>10.06</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="14">
         <v>0</v>
       </c>
-      <c r="J3" s="21">
+      <c r="J3" s="15">
         <v>10.04</v>
       </c>
-      <c r="K3" s="22">
+      <c r="K3" s="16">
         <v>14.06</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="20">
         <v>21.08</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="17">
         <v>33.23</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="24">
         <v>46.59</v>
       </c>
-      <c r="O3" s="19">
+      <c r="O3" s="18">
         <v>41.16</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="25">
         <v>31.83</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="19">
         <v>44.98</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="21">
         <v>59.44</v>
       </c>
-      <c r="S3" s="25">
+      <c r="S3" s="22">
         <v>43.47</v>
       </c>
-      <c r="T3" s="14">
+      <c r="T3" s="26">
         <v>-2.61</v>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       <c r="C4" t="str">
         <v>603300</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="29" t="str">
         <v>净买: 227.62万</v>
       </c>
       <c r="E4">
@@ -4869,40 +4869,40 @@
       <c r="H4">
         <v>-6.24</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="34">
         <v>-3.99</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="35">
         <v>1.58</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="30">
         <v>3.33</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="38">
         <v>-0.91</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="31">
         <v>1.08</v>
       </c>
-      <c r="N4" s="29">
+      <c r="N4" s="39">
         <v>-1.08</v>
       </c>
-      <c r="O4" s="34">
+      <c r="O4" s="36">
         <v>-3.91</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="37">
         <v>-1.41</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="27">
         <v>-4.49</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="28">
         <v>-11.06</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="32">
         <v>-8.56</v>
       </c>
-      <c r="T4" s="39">
+      <c r="T4" s="33">
         <v>-40.4</v>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       <c r="C5" t="str">
         <v>603300</v>
       </c>
-      <c r="D5" s="52" t="str">
+      <c r="D5" s="51" t="str">
         <v>净卖: -6041.68万</v>
       </c>
       <c r="E5">
@@ -4934,37 +4934,37 @@
       <c r="I5" s="48">
         <v>3.56</v>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="42">
         <v>5.34</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="43">
         <v>1.02</v>
       </c>
-      <c r="L5" s="46">
+      <c r="L5" s="52">
         <v>3.05</v>
       </c>
-      <c r="M5" s="40">
+      <c r="M5" s="44">
         <v>0.85</v>
       </c>
-      <c r="N5" s="47">
+      <c r="N5" s="40">
         <v>-2.03</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="45">
         <v>0.51</v>
       </c>
-      <c r="P5" s="42">
+      <c r="P5" s="41">
         <v>-2.63</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="49">
         <v>-9.32</v>
       </c>
-      <c r="R5" s="51">
+      <c r="R5" s="46">
         <v>-6.78</v>
       </c>
-      <c r="S5" s="43">
+      <c r="S5" s="50">
         <v>-13.73</v>
       </c>
-      <c r="T5" s="44">
+      <c r="T5" s="47">
         <v>-39.24</v>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       <c r="C6" t="str">
         <v>603985</v>
       </c>
-      <c r="D6" s="58" t="str">
+      <c r="D6" s="53" t="str">
         <v>净卖: -484.50万</v>
       </c>
       <c r="E6">
@@ -4993,37 +4993,37 @@
       <c r="H6">
         <v>10.01</v>
       </c>
-      <c r="I6" s="59">
+      <c r="I6" s="54">
         <v>0</v>
       </c>
-      <c r="J6" s="53">
+      <c r="J6" s="55">
         <v>10.01</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="56">
         <v>7.17</v>
       </c>
-      <c r="L6" s="57">
+      <c r="L6" s="61">
         <v>-3.55</v>
       </c>
-      <c r="M6" s="61">
+      <c r="M6" s="62">
         <v>-10.59</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="57">
         <v>-1.61</v>
       </c>
-      <c r="O6" s="62">
+      <c r="O6" s="58">
         <v>2.32</v>
       </c>
       <c r="P6" s="63">
         <v>3.87</v>
       </c>
-      <c r="Q6" s="64">
+      <c r="Q6" s="59">
         <v>6.33</v>
       </c>
-      <c r="R6" s="55">
+      <c r="R6" s="64">
         <v>4.33</v>
       </c>
-      <c r="S6" s="56">
+      <c r="S6" s="60">
         <v>5.68</v>
       </c>
       <c r="T6" s="65">
@@ -5055,40 +5055,40 @@
       <c r="H7">
         <v>10.13</v>
       </c>
-      <c r="I7" s="78">
+      <c r="I7" s="77">
         <v>0</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="71">
         <v>9.91</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="74">
         <v>15.8</v>
       </c>
       <c r="L7" s="75">
         <v>4.25</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="72">
         <v>14.62</v>
       </c>
-      <c r="N7" s="76">
+      <c r="N7" s="67">
         <v>19.34</v>
       </c>
-      <c r="O7" s="71">
+      <c r="O7" s="68">
         <v>27.36</v>
       </c>
-      <c r="P7" s="66">
+      <c r="P7" s="69">
         <v>27.36</v>
       </c>
-      <c r="Q7" s="72">
+      <c r="Q7" s="70">
         <v>25.24</v>
       </c>
-      <c r="R7" s="67">
+      <c r="R7" s="78">
         <v>24.53</v>
       </c>
-      <c r="S7" s="77">
+      <c r="S7" s="66">
         <v>22.88</v>
       </c>
-      <c r="T7" s="68">
+      <c r="T7" s="76">
         <v>76.89</v>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       <c r="C8" t="str">
         <v>603042</v>
       </c>
-      <c r="D8" s="89" t="str">
+      <c r="D8" s="85" t="str">
         <v>净买: 1056.82万</v>
       </c>
       <c r="E8">
@@ -5117,40 +5117,40 @@
       <c r="H8">
         <v>-0.69</v>
       </c>
-      <c r="I8" s="85">
+      <c r="I8" s="89">
         <v>6.28</v>
       </c>
-      <c r="J8" s="82">
+      <c r="J8" s="90">
         <v>7.66</v>
       </c>
-      <c r="K8" s="90">
+      <c r="K8" s="81">
         <v>9.48</v>
       </c>
-      <c r="L8" s="81">
+      <c r="L8" s="82">
         <v>12.44</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8" s="91">
         <v>11.93</v>
       </c>
-      <c r="N8" s="86">
+      <c r="N8" s="79">
         <v>9.99</v>
       </c>
-      <c r="O8" s="91">
+      <c r="O8" s="86">
         <v>8.73</v>
       </c>
-      <c r="P8" s="84">
+      <c r="P8" s="83">
         <v>12.5</v>
       </c>
-      <c r="Q8" s="79">
+      <c r="Q8" s="87">
         <v>9.86</v>
       </c>
-      <c r="R8" s="87">
+      <c r="R8" s="88">
         <v>3.71</v>
       </c>
-      <c r="S8" s="88">
+      <c r="S8" s="80">
         <v>5.21</v>
       </c>
-      <c r="T8" s="80">
+      <c r="T8" s="84">
         <v>36.24</v>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       <c r="C9" t="str">
         <v>603300</v>
       </c>
-      <c r="D9" s="101" t="str">
+      <c r="D9" s="95" t="str">
         <v>净卖: -5853.95万</v>
       </c>
       <c r="E9">
@@ -5179,40 +5179,40 @@
       <c r="H9">
         <v>-0.29</v>
       </c>
-      <c r="I9" s="102">
+      <c r="I9" s="96">
         <v>7.44</v>
       </c>
-      <c r="J9" s="97">
+      <c r="J9" s="102">
         <v>8.23</v>
       </c>
-      <c r="K9" s="103">
+      <c r="K9" s="92">
         <v>9.21</v>
       </c>
-      <c r="L9" s="98">
+      <c r="L9" s="93">
         <v>4.8</v>
       </c>
-      <c r="M9" s="104">
+      <c r="M9" s="103">
         <v>2.06</v>
       </c>
-      <c r="N9" s="94">
+      <c r="N9" s="98">
         <v>1.37</v>
       </c>
-      <c r="O9" s="92">
+      <c r="O9" s="104">
         <v>0.78</v>
       </c>
-      <c r="P9" s="95">
+      <c r="P9" s="97">
         <v>4.41</v>
       </c>
       <c r="Q9" s="99">
         <v>7.05</v>
       </c>
-      <c r="R9" s="93">
+      <c r="R9" s="100">
         <v>4.21</v>
       </c>
-      <c r="S9" s="96">
+      <c r="S9" s="94">
         <v>2.45</v>
       </c>
-      <c r="T9" s="100">
+      <c r="T9" s="101">
         <v>-29.77</v>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       <c r="C10" t="str">
         <v>002028</v>
       </c>
-      <c r="D10" s="116" t="str">
+      <c r="D10" s="108" t="str">
         <v>净卖: -3647.56万</v>
       </c>
       <c r="E10">
@@ -5241,40 +5241,40 @@
       <c r="H10">
         <v>7.27</v>
       </c>
-      <c r="I10" s="108">
+      <c r="I10" s="115">
         <v>2.54</v>
       </c>
-      <c r="J10" s="109">
+      <c r="J10" s="106">
         <v>9.99</v>
       </c>
-      <c r="K10" s="110">
+      <c r="K10" s="109">
         <v>6.69</v>
       </c>
-      <c r="L10" s="105">
+      <c r="L10" s="110">
         <v>5.58</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="116">
         <v>1.57</v>
       </c>
-      <c r="N10" s="112">
+      <c r="N10" s="117">
         <v>3.49</v>
       </c>
-      <c r="O10" s="117">
+      <c r="O10" s="111">
         <v>5.22</v>
       </c>
-      <c r="P10" s="113">
+      <c r="P10" s="112">
         <v>4.9</v>
       </c>
-      <c r="Q10" s="106">
+      <c r="Q10" s="105">
         <v>3.53</v>
       </c>
-      <c r="R10" s="114">
+      <c r="R10" s="107">
         <v>6.54</v>
       </c>
-      <c r="S10" s="107">
+      <c r="S10" s="113">
         <v>8.07</v>
       </c>
-      <c r="T10" s="115">
+      <c r="T10" s="114">
         <v>184.76</v>
       </c>
     </row>
@@ -5288,7 +5288,7 @@
       <c r="C11" t="str">
         <v>603257</v>
       </c>
-      <c r="D11" s="130" t="str">
+      <c r="D11" s="126" t="str">
         <v>净卖: -308.53万</v>
       </c>
       <c r="E11">
@@ -5303,40 +5303,40 @@
       <c r="H11">
         <v>0.04</v>
       </c>
-      <c r="I11" s="128">
+      <c r="I11" s="127">
         <v>3.45</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="128">
         <v>3.45</v>
       </c>
-      <c r="K11" s="124">
+      <c r="K11" s="123">
         <v>4.99</v>
       </c>
-      <c r="L11" s="119">
+      <c r="L11" s="118">
         <v>3.55</v>
       </c>
-      <c r="M11" s="122">
+      <c r="M11" s="125">
         <v>9.31</v>
       </c>
-      <c r="N11" s="120">
+      <c r="N11" s="119">
         <v>6.44</v>
       </c>
-      <c r="O11" s="123">
+      <c r="O11" s="129">
         <v>5.49</v>
       </c>
-      <c r="P11" s="121">
+      <c r="P11" s="120">
         <v>4.71</v>
       </c>
-      <c r="Q11" s="125">
+      <c r="Q11" s="121">
         <v>3.2</v>
       </c>
-      <c r="R11" s="129">
+      <c r="R11" s="130">
         <v>3.82</v>
       </c>
-      <c r="S11" s="126">
+      <c r="S11" s="124">
         <v>3.18</v>
       </c>
-      <c r="T11" s="127">
+      <c r="T11" s="122">
         <v>15.42</v>
       </c>
     </row>
@@ -5350,7 +5350,7 @@
       <c r="C12" t="str">
         <v>603280</v>
       </c>
-      <c r="D12" s="133" t="str">
+      <c r="D12" s="138" t="str">
         <v>净卖: -740.40万</v>
       </c>
       <c r="E12">
@@ -5365,40 +5365,40 @@
       <c r="H12">
         <v>3.37</v>
       </c>
-      <c r="I12" s="137">
+      <c r="I12" s="139">
         <v>6.41</v>
       </c>
-      <c r="J12" s="141">
+      <c r="J12" s="143">
         <v>17.04</v>
       </c>
-      <c r="K12" s="138">
+      <c r="K12" s="131">
         <v>28.75</v>
       </c>
-      <c r="L12" s="134">
+      <c r="L12" s="132">
         <v>41.65</v>
       </c>
-      <c r="M12" s="143">
+      <c r="M12" s="140">
         <v>38.83</v>
       </c>
-      <c r="N12" s="131">
+      <c r="N12" s="133">
         <v>52.72</v>
       </c>
-      <c r="O12" s="135">
+      <c r="O12" s="136">
         <v>67.99</v>
       </c>
-      <c r="P12" s="142">
+      <c r="P12" s="134">
         <v>84.77</v>
       </c>
-      <c r="Q12" s="139">
+      <c r="Q12" s="135">
         <v>103.26</v>
       </c>
-      <c r="R12" s="140">
+      <c r="R12" s="141">
         <v>112.93</v>
       </c>
-      <c r="S12" s="136">
+      <c r="S12" s="142">
         <v>122.68</v>
       </c>
-      <c r="T12" s="132">
+      <c r="T12" s="137">
         <v>28.97</v>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       <c r="C13" t="str">
         <v>603280</v>
       </c>
-      <c r="D13" s="144" t="str">
+      <c r="D13" s="149" t="str">
         <v>净卖: -1064.89万</v>
       </c>
       <c r="E13">
@@ -5427,40 +5427,40 @@
       <c r="H13">
         <v>4.74</v>
       </c>
-      <c r="I13" s="145">
+      <c r="I13" s="150">
         <v>5.02</v>
       </c>
-      <c r="J13" s="150">
+      <c r="J13" s="152">
         <v>15.53</v>
       </c>
-      <c r="K13" s="155">
+      <c r="K13" s="153">
         <v>27.09</v>
       </c>
-      <c r="L13" s="153">
+      <c r="L13" s="146">
         <v>24.57</v>
       </c>
-      <c r="M13" s="154">
+      <c r="M13" s="147">
         <v>37.03</v>
       </c>
       <c r="N13" s="156">
         <v>50.73</v>
       </c>
-      <c r="O13" s="146">
+      <c r="O13" s="154">
         <v>65.79</v>
       </c>
-      <c r="P13" s="151">
+      <c r="P13" s="144">
         <v>82.38</v>
       </c>
-      <c r="Q13" s="147">
+      <c r="Q13" s="151">
         <v>91.06</v>
       </c>
-      <c r="R13" s="148">
+      <c r="R13" s="155">
         <v>99.8</v>
       </c>
-      <c r="S13" s="152">
+      <c r="S13" s="148">
         <v>90.16</v>
       </c>
-      <c r="T13" s="149">
+      <c r="T13" s="145">
         <v>15.72</v>
       </c>
     </row>
@@ -5489,37 +5489,37 @@
       <c r="H14">
         <v>2.49</v>
       </c>
-      <c r="I14" s="163">
+      <c r="I14" s="158">
         <v>7.32</v>
       </c>
-      <c r="J14" s="167">
+      <c r="J14" s="163">
         <v>18.05</v>
       </c>
-      <c r="K14" s="168">
+      <c r="K14" s="167">
         <v>25.05</v>
       </c>
-      <c r="L14" s="158">
+      <c r="L14" s="161">
         <v>37.57</v>
       </c>
-      <c r="M14" s="169">
+      <c r="M14" s="159">
         <v>35.41</v>
       </c>
-      <c r="N14" s="164">
+      <c r="N14" s="160">
         <v>38.35</v>
       </c>
-      <c r="O14" s="160">
+      <c r="O14" s="168">
         <v>38.24</v>
       </c>
-      <c r="P14" s="165">
+      <c r="P14" s="162">
         <v>39.05</v>
       </c>
-      <c r="Q14" s="161">
+      <c r="Q14" s="164">
         <v>33.92</v>
       </c>
-      <c r="R14" s="159">
+      <c r="R14" s="169">
         <v>47.32</v>
       </c>
-      <c r="S14" s="162">
+      <c r="S14" s="165">
         <v>62.05</v>
       </c>
       <c r="T14" s="157">
@@ -5536,7 +5536,7 @@
       <c r="C15" t="str">
         <v>600113</v>
       </c>
-      <c r="D15" s="181" t="str">
+      <c r="D15" s="173" t="str">
         <v>净卖: -2870.19万</v>
       </c>
       <c r="E15">
@@ -5551,40 +5551,40 @@
       <c r="H15">
         <v>-0.58</v>
       </c>
-      <c r="I15" s="176">
+      <c r="I15" s="179">
         <v>10.65</v>
       </c>
-      <c r="J15" s="177">
+      <c r="J15" s="180">
         <v>8.91</v>
       </c>
-      <c r="K15" s="171">
+      <c r="K15" s="170">
         <v>11.28</v>
       </c>
-      <c r="L15" s="172">
+      <c r="L15" s="175">
         <v>11.2</v>
       </c>
-      <c r="M15" s="173">
+      <c r="M15" s="181">
         <v>11.85</v>
       </c>
       <c r="N15" s="182">
         <v>7.72</v>
       </c>
-      <c r="O15" s="174">
+      <c r="O15" s="176">
         <v>18.5</v>
       </c>
-      <c r="P15" s="179">
+      <c r="P15" s="171">
         <v>30.35</v>
       </c>
-      <c r="Q15" s="180">
+      <c r="Q15" s="172">
         <v>33.04</v>
       </c>
-      <c r="R15" s="170">
+      <c r="R15" s="174">
         <v>22.78</v>
       </c>
-      <c r="S15" s="178">
+      <c r="S15" s="177">
         <v>28.54</v>
       </c>
-      <c r="T15" s="175">
+      <c r="T15" s="178">
         <v>2.59</v>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       <c r="C16" t="str">
         <v>000014</v>
       </c>
-      <c r="D16" s="183" t="str">
+      <c r="D16" s="190" t="str">
         <v>净卖: -962.87万</v>
       </c>
       <c r="E16">
@@ -5619,34 +5619,34 @@
       <c r="J16" s="184">
         <v>-15.5</v>
       </c>
-      <c r="K16" s="192">
+      <c r="K16" s="195">
         <v>-14.75</v>
       </c>
-      <c r="L16" s="193">
+      <c r="L16" s="185">
         <v>-14.05</v>
       </c>
-      <c r="M16" s="185">
+      <c r="M16" s="191">
         <v>-12.8</v>
       </c>
-      <c r="N16" s="195">
+      <c r="N16" s="192">
         <v>-18.7</v>
       </c>
-      <c r="O16" s="186">
+      <c r="O16" s="193">
         <v>-26.81</v>
       </c>
-      <c r="P16" s="187">
+      <c r="P16" s="186">
         <v>-26.39</v>
       </c>
-      <c r="Q16" s="194">
+      <c r="Q16" s="187">
         <v>-31.3</v>
       </c>
-      <c r="R16" s="189">
+      <c r="R16" s="183">
         <v>-29.12</v>
       </c>
-      <c r="S16" s="190">
+      <c r="S16" s="194">
         <v>-29.2</v>
       </c>
-      <c r="T16" s="191">
+      <c r="T16" s="189">
         <v>-47.66</v>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       <c r="C17" t="str">
         <v>688577</v>
       </c>
-      <c r="D17" s="207" t="str">
+      <c r="D17" s="199" t="str">
         <v>净卖: -1039.47万</v>
       </c>
       <c r="E17">
@@ -5678,10 +5678,10 @@
       <c r="I17" s="200">
         <v>-19.96</v>
       </c>
-      <c r="J17" s="208">
+      <c r="J17" s="204">
         <v>-18.66</v>
       </c>
-      <c r="K17" s="204">
+      <c r="K17" s="196">
         <v>-15.24</v>
       </c>
       <c r="L17" s="201">
@@ -5690,25 +5690,25 @@
       <c r="M17" s="205">
         <v>-17.76</v>
       </c>
-      <c r="N17" s="202">
+      <c r="N17" s="197">
         <v>-16.4</v>
       </c>
-      <c r="O17" s="196">
+      <c r="O17" s="206">
         <v>-18.64</v>
       </c>
-      <c r="P17" s="197">
+      <c r="P17" s="207">
         <v>-19.41</v>
       </c>
-      <c r="Q17" s="198">
+      <c r="Q17" s="202">
         <v>-10.36</v>
       </c>
-      <c r="R17" s="206">
+      <c r="R17" s="208">
         <v>-13.75</v>
       </c>
       <c r="S17" s="203">
         <v>-14.11</v>
       </c>
-      <c r="T17" s="199">
+      <c r="T17" s="198">
         <v>-38.74</v>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       <c r="C18" t="str">
         <v>603757</v>
       </c>
-      <c r="D18" s="210" t="str">
+      <c r="D18" s="218" t="str">
         <v>净卖: -7133.87万</v>
       </c>
       <c r="E18">
@@ -5737,40 +5737,40 @@
       <c r="H18">
         <v>-1.84</v>
       </c>
-      <c r="I18" s="216">
+      <c r="I18" s="213">
         <v>12.06</v>
       </c>
-      <c r="J18" s="209">
+      <c r="J18" s="214">
         <v>13.86</v>
       </c>
-      <c r="K18" s="211">
+      <c r="K18" s="219">
         <v>17.77</v>
       </c>
-      <c r="L18" s="219">
+      <c r="L18" s="220">
         <v>14.57</v>
       </c>
-      <c r="M18" s="212">
+      <c r="M18" s="210">
         <v>16.9</v>
       </c>
-      <c r="N18" s="217">
+      <c r="N18" s="211">
         <v>11.61</v>
       </c>
-      <c r="O18" s="213">
+      <c r="O18" s="217">
         <v>9.48</v>
       </c>
-      <c r="P18" s="214">
+      <c r="P18" s="221">
         <v>12.23</v>
       </c>
-      <c r="Q18" s="220">
+      <c r="Q18" s="209">
         <v>5.19</v>
       </c>
       <c r="R18" s="215">
         <v>8.18</v>
       </c>
-      <c r="S18" s="218">
+      <c r="S18" s="216">
         <v>6.47</v>
       </c>
-      <c r="T18" s="221">
+      <c r="T18" s="212">
         <v>32.37</v>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       <c r="C19" t="str">
         <v>002117</v>
       </c>
-      <c r="D19" s="226" t="str">
+      <c r="D19" s="228" t="str">
         <v>净卖: -1144.93万</v>
       </c>
       <c r="E19">
@@ -5799,40 +5799,40 @@
       <c r="H19">
         <v>0.29</v>
       </c>
-      <c r="I19" s="223">
+      <c r="I19" s="229">
         <v>-10.25</v>
       </c>
       <c r="J19" s="232">
         <v>-10.69</v>
       </c>
-      <c r="K19" s="224">
+      <c r="K19" s="234">
         <v>-13.72</v>
       </c>
       <c r="L19" s="225">
         <v>-12.78</v>
       </c>
-      <c r="M19" s="228">
+      <c r="M19" s="230">
         <v>-12.64</v>
       </c>
-      <c r="N19" s="229">
+      <c r="N19" s="233">
         <v>-8.52</v>
       </c>
-      <c r="O19" s="233">
+      <c r="O19" s="226">
         <v>-12.27</v>
       </c>
-      <c r="P19" s="230">
+      <c r="P19" s="222">
         <v>-11.26</v>
       </c>
-      <c r="Q19" s="234">
+      <c r="Q19" s="231">
         <v>-12.13</v>
       </c>
-      <c r="R19" s="222">
+      <c r="R19" s="223">
         <v>-12.78</v>
       </c>
       <c r="S19" s="227">
         <v>-12.56</v>
       </c>
-      <c r="T19" s="231">
+      <c r="T19" s="224">
         <v>-27</v>
       </c>
     </row>
@@ -5846,7 +5846,7 @@
       <c r="C20" t="str">
         <v>600246</v>
       </c>
-      <c r="D20" s="242" t="str">
+      <c r="D20" s="247" t="str">
         <v>净买: 1107.56万</v>
       </c>
       <c r="E20">
@@ -5864,37 +5864,37 @@
       <c r="I20" s="243">
         <v>-10.98</v>
       </c>
-      <c r="J20" s="244">
+      <c r="J20" s="237">
         <v>-11.79</v>
       </c>
-      <c r="K20" s="245">
+      <c r="K20" s="238">
         <v>-11.87</v>
       </c>
-      <c r="L20" s="246">
+      <c r="L20" s="239">
         <v>-11.54</v>
       </c>
-      <c r="M20" s="238">
+      <c r="M20" s="240">
         <v>-10.08</v>
       </c>
-      <c r="N20" s="247">
+      <c r="N20" s="241">
         <v>-10.08</v>
       </c>
       <c r="O20" s="235">
         <v>-11.71</v>
       </c>
-      <c r="P20" s="239">
+      <c r="P20" s="242">
         <v>-12.52</v>
       </c>
       <c r="Q20" s="236">
         <v>-11.95</v>
       </c>
-      <c r="R20" s="237">
+      <c r="R20" s="244">
         <v>-12.44</v>
       </c>
-      <c r="S20" s="240">
+      <c r="S20" s="245">
         <v>-14.15</v>
       </c>
-      <c r="T20" s="241">
+      <c r="T20" s="246">
         <v>-21.22</v>
       </c>
     </row>
@@ -5957,40 +5957,40 @@
       <c r="F22" t="str"/>
       <c r="G22" t="str"/>
       <c r="H22" t="str"/>
-      <c r="I22" s="248">
+      <c r="I22" s="251">
         <v>57.89</v>
       </c>
-      <c r="J22" s="252">
+      <c r="J22" s="258">
         <v>73.68</v>
       </c>
-      <c r="K22" s="249">
+      <c r="K22" s="252">
         <v>73.68</v>
       </c>
-      <c r="L22" s="258">
+      <c r="L22" s="254">
         <v>68.42</v>
       </c>
-      <c r="M22" s="254">
+      <c r="M22" s="255">
         <v>68.42</v>
       </c>
-      <c r="N22" s="259">
+      <c r="N22" s="253">
         <v>57.89</v>
       </c>
-      <c r="O22" s="253">
+      <c r="O22" s="259">
         <v>68.42</v>
       </c>
-      <c r="P22" s="250">
+      <c r="P22" s="248">
         <v>63.16</v>
       </c>
-      <c r="Q22" s="255">
+      <c r="Q22" s="256">
         <v>63.16</v>
       </c>
-      <c r="R22" s="256">
+      <c r="R22" s="257">
         <v>63.16</v>
       </c>
-      <c r="S22" s="257">
+      <c r="S22" s="249">
         <v>63.16</v>
       </c>
-      <c r="T22" s="251">
+      <c r="T22" s="250">
         <v>52.63</v>
       </c>
     </row>
@@ -6005,40 +6005,40 @@
       <c r="F23" t="str"/>
       <c r="G23" t="str"/>
       <c r="H23" t="str"/>
-      <c r="I23" s="265">
+      <c r="I23" s="266">
         <v>0.61</v>
       </c>
-      <c r="J23" s="267">
+      <c r="J23" s="270">
         <v>4.05</v>
       </c>
-      <c r="K23" s="268">
+      <c r="K23" s="262">
         <v>6.6</v>
       </c>
-      <c r="L23" s="269">
+      <c r="L23" s="271">
         <v>6.65</v>
       </c>
-      <c r="M23" s="270">
+      <c r="M23" s="260">
         <v>7.77</v>
       </c>
-      <c r="N23" s="262">
+      <c r="N23" s="263">
         <v>9.94</v>
       </c>
-      <c r="O23" s="266">
+      <c r="O23" s="267">
         <v>11.31</v>
       </c>
-      <c r="P23" s="271">
+      <c r="P23" s="264">
         <v>13.62</v>
       </c>
-      <c r="Q23" s="260">
+      <c r="Q23" s="268">
         <v>14.92</v>
       </c>
-      <c r="R23" s="261">
+      <c r="R23" s="265">
         <v>16.06</v>
       </c>
-      <c r="S23" s="264">
+      <c r="S23" s="261">
         <v>15.55</v>
       </c>
-      <c r="T23" s="263">
+      <c r="T23" s="269">
         <v>10.05</v>
       </c>
     </row>

--- a/youzi/牛散唐汉若/index.xlsx
+++ b/youzi/牛散唐汉若/index.xlsx
@@ -39,43 +39,223 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCDEAD4"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE3F3E6"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA4D9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56BA6D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,31 +267,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D5D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,13 +399,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF66C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -183,19 +471,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56974"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,25 +591,541 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -237,97 +1137,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF56BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0EBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D5D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -339,13 +1155,199 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -357,49 +1359,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07A"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -411,61 +1371,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -477,67 +1413,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -549,31 +1449,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56974"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -591,931 +1533,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCB2D3C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1533,61 +1569,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF5C9CE"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1630,30 +1654,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -4730,7 +4730,7 @@
       <c r="C2" t="str">
         <v>603300</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="12" t="str">
         <v>净买: 7263.08万</v>
       </c>
       <c r="E2">
@@ -4745,41 +4745,41 @@
       <c r="H2">
         <v>5.49</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="2">
         <v>4.31</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="3">
         <v>-6.1</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="13">
         <v>-0.65</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="4">
         <v>1.06</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="5">
         <v>-3.09</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="9">
         <v>-1.14</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="6">
         <v>-3.25</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="10">
         <v>-6.02</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="7">
         <v>-3.58</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="8">
         <v>-6.59</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="11">
         <v>-13.01</v>
       </c>
-      <c r="T2" s="8">
-        <v>-41.71</v>
+      <c r="T2" s="1">
+        <v>-42.36</v>
       </c>
     </row>
     <row r="3">
@@ -4792,7 +4792,7 @@
       <c r="C3" t="str">
         <v>002093</v>
       </c>
-      <c r="D3" s="23" t="str">
+      <c r="D3" s="20" t="str">
         <v>净卖: -871.26万</v>
       </c>
       <c r="E3">
@@ -4810,38 +4810,38 @@
       <c r="I3" s="14">
         <v>0</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="21">
         <v>10.04</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="22">
         <v>14.06</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="18">
         <v>21.08</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="19">
         <v>33.23</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="25">
         <v>46.59</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="15">
         <v>41.16</v>
       </c>
-      <c r="P3" s="25">
+      <c r="P3" s="16">
         <v>31.83</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="17">
         <v>44.98</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="23">
         <v>59.44</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="26">
         <v>43.47</v>
       </c>
-      <c r="T3" s="26">
-        <v>-2.61</v>
+      <c r="T3" s="24">
+        <v>-2.11</v>
       </c>
     </row>
     <row r="4">
@@ -4854,7 +4854,7 @@
       <c r="C4" t="str">
         <v>603300</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="28" t="str">
         <v>净买: 227.62万</v>
       </c>
       <c r="E4">
@@ -4869,41 +4869,41 @@
       <c r="H4">
         <v>-6.24</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="29">
         <v>-3.99</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="30">
         <v>1.58</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="33">
         <v>3.33</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="36">
         <v>-0.91</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="27">
         <v>1.08</v>
       </c>
-      <c r="N4" s="39">
+      <c r="N4" s="31">
         <v>-1.08</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="37">
         <v>-3.91</v>
       </c>
-      <c r="P4" s="37">
+      <c r="P4" s="34">
         <v>-1.41</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="Q4" s="35">
         <v>-4.49</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="38">
         <v>-11.06</v>
       </c>
       <c r="S4" s="32">
         <v>-8.56</v>
       </c>
-      <c r="T4" s="33">
-        <v>-40.4</v>
+      <c r="T4" s="39">
+        <v>-41.06</v>
       </c>
     </row>
     <row r="5">
@@ -4916,7 +4916,7 @@
       <c r="C5" t="str">
         <v>603300</v>
       </c>
-      <c r="D5" s="51" t="str">
+      <c r="D5" s="41" t="str">
         <v>净卖: -6041.68万</v>
       </c>
       <c r="E5">
@@ -4931,41 +4931,41 @@
       <c r="H5">
         <v>2.16</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="46">
         <v>3.56</v>
       </c>
       <c r="J5" s="42">
         <v>5.34</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="44">
         <v>1.02</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="43">
         <v>3.05</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="47">
         <v>0.85</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="51">
         <v>-2.03</v>
       </c>
-      <c r="O5" s="45">
+      <c r="O5" s="48">
         <v>0.51</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="52">
         <v>-2.63</v>
       </c>
       <c r="Q5" s="49">
         <v>-9.32</v>
       </c>
-      <c r="R5" s="46">
+      <c r="R5" s="40">
         <v>-6.78</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="45">
         <v>-13.73</v>
       </c>
-      <c r="T5" s="47">
-        <v>-39.24</v>
+      <c r="T5" s="50">
+        <v>-39.92</v>
       </c>
     </row>
     <row r="6">
@@ -4978,7 +4978,7 @@
       <c r="C6" t="str">
         <v>603985</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="55" t="str">
         <v>净卖: -484.50万</v>
       </c>
       <c r="E6">
@@ -4993,13 +4993,13 @@
       <c r="H6">
         <v>10.01</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="59">
         <v>0</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="56">
         <v>10.01</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="53">
         <v>7.17</v>
       </c>
       <c r="L6" s="61">
@@ -5011,23 +5011,23 @@
       <c r="N6" s="57">
         <v>-1.61</v>
       </c>
-      <c r="O6" s="58">
+      <c r="O6" s="63">
         <v>2.32</v>
       </c>
-      <c r="P6" s="63">
+      <c r="P6" s="54">
         <v>3.87</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="64">
         <v>6.33</v>
       </c>
-      <c r="R6" s="64">
+      <c r="R6" s="58">
         <v>4.33</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="65">
         <v>5.68</v>
       </c>
-      <c r="T6" s="65">
-        <v>58.81</v>
+      <c r="T6" s="60">
+        <v>55.46</v>
       </c>
     </row>
     <row r="7">
@@ -5040,7 +5040,7 @@
       <c r="C7" t="str">
         <v>600744</v>
       </c>
-      <c r="D7" s="73" t="str">
+      <c r="D7" s="71" t="str">
         <v>净卖: -165.95万</v>
       </c>
       <c r="E7">
@@ -5055,41 +5055,41 @@
       <c r="H7">
         <v>10.13</v>
       </c>
-      <c r="I7" s="77">
+      <c r="I7" s="78">
         <v>0</v>
       </c>
-      <c r="J7" s="71">
+      <c r="J7" s="72">
         <v>9.91</v>
       </c>
-      <c r="K7" s="74">
+      <c r="K7" s="69">
         <v>15.8</v>
       </c>
-      <c r="L7" s="75">
+      <c r="L7" s="73">
         <v>4.25</v>
       </c>
-      <c r="M7" s="72">
+      <c r="M7" s="76">
         <v>14.62</v>
       </c>
-      <c r="N7" s="67">
+      <c r="N7" s="66">
         <v>19.34</v>
       </c>
-      <c r="O7" s="68">
+      <c r="O7" s="77">
         <v>27.36</v>
       </c>
-      <c r="P7" s="69">
+      <c r="P7" s="74">
         <v>27.36</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="75">
         <v>25.24</v>
       </c>
-      <c r="R7" s="78">
+      <c r="R7" s="67">
         <v>24.53</v>
       </c>
-      <c r="S7" s="66">
+      <c r="S7" s="70">
         <v>22.88</v>
       </c>
-      <c r="T7" s="76">
-        <v>76.89</v>
+      <c r="T7" s="68">
+        <v>90.57</v>
       </c>
     </row>
     <row r="8">
@@ -5102,7 +5102,7 @@
       <c r="C8" t="str">
         <v>603042</v>
       </c>
-      <c r="D8" s="85" t="str">
+      <c r="D8" s="79" t="str">
         <v>净买: 1056.82万</v>
       </c>
       <c r="E8">
@@ -5117,41 +5117,41 @@
       <c r="H8">
         <v>-0.69</v>
       </c>
-      <c r="I8" s="89">
+      <c r="I8" s="86">
         <v>6.28</v>
       </c>
-      <c r="J8" s="90">
+      <c r="J8" s="88">
         <v>7.66</v>
       </c>
-      <c r="K8" s="81">
+      <c r="K8" s="89">
         <v>9.48</v>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="80">
         <v>12.44</v>
       </c>
-      <c r="M8" s="91">
+      <c r="M8" s="90">
         <v>11.93</v>
       </c>
-      <c r="N8" s="79">
+      <c r="N8" s="83">
         <v>9.99</v>
       </c>
-      <c r="O8" s="86">
+      <c r="O8" s="84">
         <v>8.73</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8" s="81">
         <v>12.5</v>
       </c>
-      <c r="Q8" s="87">
+      <c r="Q8" s="85">
         <v>9.86</v>
       </c>
-      <c r="R8" s="88">
+      <c r="R8" s="82">
         <v>3.71</v>
       </c>
-      <c r="S8" s="80">
+      <c r="S8" s="91">
         <v>5.21</v>
       </c>
-      <c r="T8" s="84">
-        <v>36.24</v>
+      <c r="T8" s="87">
+        <v>38.57</v>
       </c>
     </row>
     <row r="9">
@@ -5164,7 +5164,7 @@
       <c r="C9" t="str">
         <v>603300</v>
       </c>
-      <c r="D9" s="95" t="str">
+      <c r="D9" s="98" t="str">
         <v>净卖: -5853.95万</v>
       </c>
       <c r="E9">
@@ -5179,41 +5179,41 @@
       <c r="H9">
         <v>-0.29</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="93">
         <v>7.44</v>
       </c>
-      <c r="J9" s="102">
+      <c r="J9" s="99">
         <v>8.23</v>
       </c>
-      <c r="K9" s="92">
+      <c r="K9" s="100">
         <v>9.21</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="101">
         <v>4.8</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="94">
         <v>2.06</v>
       </c>
-      <c r="N9" s="98">
+      <c r="N9" s="102">
         <v>1.37</v>
       </c>
-      <c r="O9" s="104">
+      <c r="O9" s="96">
         <v>0.78</v>
       </c>
-      <c r="P9" s="97">
+      <c r="P9" s="95">
         <v>4.41</v>
       </c>
-      <c r="Q9" s="99">
+      <c r="Q9" s="103">
         <v>7.05</v>
       </c>
-      <c r="R9" s="100">
+      <c r="R9" s="97">
         <v>4.21</v>
       </c>
-      <c r="S9" s="94">
+      <c r="S9" s="104">
         <v>2.45</v>
       </c>
-      <c r="T9" s="101">
-        <v>-29.77</v>
+      <c r="T9" s="92">
+        <v>-30.56</v>
       </c>
     </row>
     <row r="10">
@@ -5226,7 +5226,7 @@
       <c r="C10" t="str">
         <v>002028</v>
       </c>
-      <c r="D10" s="108" t="str">
+      <c r="D10" s="110" t="str">
         <v>净卖: -3647.56万</v>
       </c>
       <c r="E10">
@@ -5241,41 +5241,41 @@
       <c r="H10">
         <v>7.27</v>
       </c>
-      <c r="I10" s="115">
+      <c r="I10" s="108">
         <v>2.54</v>
       </c>
-      <c r="J10" s="106">
+      <c r="J10" s="111">
         <v>9.99</v>
       </c>
-      <c r="K10" s="109">
+      <c r="K10" s="113">
         <v>6.69</v>
       </c>
-      <c r="L10" s="110">
+      <c r="L10" s="116">
         <v>5.58</v>
       </c>
-      <c r="M10" s="116">
+      <c r="M10" s="109">
         <v>1.57</v>
       </c>
       <c r="N10" s="117">
         <v>3.49</v>
       </c>
-      <c r="O10" s="111">
+      <c r="O10" s="114">
         <v>5.22</v>
       </c>
-      <c r="P10" s="112">
+      <c r="P10" s="105">
         <v>4.9</v>
       </c>
-      <c r="Q10" s="105">
+      <c r="Q10" s="115">
         <v>3.53</v>
       </c>
-      <c r="R10" s="107">
+      <c r="R10" s="106">
         <v>6.54</v>
       </c>
-      <c r="S10" s="113">
+      <c r="S10" s="107">
         <v>8.07</v>
       </c>
-      <c r="T10" s="114">
-        <v>184.76</v>
+      <c r="T10" s="112">
+        <v>190.12</v>
       </c>
     </row>
     <row r="11">
@@ -5288,7 +5288,7 @@
       <c r="C11" t="str">
         <v>603257</v>
       </c>
-      <c r="D11" s="126" t="str">
+      <c r="D11" s="124" t="str">
         <v>净卖: -308.53万</v>
       </c>
       <c r="E11">
@@ -5303,41 +5303,41 @@
       <c r="H11">
         <v>0.04</v>
       </c>
-      <c r="I11" s="127">
+      <c r="I11" s="118">
         <v>3.45</v>
       </c>
-      <c r="J11" s="128">
+      <c r="J11" s="119">
         <v>3.45</v>
       </c>
-      <c r="K11" s="123">
+      <c r="K11" s="125">
         <v>4.99</v>
       </c>
-      <c r="L11" s="118">
+      <c r="L11" s="127">
         <v>3.55</v>
       </c>
-      <c r="M11" s="125">
+      <c r="M11" s="120">
         <v>9.31</v>
       </c>
-      <c r="N11" s="119">
+      <c r="N11" s="121">
         <v>6.44</v>
       </c>
-      <c r="O11" s="129">
+      <c r="O11" s="122">
         <v>5.49</v>
       </c>
-      <c r="P11" s="120">
+      <c r="P11" s="123">
         <v>4.71</v>
       </c>
-      <c r="Q11" s="121">
+      <c r="Q11" s="128">
         <v>3.2</v>
       </c>
-      <c r="R11" s="130">
+      <c r="R11" s="129">
         <v>3.82</v>
       </c>
-      <c r="S11" s="124">
+      <c r="S11" s="126">
         <v>3.18</v>
       </c>
-      <c r="T11" s="122">
-        <v>15.42</v>
+      <c r="T11" s="130">
+        <v>17.25</v>
       </c>
     </row>
     <row r="12">
@@ -5350,7 +5350,7 @@
       <c r="C12" t="str">
         <v>603280</v>
       </c>
-      <c r="D12" s="138" t="str">
+      <c r="D12" s="142" t="str">
         <v>净卖: -740.40万</v>
       </c>
       <c r="E12">
@@ -5365,41 +5365,41 @@
       <c r="H12">
         <v>3.37</v>
       </c>
-      <c r="I12" s="139">
+      <c r="I12" s="143">
         <v>6.41</v>
       </c>
-      <c r="J12" s="143">
+      <c r="J12" s="135">
         <v>17.04</v>
       </c>
       <c r="K12" s="131">
         <v>28.75</v>
       </c>
-      <c r="L12" s="132">
+      <c r="L12" s="136">
         <v>41.65</v>
       </c>
-      <c r="M12" s="140">
+      <c r="M12" s="132">
         <v>38.83</v>
       </c>
-      <c r="N12" s="133">
+      <c r="N12" s="137">
         <v>52.72</v>
       </c>
-      <c r="O12" s="136">
+      <c r="O12" s="133">
         <v>67.99</v>
       </c>
-      <c r="P12" s="134">
+      <c r="P12" s="138">
         <v>84.77</v>
       </c>
-      <c r="Q12" s="135">
+      <c r="Q12" s="134">
         <v>103.26</v>
       </c>
-      <c r="R12" s="141">
+      <c r="R12" s="139">
         <v>112.93</v>
       </c>
-      <c r="S12" s="142">
+      <c r="S12" s="140">
         <v>122.68</v>
       </c>
-      <c r="T12" s="137">
-        <v>28.97</v>
+      <c r="T12" s="141">
+        <v>29.57</v>
       </c>
     </row>
     <row r="13">
@@ -5412,7 +5412,7 @@
       <c r="C13" t="str">
         <v>603280</v>
       </c>
-      <c r="D13" s="149" t="str">
+      <c r="D13" s="147" t="str">
         <v>净卖: -1064.89万</v>
       </c>
       <c r="E13">
@@ -5427,41 +5427,41 @@
       <c r="H13">
         <v>4.74</v>
       </c>
-      <c r="I13" s="150">
+      <c r="I13" s="144">
         <v>5.02</v>
       </c>
-      <c r="J13" s="152">
+      <c r="J13" s="145">
         <v>15.53</v>
       </c>
-      <c r="K13" s="153">
+      <c r="K13" s="148">
         <v>27.09</v>
       </c>
-      <c r="L13" s="146">
+      <c r="L13" s="153">
         <v>24.57</v>
       </c>
-      <c r="M13" s="147">
+      <c r="M13" s="149">
         <v>37.03</v>
       </c>
-      <c r="N13" s="156">
+      <c r="N13" s="151">
         <v>50.73</v>
       </c>
       <c r="O13" s="154">
         <v>65.79</v>
       </c>
-      <c r="P13" s="144">
+      <c r="P13" s="152">
         <v>82.38</v>
       </c>
-      <c r="Q13" s="151">
+      <c r="Q13" s="155">
         <v>91.06</v>
       </c>
-      <c r="R13" s="155">
+      <c r="R13" s="146">
         <v>99.8</v>
       </c>
-      <c r="S13" s="148">
+      <c r="S13" s="150">
         <v>90.16</v>
       </c>
-      <c r="T13" s="145">
-        <v>15.72</v>
+      <c r="T13" s="156">
+        <v>16.26</v>
       </c>
     </row>
     <row r="14">
@@ -5469,12 +5469,12 @@
         <v>2025-08-12</v>
       </c>
       <c r="B14" t="str">
-        <v>XD浙江东</v>
+        <v>浙江东日</v>
       </c>
       <c r="C14" t="str">
         <v>600113</v>
       </c>
-      <c r="D14" s="166" t="str">
+      <c r="D14" s="169" t="str">
         <v>净卖: -1621.26万</v>
       </c>
       <c r="E14">
@@ -5489,41 +5489,41 @@
       <c r="H14">
         <v>2.49</v>
       </c>
-      <c r="I14" s="158">
+      <c r="I14" s="157">
         <v>7.32</v>
       </c>
-      <c r="J14" s="163">
+      <c r="J14" s="158">
         <v>18.05</v>
       </c>
-      <c r="K14" s="167">
+      <c r="K14" s="159">
         <v>25.05</v>
       </c>
-      <c r="L14" s="161">
+      <c r="L14" s="163">
         <v>37.57</v>
       </c>
-      <c r="M14" s="159">
+      <c r="M14" s="164">
         <v>35.41</v>
       </c>
-      <c r="N14" s="160">
+      <c r="N14" s="165">
         <v>38.35</v>
       </c>
-      <c r="O14" s="168">
+      <c r="O14" s="160">
         <v>38.24</v>
       </c>
-      <c r="P14" s="162">
+      <c r="P14" s="166">
         <v>39.05</v>
       </c>
-      <c r="Q14" s="164">
+      <c r="Q14" s="167">
         <v>33.92</v>
       </c>
-      <c r="R14" s="169">
+      <c r="R14" s="168">
         <v>47.32</v>
       </c>
-      <c r="S14" s="165">
+      <c r="S14" s="161">
         <v>62.05</v>
       </c>
-      <c r="T14" s="157">
-        <v>27.54</v>
+      <c r="T14" s="162">
+        <v>25.7</v>
       </c>
     </row>
     <row r="15">
@@ -5531,12 +5531,12 @@
         <v>2025-08-15</v>
       </c>
       <c r="B15" t="str">
-        <v>XD浙江东</v>
+        <v>浙江东日</v>
       </c>
       <c r="C15" t="str">
         <v>600113</v>
       </c>
-      <c r="D15" s="173" t="str">
+      <c r="D15" s="182" t="str">
         <v>净卖: -2870.19万</v>
       </c>
       <c r="E15">
@@ -5551,41 +5551,41 @@
       <c r="H15">
         <v>-0.58</v>
       </c>
-      <c r="I15" s="179">
+      <c r="I15" s="176">
         <v>10.65</v>
       </c>
-      <c r="J15" s="180">
+      <c r="J15" s="170">
         <v>8.91</v>
       </c>
-      <c r="K15" s="170">
+      <c r="K15" s="178">
         <v>11.28</v>
       </c>
-      <c r="L15" s="175">
+      <c r="L15" s="171">
         <v>11.2</v>
       </c>
-      <c r="M15" s="181">
+      <c r="M15" s="172">
         <v>11.85</v>
       </c>
-      <c r="N15" s="182">
+      <c r="N15" s="179">
         <v>7.72</v>
       </c>
-      <c r="O15" s="176">
+      <c r="O15" s="177">
         <v>18.5</v>
       </c>
-      <c r="P15" s="171">
+      <c r="P15" s="180">
         <v>30.35</v>
       </c>
-      <c r="Q15" s="172">
+      <c r="Q15" s="173">
         <v>33.04</v>
       </c>
       <c r="R15" s="174">
         <v>22.78</v>
       </c>
-      <c r="S15" s="177">
+      <c r="S15" s="181">
         <v>28.54</v>
       </c>
-      <c r="T15" s="178">
-        <v>2.59</v>
+      <c r="T15" s="175">
+        <v>1.11</v>
       </c>
     </row>
     <row r="16">
@@ -5598,7 +5598,7 @@
       <c r="C16" t="str">
         <v>000014</v>
       </c>
-      <c r="D16" s="190" t="str">
+      <c r="D16" s="185" t="str">
         <v>净卖: -962.87万</v>
       </c>
       <c r="E16">
@@ -5613,41 +5613,41 @@
       <c r="H16">
         <v>9.96</v>
       </c>
-      <c r="I16" s="188">
+      <c r="I16" s="183">
         <v>-12.33</v>
       </c>
-      <c r="J16" s="184">
+      <c r="J16" s="186">
         <v>-15.5</v>
       </c>
-      <c r="K16" s="195">
+      <c r="K16" s="193">
         <v>-14.75</v>
       </c>
-      <c r="L16" s="185">
+      <c r="L16" s="187">
         <v>-14.05</v>
       </c>
-      <c r="M16" s="191">
+      <c r="M16" s="188">
         <v>-12.8</v>
       </c>
-      <c r="N16" s="192">
+      <c r="N16" s="194">
         <v>-18.7</v>
       </c>
-      <c r="O16" s="193">
+      <c r="O16" s="195">
         <v>-26.81</v>
       </c>
-      <c r="P16" s="186">
+      <c r="P16" s="189">
         <v>-26.39</v>
       </c>
-      <c r="Q16" s="187">
+      <c r="Q16" s="191">
         <v>-31.3</v>
       </c>
-      <c r="R16" s="183">
+      <c r="R16" s="190">
         <v>-29.12</v>
       </c>
-      <c r="S16" s="194">
+      <c r="S16" s="192">
         <v>-29.2</v>
       </c>
-      <c r="T16" s="189">
-        <v>-47.66</v>
+      <c r="T16" s="184">
+        <v>-47.03</v>
       </c>
     </row>
     <row r="17">
@@ -5660,7 +5660,7 @@
       <c r="C17" t="str">
         <v>688577</v>
       </c>
-      <c r="D17" s="199" t="str">
+      <c r="D17" s="200" t="str">
         <v>净卖: -1039.47万</v>
       </c>
       <c r="E17">
@@ -5675,41 +5675,41 @@
       <c r="H17">
         <v>-0.04</v>
       </c>
-      <c r="I17" s="200">
+      <c r="I17" s="202">
         <v>-19.96</v>
       </c>
-      <c r="J17" s="204">
+      <c r="J17" s="205">
         <v>-18.66</v>
       </c>
-      <c r="K17" s="196">
+      <c r="K17" s="206">
         <v>-15.24</v>
       </c>
-      <c r="L17" s="201">
+      <c r="L17" s="203">
         <v>-16.26</v>
       </c>
-      <c r="M17" s="205">
+      <c r="M17" s="207">
         <v>-17.76</v>
       </c>
-      <c r="N17" s="197">
+      <c r="N17" s="208">
         <v>-16.4</v>
       </c>
-      <c r="O17" s="206">
+      <c r="O17" s="204">
         <v>-18.64</v>
       </c>
-      <c r="P17" s="207">
+      <c r="P17" s="196">
         <v>-19.41</v>
       </c>
-      <c r="Q17" s="202">
+      <c r="Q17" s="199">
         <v>-10.36</v>
       </c>
-      <c r="R17" s="208">
+      <c r="R17" s="197">
         <v>-13.75</v>
       </c>
-      <c r="S17" s="203">
+      <c r="S17" s="201">
         <v>-14.11</v>
       </c>
       <c r="T17" s="198">
-        <v>-38.74</v>
+        <v>-38.41</v>
       </c>
     </row>
     <row r="18">
@@ -5722,7 +5722,7 @@
       <c r="C18" t="str">
         <v>603757</v>
       </c>
-      <c r="D18" s="218" t="str">
+      <c r="D18" s="220" t="str">
         <v>净卖: -7133.87万</v>
       </c>
       <c r="E18">
@@ -5737,41 +5737,41 @@
       <c r="H18">
         <v>-1.84</v>
       </c>
-      <c r="I18" s="213">
+      <c r="I18" s="216">
         <v>12.06</v>
       </c>
-      <c r="J18" s="214">
+      <c r="J18" s="221">
         <v>13.86</v>
       </c>
-      <c r="K18" s="219">
+      <c r="K18" s="217">
         <v>17.77</v>
       </c>
-      <c r="L18" s="220">
+      <c r="L18" s="218">
         <v>14.57</v>
       </c>
-      <c r="M18" s="210">
+      <c r="M18" s="212">
         <v>16.9</v>
       </c>
-      <c r="N18" s="211">
+      <c r="N18" s="209">
         <v>11.61</v>
       </c>
-      <c r="O18" s="217">
+      <c r="O18" s="210">
         <v>9.48</v>
       </c>
-      <c r="P18" s="221">
+      <c r="P18" s="213">
         <v>12.23</v>
       </c>
-      <c r="Q18" s="209">
+      <c r="Q18" s="214">
         <v>5.19</v>
       </c>
-      <c r="R18" s="215">
+      <c r="R18" s="219">
         <v>8.18</v>
       </c>
-      <c r="S18" s="216">
+      <c r="S18" s="215">
         <v>6.47</v>
       </c>
-      <c r="T18" s="212">
-        <v>32.37</v>
+      <c r="T18" s="211">
+        <v>38.86</v>
       </c>
     </row>
     <row r="19">
@@ -5784,7 +5784,7 @@
       <c r="C19" t="str">
         <v>002117</v>
       </c>
-      <c r="D19" s="228" t="str">
+      <c r="D19" s="229" t="str">
         <v>净卖: -1144.93万</v>
       </c>
       <c r="E19">
@@ -5799,41 +5799,41 @@
       <c r="H19">
         <v>0.29</v>
       </c>
-      <c r="I19" s="229">
+      <c r="I19" s="222">
         <v>-10.25</v>
       </c>
-      <c r="J19" s="232">
+      <c r="J19" s="226">
         <v>-10.69</v>
       </c>
-      <c r="K19" s="234">
+      <c r="K19" s="223">
         <v>-13.72</v>
       </c>
-      <c r="L19" s="225">
+      <c r="L19" s="230">
         <v>-12.78</v>
       </c>
-      <c r="M19" s="230">
+      <c r="M19" s="232">
         <v>-12.64</v>
       </c>
       <c r="N19" s="233">
         <v>-8.52</v>
       </c>
-      <c r="O19" s="226">
+      <c r="O19" s="224">
         <v>-12.27</v>
       </c>
-      <c r="P19" s="222">
+      <c r="P19" s="234">
         <v>-11.26</v>
       </c>
-      <c r="Q19" s="231">
+      <c r="Q19" s="225">
         <v>-12.13</v>
       </c>
-      <c r="R19" s="223">
+      <c r="R19" s="231">
         <v>-12.78</v>
       </c>
       <c r="S19" s="227">
         <v>-12.56</v>
       </c>
-      <c r="T19" s="224">
-        <v>-27</v>
+      <c r="T19" s="228">
+        <v>-26.43</v>
       </c>
     </row>
     <row r="20">
@@ -5846,7 +5846,7 @@
       <c r="C20" t="str">
         <v>600246</v>
       </c>
-      <c r="D20" s="247" t="str">
+      <c r="D20" s="235" t="str">
         <v>净买: 1107.56万</v>
       </c>
       <c r="E20">
@@ -5861,41 +5861,41 @@
       <c r="H20">
         <v>1.07</v>
       </c>
-      <c r="I20" s="243">
+      <c r="I20" s="236">
         <v>-10.98</v>
       </c>
-      <c r="J20" s="237">
+      <c r="J20" s="243">
         <v>-11.79</v>
       </c>
-      <c r="K20" s="238">
+      <c r="K20" s="242">
         <v>-11.87</v>
       </c>
-      <c r="L20" s="239">
+      <c r="L20" s="244">
         <v>-11.54</v>
       </c>
-      <c r="M20" s="240">
+      <c r="M20" s="237">
         <v>-10.08</v>
       </c>
-      <c r="N20" s="241">
+      <c r="N20" s="245">
         <v>-10.08</v>
       </c>
-      <c r="O20" s="235">
+      <c r="O20" s="241">
         <v>-11.71</v>
       </c>
-      <c r="P20" s="242">
+      <c r="P20" s="246">
         <v>-12.52</v>
       </c>
-      <c r="Q20" s="236">
+      <c r="Q20" s="247">
         <v>-11.95</v>
       </c>
-      <c r="R20" s="244">
+      <c r="R20" s="238">
         <v>-12.44</v>
       </c>
-      <c r="S20" s="245">
+      <c r="S20" s="239">
         <v>-14.15</v>
       </c>
-      <c r="T20" s="246">
-        <v>-21.22</v>
+      <c r="T20" s="240">
+        <v>-20.49</v>
       </c>
     </row>
     <row r="21">
@@ -5960,37 +5960,37 @@
       <c r="I22" s="251">
         <v>57.89</v>
       </c>
-      <c r="J22" s="258">
+      <c r="J22" s="259">
         <v>73.68</v>
       </c>
-      <c r="K22" s="252">
+      <c r="K22" s="248">
         <v>73.68</v>
       </c>
-      <c r="L22" s="254">
+      <c r="L22" s="252">
         <v>68.42</v>
       </c>
-      <c r="M22" s="255">
+      <c r="M22" s="249">
         <v>68.42</v>
       </c>
       <c r="N22" s="253">
         <v>57.89</v>
       </c>
-      <c r="O22" s="259">
+      <c r="O22" s="256">
         <v>68.42</v>
       </c>
-      <c r="P22" s="248">
+      <c r="P22" s="254">
         <v>63.16</v>
       </c>
-      <c r="Q22" s="256">
+      <c r="Q22" s="250">
         <v>63.16</v>
       </c>
-      <c r="R22" s="257">
+      <c r="R22" s="255">
         <v>63.16</v>
       </c>
-      <c r="S22" s="249">
+      <c r="S22" s="257">
         <v>63.16</v>
       </c>
-      <c r="T22" s="250">
+      <c r="T22" s="258">
         <v>52.63</v>
       </c>
     </row>
@@ -6005,41 +6005,41 @@
       <c r="F23" t="str"/>
       <c r="G23" t="str"/>
       <c r="H23" t="str"/>
-      <c r="I23" s="266">
+      <c r="I23" s="270">
         <v>0.61</v>
       </c>
-      <c r="J23" s="270">
+      <c r="J23" s="261">
         <v>4.05</v>
       </c>
-      <c r="K23" s="262">
+      <c r="K23" s="266">
         <v>6.6</v>
       </c>
-      <c r="L23" s="271">
+      <c r="L23" s="267">
         <v>6.65</v>
       </c>
-      <c r="M23" s="260">
+      <c r="M23" s="268">
         <v>7.77</v>
       </c>
-      <c r="N23" s="263">
+      <c r="N23" s="269">
         <v>9.94</v>
       </c>
-      <c r="O23" s="267">
+      <c r="O23" s="271">
         <v>11.31</v>
       </c>
-      <c r="P23" s="264">
+      <c r="P23" s="262">
         <v>13.62</v>
       </c>
-      <c r="Q23" s="268">
+      <c r="Q23" s="263">
         <v>14.92</v>
       </c>
-      <c r="R23" s="265">
+      <c r="R23" s="264">
         <v>16.06</v>
       </c>
-      <c r="S23" s="261">
+      <c r="S23" s="260">
         <v>15.55</v>
       </c>
-      <c r="T23" s="269">
-        <v>10.05</v>
+      <c r="T23" s="265">
+        <v>11.32</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/牛散唐汉若/index.xlsx
+++ b/youzi/牛散唐汉若/index.xlsx
@@ -39,49 +39,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE0505E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF7AC88C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,7 +117,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,13 +213,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
+        <fgColor rgb="FFD7EEDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D5D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,7 +363,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF66C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,37 +501,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA4D9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56974"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,13 +585,469 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,37 +1059,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF56BA6D"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -273,91 +1143,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D5D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -369,85 +1227,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -471,37 +1341,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -513,121 +1497,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56974"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -639,31 +1533,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
+        <fgColor rgb="FFAF202E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -675,847 +1545,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1545,108 +1581,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCB2D3C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -1654,6 +1594,66 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4C1C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -4730,7 +4730,7 @@
       <c r="C2" t="str">
         <v>603300</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="4" t="str">
         <v>净买: 7263.08万</v>
       </c>
       <c r="E2">
@@ -4745,28 +4745,28 @@
       <c r="H2">
         <v>5.49</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="9">
         <v>4.31</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="1">
         <v>-6.1</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="5">
         <v>-0.65</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="6">
         <v>1.06</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="10">
         <v>-3.09</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="13">
         <v>-1.14</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="2">
         <v>-3.25</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="11">
         <v>-6.02</v>
       </c>
       <c r="Q2" s="7">
@@ -4775,11 +4775,11 @@
       <c r="R2" s="8">
         <v>-6.59</v>
       </c>
-      <c r="S2" s="11">
+      <c r="S2" s="3">
         <v>-13.01</v>
       </c>
-      <c r="T2" s="1">
-        <v>-42.36</v>
+      <c r="T2" s="12">
+        <v>-42.6</v>
       </c>
     </row>
     <row r="3">
@@ -4792,7 +4792,7 @@
       <c r="C3" t="str">
         <v>002093</v>
       </c>
-      <c r="D3" s="20" t="str">
+      <c r="D3" s="25" t="str">
         <v>净卖: -871.26万</v>
       </c>
       <c r="E3">
@@ -4807,41 +4807,41 @@
       <c r="H3">
         <v>10.06</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="17">
         <v>0</v>
       </c>
-      <c r="J3" s="21">
+      <c r="J3" s="18">
         <v>10.04</v>
       </c>
-      <c r="K3" s="22">
+      <c r="K3" s="26">
         <v>14.06</v>
       </c>
-      <c r="L3" s="18">
+      <c r="L3" s="19">
         <v>21.08</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="22">
         <v>33.23</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="20">
         <v>46.59</v>
       </c>
-      <c r="O3" s="15">
+      <c r="O3" s="14">
         <v>41.16</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="15">
         <v>31.83</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="23">
         <v>44.98</v>
       </c>
-      <c r="R3" s="23">
+      <c r="R3" s="24">
         <v>59.44</v>
       </c>
-      <c r="S3" s="26">
+      <c r="S3" s="21">
         <v>43.47</v>
       </c>
-      <c r="T3" s="24">
-        <v>-2.11</v>
+      <c r="T3" s="16">
+        <v>-3.71</v>
       </c>
     </row>
     <row r="4">
@@ -4854,7 +4854,7 @@
       <c r="C4" t="str">
         <v>603300</v>
       </c>
-      <c r="D4" s="28" t="str">
+      <c r="D4" s="34" t="str">
         <v>净买: 227.62万</v>
       </c>
       <c r="E4">
@@ -4869,41 +4869,41 @@
       <c r="H4">
         <v>-6.24</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="38">
         <v>-3.99</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="39">
         <v>1.58</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="37">
         <v>3.33</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="35">
         <v>-0.91</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="31">
         <v>1.08</v>
       </c>
-      <c r="N4" s="31">
+      <c r="N4" s="36">
         <v>-1.08</v>
       </c>
-      <c r="O4" s="37">
+      <c r="O4" s="32">
         <v>-3.91</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="27">
         <v>-1.41</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="28">
         <v>-4.49</v>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="29">
         <v>-11.06</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="30">
         <v>-8.56</v>
       </c>
-      <c r="T4" s="39">
-        <v>-41.06</v>
+      <c r="T4" s="33">
+        <v>-41.31</v>
       </c>
     </row>
     <row r="5">
@@ -4931,28 +4931,28 @@
       <c r="H5">
         <v>2.16</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="44">
         <v>3.56</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="45">
         <v>5.34</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="51">
         <v>1.02</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="48">
         <v>3.05</v>
       </c>
-      <c r="M5" s="47">
+      <c r="M5" s="42">
         <v>0.85</v>
       </c>
-      <c r="N5" s="51">
+      <c r="N5" s="43">
         <v>-2.03</v>
       </c>
-      <c r="O5" s="48">
+      <c r="O5" s="52">
         <v>0.51</v>
       </c>
-      <c r="P5" s="52">
+      <c r="P5" s="46">
         <v>-2.63</v>
       </c>
       <c r="Q5" s="49">
@@ -4961,11 +4961,11 @@
       <c r="R5" s="40">
         <v>-6.78</v>
       </c>
-      <c r="S5" s="45">
+      <c r="S5" s="47">
         <v>-13.73</v>
       </c>
       <c r="T5" s="50">
-        <v>-39.92</v>
+        <v>-40.17</v>
       </c>
     </row>
     <row r="6">
@@ -4978,7 +4978,7 @@
       <c r="C6" t="str">
         <v>603985</v>
       </c>
-      <c r="D6" s="55" t="str">
+      <c r="D6" s="53" t="str">
         <v>净卖: -484.50万</v>
       </c>
       <c r="E6">
@@ -4993,19 +4993,19 @@
       <c r="H6">
         <v>10.01</v>
       </c>
-      <c r="I6" s="59">
+      <c r="I6" s="54">
         <v>0</v>
       </c>
-      <c r="J6" s="56">
+      <c r="J6" s="59">
         <v>10.01</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="60">
         <v>7.17</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="55">
         <v>-3.55</v>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="56">
         <v>-10.59</v>
       </c>
       <c r="N6" s="57">
@@ -5014,20 +5014,20 @@
       <c r="O6" s="63">
         <v>2.32</v>
       </c>
-      <c r="P6" s="54">
+      <c r="P6" s="58">
         <v>3.87</v>
       </c>
       <c r="Q6" s="64">
         <v>6.33</v>
       </c>
-      <c r="R6" s="58">
+      <c r="R6" s="62">
         <v>4.33</v>
       </c>
-      <c r="S6" s="65">
+      <c r="S6" s="61">
         <v>5.68</v>
       </c>
-      <c r="T6" s="60">
-        <v>55.46</v>
+      <c r="T6" s="65">
+        <v>55.65</v>
       </c>
     </row>
     <row r="7">
@@ -5040,7 +5040,7 @@
       <c r="C7" t="str">
         <v>600744</v>
       </c>
-      <c r="D7" s="71" t="str">
+      <c r="D7" s="76" t="str">
         <v>净卖: -165.95万</v>
       </c>
       <c r="E7">
@@ -5055,28 +5055,28 @@
       <c r="H7">
         <v>10.13</v>
       </c>
-      <c r="I7" s="78">
+      <c r="I7" s="71">
         <v>0</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="77">
         <v>9.91</v>
       </c>
       <c r="K7" s="69">
         <v>15.8</v>
       </c>
-      <c r="L7" s="73">
+      <c r="L7" s="78">
         <v>4.25</v>
       </c>
-      <c r="M7" s="76">
+      <c r="M7" s="70">
         <v>14.62</v>
       </c>
-      <c r="N7" s="66">
+      <c r="N7" s="74">
         <v>19.34</v>
       </c>
-      <c r="O7" s="77">
+      <c r="O7" s="66">
         <v>27.36</v>
       </c>
-      <c r="P7" s="74">
+      <c r="P7" s="72">
         <v>27.36</v>
       </c>
       <c r="Q7" s="75">
@@ -5085,11 +5085,11 @@
       <c r="R7" s="67">
         <v>24.53</v>
       </c>
-      <c r="S7" s="70">
+      <c r="S7" s="68">
         <v>22.88</v>
       </c>
-      <c r="T7" s="68">
-        <v>90.57</v>
+      <c r="T7" s="73">
+        <v>94.81</v>
       </c>
     </row>
     <row r="8">
@@ -5102,7 +5102,7 @@
       <c r="C8" t="str">
         <v>603042</v>
       </c>
-      <c r="D8" s="79" t="str">
+      <c r="D8" s="91" t="str">
         <v>净买: 1056.82万</v>
       </c>
       <c r="E8">
@@ -5117,41 +5117,41 @@
       <c r="H8">
         <v>-0.69</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="79">
         <v>6.28</v>
       </c>
-      <c r="J8" s="88">
+      <c r="J8" s="83">
         <v>7.66</v>
       </c>
-      <c r="K8" s="89">
+      <c r="K8" s="84">
         <v>9.48</v>
       </c>
       <c r="L8" s="80">
         <v>12.44</v>
       </c>
-      <c r="M8" s="90">
+      <c r="M8" s="87">
         <v>11.93</v>
       </c>
-      <c r="N8" s="83">
+      <c r="N8" s="85">
         <v>9.99</v>
       </c>
-      <c r="O8" s="84">
+      <c r="O8" s="88">
         <v>8.73</v>
       </c>
-      <c r="P8" s="81">
+      <c r="P8" s="86">
         <v>12.5</v>
       </c>
-      <c r="Q8" s="85">
+      <c r="Q8" s="81">
         <v>9.86</v>
       </c>
-      <c r="R8" s="82">
+      <c r="R8" s="89">
         <v>3.71</v>
       </c>
-      <c r="S8" s="91">
+      <c r="S8" s="82">
         <v>5.21</v>
       </c>
-      <c r="T8" s="87">
-        <v>38.57</v>
+      <c r="T8" s="90">
+        <v>31.72</v>
       </c>
     </row>
     <row r="9">
@@ -5164,7 +5164,7 @@
       <c r="C9" t="str">
         <v>603300</v>
       </c>
-      <c r="D9" s="98" t="str">
+      <c r="D9" s="104" t="str">
         <v>净卖: -5853.95万</v>
       </c>
       <c r="E9">
@@ -5179,41 +5179,41 @@
       <c r="H9">
         <v>-0.29</v>
       </c>
-      <c r="I9" s="93">
+      <c r="I9" s="97">
         <v>7.44</v>
       </c>
       <c r="J9" s="99">
         <v>8.23</v>
       </c>
-      <c r="K9" s="100">
+      <c r="K9" s="102">
         <v>9.21</v>
       </c>
-      <c r="L9" s="101">
+      <c r="L9" s="92">
         <v>4.8</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="93">
         <v>2.06</v>
       </c>
-      <c r="N9" s="102">
+      <c r="N9" s="94">
         <v>1.37</v>
       </c>
-      <c r="O9" s="96">
+      <c r="O9" s="100">
         <v>0.78</v>
       </c>
-      <c r="P9" s="95">
+      <c r="P9" s="103">
         <v>4.41</v>
       </c>
-      <c r="Q9" s="103">
+      <c r="Q9" s="95">
         <v>7.05</v>
       </c>
-      <c r="R9" s="97">
+      <c r="R9" s="101">
         <v>4.21</v>
       </c>
-      <c r="S9" s="104">
+      <c r="S9" s="96">
         <v>2.45</v>
       </c>
-      <c r="T9" s="92">
-        <v>-30.56</v>
+      <c r="T9" s="98">
+        <v>-30.85</v>
       </c>
     </row>
     <row r="10">
@@ -5226,7 +5226,7 @@
       <c r="C10" t="str">
         <v>002028</v>
       </c>
-      <c r="D10" s="110" t="str">
+      <c r="D10" s="114" t="str">
         <v>净卖: -3647.56万</v>
       </c>
       <c r="E10">
@@ -5241,41 +5241,41 @@
       <c r="H10">
         <v>7.27</v>
       </c>
-      <c r="I10" s="108">
+      <c r="I10" s="109">
         <v>2.54</v>
       </c>
-      <c r="J10" s="111">
+      <c r="J10" s="113">
         <v>9.99</v>
       </c>
-      <c r="K10" s="113">
+      <c r="K10" s="110">
         <v>6.69</v>
       </c>
-      <c r="L10" s="116">
+      <c r="L10" s="115">
         <v>5.58</v>
       </c>
-      <c r="M10" s="109">
+      <c r="M10" s="111">
         <v>1.57</v>
       </c>
-      <c r="N10" s="117">
+      <c r="N10" s="106">
         <v>3.49</v>
       </c>
-      <c r="O10" s="114">
+      <c r="O10" s="107">
         <v>5.22</v>
       </c>
-      <c r="P10" s="105">
+      <c r="P10" s="116">
         <v>4.9</v>
       </c>
-      <c r="Q10" s="115">
+      <c r="Q10" s="117">
         <v>3.53</v>
       </c>
-      <c r="R10" s="106">
+      <c r="R10" s="112">
         <v>6.54</v>
       </c>
-      <c r="S10" s="107">
+      <c r="S10" s="105">
         <v>8.07</v>
       </c>
-      <c r="T10" s="112">
-        <v>190.12</v>
+      <c r="T10" s="108">
+        <v>188.01</v>
       </c>
     </row>
     <row r="11">
@@ -5288,7 +5288,7 @@
       <c r="C11" t="str">
         <v>603257</v>
       </c>
-      <c r="D11" s="124" t="str">
+      <c r="D11" s="118" t="str">
         <v>净卖: -308.53万</v>
       </c>
       <c r="E11">
@@ -5303,41 +5303,41 @@
       <c r="H11">
         <v>0.04</v>
       </c>
-      <c r="I11" s="118">
+      <c r="I11" s="121">
         <v>3.45</v>
       </c>
-      <c r="J11" s="119">
+      <c r="J11" s="122">
         <v>3.45</v>
       </c>
       <c r="K11" s="125">
         <v>4.99</v>
       </c>
-      <c r="L11" s="127">
+      <c r="L11" s="119">
         <v>3.55</v>
       </c>
-      <c r="M11" s="120">
+      <c r="M11" s="126">
         <v>9.31</v>
       </c>
-      <c r="N11" s="121">
+      <c r="N11" s="127">
         <v>6.44</v>
       </c>
-      <c r="O11" s="122">
+      <c r="O11" s="123">
         <v>5.49</v>
       </c>
-      <c r="P11" s="123">
+      <c r="P11" s="120">
         <v>4.71</v>
       </c>
-      <c r="Q11" s="128">
+      <c r="Q11" s="130">
         <v>3.2</v>
       </c>
-      <c r="R11" s="129">
+      <c r="R11" s="124">
         <v>3.82</v>
       </c>
-      <c r="S11" s="126">
+      <c r="S11" s="128">
         <v>3.18</v>
       </c>
-      <c r="T11" s="130">
-        <v>17.25</v>
+      <c r="T11" s="129">
+        <v>17.48</v>
       </c>
     </row>
     <row r="12">
@@ -5350,7 +5350,7 @@
       <c r="C12" t="str">
         <v>603280</v>
       </c>
-      <c r="D12" s="142" t="str">
+      <c r="D12" s="143" t="str">
         <v>净卖: -740.40万</v>
       </c>
       <c r="E12">
@@ -5365,41 +5365,41 @@
       <c r="H12">
         <v>3.37</v>
       </c>
-      <c r="I12" s="143">
+      <c r="I12" s="139">
         <v>6.41</v>
       </c>
-      <c r="J12" s="135">
+      <c r="J12" s="136">
         <v>17.04</v>
       </c>
       <c r="K12" s="131">
         <v>28.75</v>
       </c>
-      <c r="L12" s="136">
+      <c r="L12" s="137">
         <v>41.65</v>
       </c>
-      <c r="M12" s="132">
+      <c r="M12" s="140">
         <v>38.83</v>
       </c>
-      <c r="N12" s="137">
+      <c r="N12" s="141">
         <v>52.72</v>
       </c>
-      <c r="O12" s="133">
+      <c r="O12" s="132">
         <v>67.99</v>
       </c>
-      <c r="P12" s="138">
+      <c r="P12" s="133">
         <v>84.77</v>
       </c>
-      <c r="Q12" s="134">
+      <c r="Q12" s="135">
         <v>103.26</v>
       </c>
-      <c r="R12" s="139">
+      <c r="R12" s="138">
         <v>112.93</v>
       </c>
-      <c r="S12" s="140">
+      <c r="S12" s="134">
         <v>122.68</v>
       </c>
-      <c r="T12" s="141">
-        <v>29.57</v>
+      <c r="T12" s="142">
+        <v>29.42</v>
       </c>
     </row>
     <row r="13">
@@ -5412,7 +5412,7 @@
       <c r="C13" t="str">
         <v>603280</v>
       </c>
-      <c r="D13" s="147" t="str">
+      <c r="D13" s="145" t="str">
         <v>净卖: -1064.89万</v>
       </c>
       <c r="E13">
@@ -5427,41 +5427,41 @@
       <c r="H13">
         <v>4.74</v>
       </c>
-      <c r="I13" s="144">
+      <c r="I13" s="152">
         <v>5.02</v>
       </c>
-      <c r="J13" s="145">
+      <c r="J13" s="146">
         <v>15.53</v>
       </c>
-      <c r="K13" s="148">
+      <c r="K13" s="147">
         <v>27.09</v>
       </c>
-      <c r="L13" s="153">
+      <c r="L13" s="148">
         <v>24.57</v>
       </c>
       <c r="M13" s="149">
         <v>37.03</v>
       </c>
-      <c r="N13" s="151">
+      <c r="N13" s="155">
         <v>50.73</v>
       </c>
-      <c r="O13" s="154">
+      <c r="O13" s="153">
         <v>65.79</v>
       </c>
-      <c r="P13" s="152">
+      <c r="P13" s="150">
         <v>82.38</v>
       </c>
-      <c r="Q13" s="155">
+      <c r="Q13" s="156">
         <v>91.06</v>
       </c>
-      <c r="R13" s="146">
+      <c r="R13" s="151">
         <v>99.8</v>
       </c>
-      <c r="S13" s="150">
+      <c r="S13" s="154">
         <v>90.16</v>
       </c>
-      <c r="T13" s="156">
-        <v>16.26</v>
+      <c r="T13" s="144">
+        <v>16.12</v>
       </c>
     </row>
     <row r="14">
@@ -5474,7 +5474,7 @@
       <c r="C14" t="str">
         <v>600113</v>
       </c>
-      <c r="D14" s="169" t="str">
+      <c r="D14" s="162" t="str">
         <v>净卖: -1621.26万</v>
       </c>
       <c r="E14">
@@ -5489,41 +5489,41 @@
       <c r="H14">
         <v>2.49</v>
       </c>
-      <c r="I14" s="157">
+      <c r="I14" s="166">
         <v>7.32</v>
       </c>
-      <c r="J14" s="158">
+      <c r="J14" s="167">
         <v>18.05</v>
       </c>
-      <c r="K14" s="159">
+      <c r="K14" s="163">
         <v>25.05</v>
       </c>
-      <c r="L14" s="163">
+      <c r="L14" s="158">
         <v>37.57</v>
       </c>
-      <c r="M14" s="164">
+      <c r="M14" s="159">
         <v>35.41</v>
       </c>
-      <c r="N14" s="165">
+      <c r="N14" s="168">
         <v>38.35</v>
       </c>
-      <c r="O14" s="160">
+      <c r="O14" s="169">
         <v>38.24</v>
       </c>
-      <c r="P14" s="166">
+      <c r="P14" s="157">
         <v>39.05</v>
       </c>
-      <c r="Q14" s="167">
+      <c r="Q14" s="160">
         <v>33.92</v>
       </c>
-      <c r="R14" s="168">
+      <c r="R14" s="164">
         <v>47.32</v>
       </c>
-      <c r="S14" s="161">
+      <c r="S14" s="165">
         <v>62.05</v>
       </c>
-      <c r="T14" s="162">
-        <v>25.7</v>
+      <c r="T14" s="161">
+        <v>22.97</v>
       </c>
     </row>
     <row r="15">
@@ -5536,7 +5536,7 @@
       <c r="C15" t="str">
         <v>600113</v>
       </c>
-      <c r="D15" s="182" t="str">
+      <c r="D15" s="181" t="str">
         <v>净卖: -2870.19万</v>
       </c>
       <c r="E15">
@@ -5551,41 +5551,41 @@
       <c r="H15">
         <v>-0.58</v>
       </c>
-      <c r="I15" s="176">
+      <c r="I15" s="173">
         <v>10.65</v>
       </c>
-      <c r="J15" s="170">
+      <c r="J15" s="182">
         <v>8.91</v>
       </c>
-      <c r="K15" s="178">
+      <c r="K15" s="171">
         <v>11.28</v>
       </c>
-      <c r="L15" s="171">
+      <c r="L15" s="172">
         <v>11.2</v>
       </c>
-      <c r="M15" s="172">
+      <c r="M15" s="176">
         <v>11.85</v>
       </c>
-      <c r="N15" s="179">
+      <c r="N15" s="174">
         <v>7.72</v>
       </c>
-      <c r="O15" s="177">
+      <c r="O15" s="175">
         <v>18.5</v>
       </c>
-      <c r="P15" s="180">
+      <c r="P15" s="177">
         <v>30.35</v>
       </c>
-      <c r="Q15" s="173">
+      <c r="Q15" s="178">
         <v>33.04</v>
       </c>
-      <c r="R15" s="174">
+      <c r="R15" s="179">
         <v>22.78</v>
       </c>
-      <c r="S15" s="181">
+      <c r="S15" s="180">
         <v>28.54</v>
       </c>
-      <c r="T15" s="175">
-        <v>1.11</v>
+      <c r="T15" s="170">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="16">
@@ -5613,41 +5613,41 @@
       <c r="H16">
         <v>9.96</v>
       </c>
-      <c r="I16" s="183">
+      <c r="I16" s="186">
         <v>-12.33</v>
       </c>
-      <c r="J16" s="186">
+      <c r="J16" s="193">
         <v>-15.5</v>
       </c>
-      <c r="K16" s="193">
+      <c r="K16" s="187">
         <v>-14.75</v>
       </c>
-      <c r="L16" s="187">
+      <c r="L16" s="194">
         <v>-14.05</v>
       </c>
-      <c r="M16" s="188">
+      <c r="M16" s="195">
         <v>-12.8</v>
       </c>
-      <c r="N16" s="194">
+      <c r="N16" s="188">
         <v>-18.7</v>
       </c>
-      <c r="O16" s="195">
+      <c r="O16" s="191">
         <v>-26.81</v>
       </c>
-      <c r="P16" s="189">
+      <c r="P16" s="192">
         <v>-26.39</v>
       </c>
-      <c r="Q16" s="191">
+      <c r="Q16" s="183">
         <v>-31.3</v>
       </c>
-      <c r="R16" s="190">
+      <c r="R16" s="189">
         <v>-29.12</v>
       </c>
-      <c r="S16" s="192">
+      <c r="S16" s="190">
         <v>-29.2</v>
       </c>
       <c r="T16" s="184">
-        <v>-47.03</v>
+        <v>-48.28</v>
       </c>
     </row>
     <row r="17">
@@ -5660,7 +5660,7 @@
       <c r="C17" t="str">
         <v>688577</v>
       </c>
-      <c r="D17" s="200" t="str">
+      <c r="D17" s="198" t="str">
         <v>净卖: -1039.47万</v>
       </c>
       <c r="E17">
@@ -5675,41 +5675,41 @@
       <c r="H17">
         <v>-0.04</v>
       </c>
-      <c r="I17" s="202">
+      <c r="I17" s="199">
         <v>-19.96</v>
       </c>
-      <c r="J17" s="205">
+      <c r="J17" s="203">
         <v>-18.66</v>
       </c>
-      <c r="K17" s="206">
+      <c r="K17" s="207">
         <v>-15.24</v>
       </c>
-      <c r="L17" s="203">
+      <c r="L17" s="200">
         <v>-16.26</v>
       </c>
-      <c r="M17" s="207">
+      <c r="M17" s="201">
         <v>-17.76</v>
       </c>
       <c r="N17" s="208">
         <v>-16.4</v>
       </c>
-      <c r="O17" s="204">
+      <c r="O17" s="202">
         <v>-18.64</v>
       </c>
       <c r="P17" s="196">
         <v>-19.41</v>
       </c>
-      <c r="Q17" s="199">
+      <c r="Q17" s="204">
         <v>-10.36</v>
       </c>
-      <c r="R17" s="197">
+      <c r="R17" s="205">
         <v>-13.75</v>
       </c>
-      <c r="S17" s="201">
+      <c r="S17" s="206">
         <v>-14.11</v>
       </c>
-      <c r="T17" s="198">
-        <v>-38.41</v>
+      <c r="T17" s="197">
+        <v>-38.38</v>
       </c>
     </row>
     <row r="18">
@@ -5722,7 +5722,7 @@
       <c r="C18" t="str">
         <v>603757</v>
       </c>
-      <c r="D18" s="220" t="str">
+      <c r="D18" s="216" t="str">
         <v>净卖: -7133.87万</v>
       </c>
       <c r="E18">
@@ -5737,41 +5737,41 @@
       <c r="H18">
         <v>-1.84</v>
       </c>
-      <c r="I18" s="216">
+      <c r="I18" s="220">
         <v>12.06</v>
       </c>
       <c r="J18" s="221">
         <v>13.86</v>
       </c>
-      <c r="K18" s="217">
+      <c r="K18" s="209">
         <v>17.77</v>
       </c>
-      <c r="L18" s="218">
+      <c r="L18" s="217">
         <v>14.57</v>
       </c>
-      <c r="M18" s="212">
+      <c r="M18" s="218">
         <v>16.9</v>
       </c>
-      <c r="N18" s="209">
+      <c r="N18" s="210">
         <v>11.61</v>
       </c>
-      <c r="O18" s="210">
+      <c r="O18" s="212">
         <v>9.48</v>
       </c>
-      <c r="P18" s="213">
+      <c r="P18" s="211">
         <v>12.23</v>
       </c>
-      <c r="Q18" s="214">
+      <c r="Q18" s="213">
         <v>5.19</v>
       </c>
       <c r="R18" s="219">
         <v>8.18</v>
       </c>
-      <c r="S18" s="215">
+      <c r="S18" s="214">
         <v>6.47</v>
       </c>
-      <c r="T18" s="211">
-        <v>38.86</v>
+      <c r="T18" s="215">
+        <v>28.74</v>
       </c>
     </row>
     <row r="19">
@@ -5799,41 +5799,41 @@
       <c r="H19">
         <v>0.29</v>
       </c>
-      <c r="I19" s="222">
+      <c r="I19" s="223">
         <v>-10.25</v>
       </c>
-      <c r="J19" s="226">
+      <c r="J19" s="224">
         <v>-10.69</v>
       </c>
-      <c r="K19" s="223">
+      <c r="K19" s="230">
         <v>-13.72</v>
       </c>
-      <c r="L19" s="230">
+      <c r="L19" s="233">
         <v>-12.78</v>
       </c>
-      <c r="M19" s="232">
+      <c r="M19" s="225">
         <v>-12.64</v>
       </c>
-      <c r="N19" s="233">
+      <c r="N19" s="234">
         <v>-8.52</v>
       </c>
-      <c r="O19" s="224">
+      <c r="O19" s="226">
         <v>-12.27</v>
       </c>
-      <c r="P19" s="234">
+      <c r="P19" s="231">
         <v>-11.26</v>
       </c>
-      <c r="Q19" s="225">
+      <c r="Q19" s="222">
         <v>-12.13</v>
       </c>
-      <c r="R19" s="231">
+      <c r="R19" s="228">
         <v>-12.78</v>
       </c>
-      <c r="S19" s="227">
+      <c r="S19" s="232">
         <v>-12.56</v>
       </c>
-      <c r="T19" s="228">
-        <v>-26.43</v>
+      <c r="T19" s="227">
+        <v>-28.01</v>
       </c>
     </row>
     <row r="20">
@@ -5846,7 +5846,7 @@
       <c r="C20" t="str">
         <v>600246</v>
       </c>
-      <c r="D20" s="235" t="str">
+      <c r="D20" s="243" t="str">
         <v>净买: 1107.56万</v>
       </c>
       <c r="E20">
@@ -5861,41 +5861,41 @@
       <c r="H20">
         <v>1.07</v>
       </c>
-      <c r="I20" s="236">
+      <c r="I20" s="246">
         <v>-10.98</v>
       </c>
-      <c r="J20" s="243">
+      <c r="J20" s="239">
         <v>-11.79</v>
       </c>
-      <c r="K20" s="242">
+      <c r="K20" s="244">
         <v>-11.87</v>
       </c>
-      <c r="L20" s="244">
+      <c r="L20" s="247">
         <v>-11.54</v>
       </c>
-      <c r="M20" s="237">
+      <c r="M20" s="242">
         <v>-10.08</v>
       </c>
       <c r="N20" s="245">
         <v>-10.08</v>
       </c>
-      <c r="O20" s="241">
+      <c r="O20" s="235">
         <v>-11.71</v>
       </c>
-      <c r="P20" s="246">
+      <c r="P20" s="236">
         <v>-12.52</v>
       </c>
-      <c r="Q20" s="247">
+      <c r="Q20" s="237">
         <v>-11.95</v>
       </c>
-      <c r="R20" s="238">
+      <c r="R20" s="240">
         <v>-12.44</v>
       </c>
-      <c r="S20" s="239">
+      <c r="S20" s="241">
         <v>-14.15</v>
       </c>
-      <c r="T20" s="240">
-        <v>-20.49</v>
+      <c r="T20" s="238">
+        <v>-21.3</v>
       </c>
     </row>
     <row r="21">
@@ -5957,41 +5957,41 @@
       <c r="F22" t="str"/>
       <c r="G22" t="str"/>
       <c r="H22" t="str"/>
-      <c r="I22" s="251">
+      <c r="I22" s="248">
         <v>57.89</v>
       </c>
-      <c r="J22" s="259">
+      <c r="J22" s="254">
         <v>73.68</v>
       </c>
-      <c r="K22" s="248">
+      <c r="K22" s="259">
         <v>73.68</v>
       </c>
-      <c r="L22" s="252">
+      <c r="L22" s="255">
         <v>68.42</v>
       </c>
       <c r="M22" s="249">
         <v>68.42</v>
       </c>
-      <c r="N22" s="253">
+      <c r="N22" s="257">
         <v>57.89</v>
       </c>
-      <c r="O22" s="256">
+      <c r="O22" s="250">
         <v>68.42</v>
       </c>
-      <c r="P22" s="254">
+      <c r="P22" s="251">
         <v>63.16</v>
       </c>
-      <c r="Q22" s="250">
+      <c r="Q22" s="258">
         <v>63.16</v>
       </c>
-      <c r="R22" s="255">
+      <c r="R22" s="256">
         <v>63.16</v>
       </c>
-      <c r="S22" s="257">
+      <c r="S22" s="252">
         <v>63.16</v>
       </c>
-      <c r="T22" s="258">
-        <v>52.63</v>
+      <c r="T22" s="253">
+        <v>47.37</v>
       </c>
     </row>
     <row r="23">
@@ -6005,41 +6005,41 @@
       <c r="F23" t="str"/>
       <c r="G23" t="str"/>
       <c r="H23" t="str"/>
-      <c r="I23" s="270">
+      <c r="I23" s="260">
         <v>0.61</v>
       </c>
       <c r="J23" s="261">
         <v>4.05</v>
       </c>
-      <c r="K23" s="266">
+      <c r="K23" s="262">
         <v>6.6</v>
       </c>
-      <c r="L23" s="267">
+      <c r="L23" s="264">
         <v>6.65</v>
       </c>
-      <c r="M23" s="268">
+      <c r="M23" s="265">
         <v>7.77</v>
       </c>
-      <c r="N23" s="269">
+      <c r="N23" s="268">
         <v>9.94</v>
       </c>
-      <c r="O23" s="271">
+      <c r="O23" s="269">
         <v>11.31</v>
       </c>
-      <c r="P23" s="262">
+      <c r="P23" s="270">
         <v>13.62</v>
       </c>
       <c r="Q23" s="263">
         <v>14.92</v>
       </c>
-      <c r="R23" s="264">
+      <c r="R23" s="266">
         <v>16.06</v>
       </c>
-      <c r="S23" s="260">
+      <c r="S23" s="271">
         <v>15.55</v>
       </c>
-      <c r="T23" s="265">
-        <v>11.32</v>
+      <c r="T23" s="267">
+        <v>9.96</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/牛散唐汉若/index.xlsx
+++ b/youzi/牛散唐汉若/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="273">
+  <fills count="279">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,6 +39,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF249A3F"/>
         <bgColor/>
       </patternFill>
@@ -51,6 +99,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -63,43 +117,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,25 +207,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D5D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,37 +381,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFEEA1A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,19 +441,199 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56974"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -213,19 +645,487 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF56BA6D"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -237,301 +1137,523 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD7EEDD"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD0EBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D5D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
+        <fgColor rgb="FF3EB058"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -561,1092 +1683,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56974"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0EBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -1664,7 +1700,49 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="272">
+  <borders count="278">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -3573,7 +3651,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="272">
+  <cellXfs count="278">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -4386,6 +4464,24 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="271" fillId="272" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="272" fillId="273" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="273" fillId="274" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="274" fillId="275" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="275" fillId="276" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="276" fillId="277" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="277" fillId="278" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -4730,7 +4826,7 @@
       <c r="C2" t="str">
         <v>603300</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="13" t="str">
         <v>净买: 7263.08万</v>
       </c>
       <c r="E2">
@@ -4745,41 +4841,41 @@
       <c r="H2">
         <v>5.49</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="1">
         <v>4.31</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="9">
         <v>-6.1</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="2">
         <v>-0.65</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="7">
         <v>1.06</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="3">
         <v>-3.09</v>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="11">
         <v>-1.14</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2" s="10">
         <v>-3.25</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="4">
         <v>-6.02</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="5">
         <v>-3.58</v>
       </c>
       <c r="R2" s="8">
         <v>-6.59</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="12">
         <v>-13.01</v>
       </c>
-      <c r="T2" s="12">
-        <v>-42.6</v>
+      <c r="T2" s="6">
+        <v>-43.98</v>
       </c>
     </row>
     <row r="3">
@@ -4792,7 +4888,7 @@
       <c r="C3" t="str">
         <v>002093</v>
       </c>
-      <c r="D3" s="25" t="str">
+      <c r="D3" s="18" t="str">
         <v>净卖: -871.26万</v>
       </c>
       <c r="E3">
@@ -4807,41 +4903,41 @@
       <c r="H3">
         <v>10.06</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="19">
         <v>0</v>
       </c>
-      <c r="J3" s="18">
+      <c r="J3" s="22">
         <v>10.04</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="23">
         <v>14.06</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="20">
         <v>21.08</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="26">
         <v>33.23</v>
       </c>
-      <c r="N3" s="20">
+      <c r="N3" s="24">
         <v>46.59</v>
       </c>
       <c r="O3" s="14">
         <v>41.16</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="16">
         <v>31.83</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="15">
         <v>44.98</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="17">
         <v>59.44</v>
       </c>
       <c r="S3" s="21">
         <v>43.47</v>
       </c>
-      <c r="T3" s="16">
-        <v>-3.71</v>
+      <c r="T3" s="25">
+        <v>-6.83</v>
       </c>
     </row>
     <row r="4">
@@ -4854,7 +4950,7 @@
       <c r="C4" t="str">
         <v>603300</v>
       </c>
-      <c r="D4" s="34" t="str">
+      <c r="D4" s="32" t="str">
         <v>净买: 227.62万</v>
       </c>
       <c r="E4">
@@ -4869,41 +4965,41 @@
       <c r="H4">
         <v>-6.24</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="36">
         <v>-3.99</v>
       </c>
-      <c r="J4" s="39">
+      <c r="J4" s="29">
         <v>1.58</v>
       </c>
-      <c r="K4" s="37">
+      <c r="K4" s="39">
         <v>3.33</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="33">
         <v>-0.91</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="30">
         <v>1.08</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="37">
         <v>-1.08</v>
       </c>
-      <c r="O4" s="32">
+      <c r="O4" s="34">
         <v>-3.91</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="31">
         <v>-1.41</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="27">
         <v>-4.49</v>
       </c>
-      <c r="R4" s="29">
+      <c r="R4" s="38">
         <v>-11.06</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="35">
         <v>-8.56</v>
       </c>
-      <c r="T4" s="33">
-        <v>-41.31</v>
+      <c r="T4" s="28">
+        <v>-42.73</v>
       </c>
     </row>
     <row r="5">
@@ -4916,7 +5012,7 @@
       <c r="C5" t="str">
         <v>603300</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="48" t="str">
         <v>净卖: -6041.68万</v>
       </c>
       <c r="E5">
@@ -4931,41 +5027,41 @@
       <c r="H5">
         <v>2.16</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="45">
         <v>3.56</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="42">
         <v>5.34</v>
       </c>
-      <c r="K5" s="51">
+      <c r="K5" s="46">
         <v>1.02</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="49">
         <v>3.05</v>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="47">
         <v>0.85</v>
       </c>
-      <c r="N5" s="43">
+      <c r="N5" s="41">
         <v>-2.03</v>
       </c>
-      <c r="O5" s="52">
+      <c r="O5" s="50">
         <v>0.51</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="43">
         <v>-2.63</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="44">
         <v>-9.32</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="51">
         <v>-6.78</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="52">
         <v>-13.73</v>
       </c>
-      <c r="T5" s="50">
-        <v>-40.17</v>
+      <c r="T5" s="40">
+        <v>-41.61</v>
       </c>
     </row>
     <row r="6">
@@ -4978,7 +5074,7 @@
       <c r="C6" t="str">
         <v>603985</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="56" t="str">
         <v>净卖: -484.50万</v>
       </c>
       <c r="E6">
@@ -4993,41 +5089,41 @@
       <c r="H6">
         <v>10.01</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="57">
         <v>0</v>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="60">
         <v>10.01</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="53">
         <v>7.17</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="54">
         <v>-3.55</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="55">
         <v>-10.59</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="61">
         <v>-1.61</v>
       </c>
-      <c r="O6" s="63">
+      <c r="O6" s="58">
         <v>2.32</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="59">
         <v>3.87</v>
       </c>
       <c r="Q6" s="64">
         <v>6.33</v>
       </c>
-      <c r="R6" s="62">
+      <c r="R6" s="65">
         <v>4.33</v>
       </c>
-      <c r="S6" s="61">
+      <c r="S6" s="62">
         <v>5.68</v>
       </c>
-      <c r="T6" s="65">
-        <v>55.65</v>
+      <c r="T6" s="63">
+        <v>63.65</v>
       </c>
     </row>
     <row r="7">
@@ -5040,7 +5136,7 @@
       <c r="C7" t="str">
         <v>600744</v>
       </c>
-      <c r="D7" s="76" t="str">
+      <c r="D7" s="67" t="str">
         <v>净卖: -165.95万</v>
       </c>
       <c r="E7">
@@ -5055,41 +5151,41 @@
       <c r="H7">
         <v>10.13</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="72">
         <v>0</v>
       </c>
-      <c r="J7" s="77">
+      <c r="J7" s="73">
         <v>9.91</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="74">
         <v>15.8</v>
       </c>
-      <c r="L7" s="78">
+      <c r="L7" s="68">
         <v>4.25</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="75">
         <v>14.62</v>
       </c>
-      <c r="N7" s="74">
+      <c r="N7" s="66">
         <v>19.34</v>
       </c>
-      <c r="O7" s="66">
+      <c r="O7" s="76">
         <v>27.36</v>
       </c>
-      <c r="P7" s="72">
+      <c r="P7" s="77">
         <v>27.36</v>
       </c>
-      <c r="Q7" s="75">
+      <c r="Q7" s="69">
         <v>25.24</v>
       </c>
-      <c r="R7" s="67">
+      <c r="R7" s="70">
         <v>24.53</v>
       </c>
-      <c r="S7" s="68">
+      <c r="S7" s="71">
         <v>22.88</v>
       </c>
-      <c r="T7" s="73">
-        <v>94.81</v>
+      <c r="T7" s="78">
+        <v>88.92</v>
       </c>
     </row>
     <row r="8">
@@ -5102,7 +5198,7 @@
       <c r="C8" t="str">
         <v>603042</v>
       </c>
-      <c r="D8" s="91" t="str">
+      <c r="D8" s="84" t="str">
         <v>净买: 1056.82万</v>
       </c>
       <c r="E8">
@@ -5117,41 +5213,41 @@
       <c r="H8">
         <v>-0.69</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="87">
         <v>6.28</v>
       </c>
       <c r="J8" s="83">
         <v>7.66</v>
       </c>
-      <c r="K8" s="84">
+      <c r="K8" s="85">
         <v>9.48</v>
       </c>
-      <c r="L8" s="80">
+      <c r="L8" s="88">
         <v>12.44</v>
       </c>
-      <c r="M8" s="87">
+      <c r="M8" s="79">
         <v>11.93</v>
       </c>
-      <c r="N8" s="85">
+      <c r="N8" s="89">
         <v>9.99</v>
       </c>
-      <c r="O8" s="88">
+      <c r="O8" s="86">
         <v>8.73</v>
       </c>
-      <c r="P8" s="86">
+      <c r="P8" s="80">
         <v>12.5</v>
       </c>
       <c r="Q8" s="81">
         <v>9.86</v>
       </c>
-      <c r="R8" s="89">
+      <c r="R8" s="90">
         <v>3.71</v>
       </c>
-      <c r="S8" s="82">
+      <c r="S8" s="91">
         <v>5.21</v>
       </c>
-      <c r="T8" s="90">
-        <v>31.72</v>
+      <c r="T8" s="82">
+        <v>25.63</v>
       </c>
     </row>
     <row r="9">
@@ -5164,7 +5260,7 @@
       <c r="C9" t="str">
         <v>603300</v>
       </c>
-      <c r="D9" s="104" t="str">
+      <c r="D9" s="102" t="str">
         <v>净卖: -5853.95万</v>
       </c>
       <c r="E9">
@@ -5179,41 +5275,41 @@
       <c r="H9">
         <v>-0.29</v>
       </c>
-      <c r="I9" s="97">
+      <c r="I9" s="95">
         <v>7.44</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="100">
         <v>8.23</v>
       </c>
-      <c r="K9" s="102">
+      <c r="K9" s="96">
         <v>9.21</v>
       </c>
-      <c r="L9" s="92">
+      <c r="L9" s="98">
         <v>4.8</v>
       </c>
-      <c r="M9" s="93">
+      <c r="M9" s="103">
         <v>2.06</v>
       </c>
-      <c r="N9" s="94">
+      <c r="N9" s="104">
         <v>1.37</v>
       </c>
-      <c r="O9" s="100">
+      <c r="O9" s="92">
         <v>0.78</v>
       </c>
-      <c r="P9" s="103">
+      <c r="P9" s="97">
         <v>4.41</v>
       </c>
-      <c r="Q9" s="95">
+      <c r="Q9" s="93">
         <v>7.05</v>
       </c>
-      <c r="R9" s="101">
+      <c r="R9" s="94">
         <v>4.21</v>
       </c>
-      <c r="S9" s="96">
+      <c r="S9" s="99">
         <v>2.45</v>
       </c>
-      <c r="T9" s="98">
-        <v>-30.85</v>
+      <c r="T9" s="101">
+        <v>-32.52</v>
       </c>
     </row>
     <row r="10">
@@ -5241,41 +5337,41 @@
       <c r="H10">
         <v>7.27</v>
       </c>
-      <c r="I10" s="109">
+      <c r="I10" s="115">
         <v>2.54</v>
       </c>
-      <c r="J10" s="113">
+      <c r="J10" s="112">
         <v>9.99</v>
       </c>
-      <c r="K10" s="110">
+      <c r="K10" s="109">
         <v>6.69</v>
       </c>
-      <c r="L10" s="115">
+      <c r="L10" s="107">
         <v>5.58</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="116">
         <v>1.57</v>
       </c>
-      <c r="N10" s="106">
+      <c r="N10" s="110">
         <v>3.49</v>
       </c>
-      <c r="O10" s="107">
+      <c r="O10" s="117">
         <v>5.22</v>
       </c>
-      <c r="P10" s="116">
+      <c r="P10" s="113">
         <v>4.9</v>
       </c>
-      <c r="Q10" s="117">
+      <c r="Q10" s="111">
         <v>3.53</v>
       </c>
-      <c r="R10" s="112">
+      <c r="R10" s="105">
         <v>6.54</v>
       </c>
-      <c r="S10" s="105">
+      <c r="S10" s="106">
         <v>8.07</v>
       </c>
       <c r="T10" s="108">
-        <v>188.01</v>
+        <v>195.86</v>
       </c>
     </row>
     <row r="11">
@@ -5288,7 +5384,7 @@
       <c r="C11" t="str">
         <v>603257</v>
       </c>
-      <c r="D11" s="118" t="str">
+      <c r="D11" s="121" t="str">
         <v>净卖: -308.53万</v>
       </c>
       <c r="E11">
@@ -5303,41 +5399,41 @@
       <c r="H11">
         <v>0.04</v>
       </c>
-      <c r="I11" s="121">
+      <c r="I11" s="122">
         <v>3.45</v>
       </c>
-      <c r="J11" s="122">
+      <c r="J11" s="123">
         <v>3.45</v>
       </c>
-      <c r="K11" s="125">
+      <c r="K11" s="124">
         <v>4.99</v>
       </c>
-      <c r="L11" s="119">
+      <c r="L11" s="125">
         <v>3.55</v>
       </c>
-      <c r="M11" s="126">
+      <c r="M11" s="128">
         <v>9.31</v>
       </c>
-      <c r="N11" s="127">
+      <c r="N11" s="130">
         <v>6.44</v>
       </c>
-      <c r="O11" s="123">
+      <c r="O11" s="118">
         <v>5.49</v>
       </c>
-      <c r="P11" s="120">
+      <c r="P11" s="126">
         <v>4.71</v>
       </c>
-      <c r="Q11" s="130">
+      <c r="Q11" s="127">
         <v>3.2</v>
       </c>
-      <c r="R11" s="124">
+      <c r="R11" s="129">
         <v>3.82</v>
       </c>
-      <c r="S11" s="128">
+      <c r="S11" s="119">
         <v>3.18</v>
       </c>
-      <c r="T11" s="129">
-        <v>17.48</v>
+      <c r="T11" s="120">
+        <v>10.94</v>
       </c>
     </row>
     <row r="12">
@@ -5350,7 +5446,7 @@
       <c r="C12" t="str">
         <v>603280</v>
       </c>
-      <c r="D12" s="143" t="str">
+      <c r="D12" s="135" t="str">
         <v>净卖: -740.40万</v>
       </c>
       <c r="E12">
@@ -5365,41 +5461,41 @@
       <c r="H12">
         <v>3.37</v>
       </c>
-      <c r="I12" s="139">
+      <c r="I12" s="136">
         <v>6.41</v>
       </c>
-      <c r="J12" s="136">
+      <c r="J12" s="131">
         <v>17.04</v>
       </c>
-      <c r="K12" s="131">
+      <c r="K12" s="132">
         <v>28.75</v>
       </c>
-      <c r="L12" s="137">
+      <c r="L12" s="133">
         <v>41.65</v>
       </c>
-      <c r="M12" s="140">
+      <c r="M12" s="137">
         <v>38.83</v>
       </c>
-      <c r="N12" s="141">
+      <c r="N12" s="134">
         <v>52.72</v>
       </c>
-      <c r="O12" s="132">
+      <c r="O12" s="142">
         <v>67.99</v>
       </c>
-      <c r="P12" s="133">
+      <c r="P12" s="138">
         <v>84.77</v>
       </c>
-      <c r="Q12" s="135">
+      <c r="Q12" s="143">
         <v>103.26</v>
       </c>
-      <c r="R12" s="138">
+      <c r="R12" s="139">
         <v>112.93</v>
       </c>
-      <c r="S12" s="134">
+      <c r="S12" s="140">
         <v>122.68</v>
       </c>
-      <c r="T12" s="142">
-        <v>29.42</v>
+      <c r="T12" s="141">
+        <v>25.68</v>
       </c>
     </row>
     <row r="13">
@@ -5412,7 +5508,7 @@
       <c r="C13" t="str">
         <v>603280</v>
       </c>
-      <c r="D13" s="145" t="str">
+      <c r="D13" s="154" t="str">
         <v>净卖: -1064.89万</v>
       </c>
       <c r="E13">
@@ -5427,41 +5523,41 @@
       <c r="H13">
         <v>4.74</v>
       </c>
-      <c r="I13" s="152">
+      <c r="I13" s="149">
         <v>5.02</v>
       </c>
-      <c r="J13" s="146">
+      <c r="J13" s="150">
         <v>15.53</v>
       </c>
-      <c r="K13" s="147">
+      <c r="K13" s="151">
         <v>27.09</v>
       </c>
-      <c r="L13" s="148">
+      <c r="L13" s="146">
         <v>24.57</v>
       </c>
-      <c r="M13" s="149">
+      <c r="M13" s="155">
         <v>37.03</v>
       </c>
-      <c r="N13" s="155">
+      <c r="N13" s="156">
         <v>50.73</v>
       </c>
-      <c r="O13" s="153">
+      <c r="O13" s="147">
         <v>65.79</v>
       </c>
-      <c r="P13" s="150">
+      <c r="P13" s="153">
         <v>82.38</v>
       </c>
-      <c r="Q13" s="156">
+      <c r="Q13" s="152">
         <v>91.06</v>
       </c>
-      <c r="R13" s="151">
+      <c r="R13" s="144">
         <v>99.8</v>
       </c>
-      <c r="S13" s="154">
+      <c r="S13" s="145">
         <v>90.16</v>
       </c>
-      <c r="T13" s="144">
-        <v>16.12</v>
+      <c r="T13" s="148">
+        <v>12.77</v>
       </c>
     </row>
     <row r="14">
@@ -5474,7 +5570,7 @@
       <c r="C14" t="str">
         <v>600113</v>
       </c>
-      <c r="D14" s="162" t="str">
+      <c r="D14" s="167" t="str">
         <v>净卖: -1621.26万</v>
       </c>
       <c r="E14">
@@ -5489,41 +5585,41 @@
       <c r="H14">
         <v>2.49</v>
       </c>
-      <c r="I14" s="166">
+      <c r="I14" s="168">
         <v>7.32</v>
       </c>
-      <c r="J14" s="167">
+      <c r="J14" s="161">
         <v>18.05</v>
       </c>
-      <c r="K14" s="163">
+      <c r="K14" s="165">
         <v>25.05</v>
       </c>
-      <c r="L14" s="158">
+      <c r="L14" s="169">
         <v>37.57</v>
       </c>
-      <c r="M14" s="159">
+      <c r="M14" s="157">
         <v>35.41</v>
       </c>
-      <c r="N14" s="168">
+      <c r="N14" s="162">
         <v>38.35</v>
       </c>
-      <c r="O14" s="169">
+      <c r="O14" s="158">
         <v>38.24</v>
       </c>
-      <c r="P14" s="157">
+      <c r="P14" s="159">
         <v>39.05</v>
       </c>
-      <c r="Q14" s="160">
+      <c r="Q14" s="163">
         <v>33.92</v>
       </c>
       <c r="R14" s="164">
         <v>47.32</v>
       </c>
-      <c r="S14" s="165">
+      <c r="S14" s="160">
         <v>62.05</v>
       </c>
-      <c r="T14" s="161">
-        <v>22.97</v>
+      <c r="T14" s="166">
+        <v>22.43</v>
       </c>
     </row>
     <row r="15">
@@ -5536,7 +5632,7 @@
       <c r="C15" t="str">
         <v>600113</v>
       </c>
-      <c r="D15" s="181" t="str">
+      <c r="D15" s="180" t="str">
         <v>净卖: -2870.19万</v>
       </c>
       <c r="E15">
@@ -5551,41 +5647,41 @@
       <c r="H15">
         <v>-0.58</v>
       </c>
-      <c r="I15" s="173">
+      <c r="I15" s="172">
         <v>10.65</v>
       </c>
-      <c r="J15" s="182">
+      <c r="J15" s="181">
         <v>8.91</v>
       </c>
-      <c r="K15" s="171">
+      <c r="K15" s="173">
         <v>11.28</v>
       </c>
-      <c r="L15" s="172">
+      <c r="L15" s="179">
         <v>11.2</v>
       </c>
-      <c r="M15" s="176">
+      <c r="M15" s="182">
         <v>11.85</v>
       </c>
-      <c r="N15" s="174">
+      <c r="N15" s="170">
         <v>7.72</v>
       </c>
-      <c r="O15" s="175">
+      <c r="O15" s="174">
         <v>18.5</v>
       </c>
-      <c r="P15" s="177">
+      <c r="P15" s="175">
         <v>30.35</v>
       </c>
-      <c r="Q15" s="178">
+      <c r="Q15" s="176">
         <v>33.04</v>
       </c>
-      <c r="R15" s="179">
+      <c r="R15" s="177">
         <v>22.78</v>
       </c>
-      <c r="S15" s="180">
+      <c r="S15" s="171">
         <v>28.54</v>
       </c>
-      <c r="T15" s="170">
-        <v>-1.09</v>
+      <c r="T15" s="178">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="16">
@@ -5598,7 +5694,7 @@
       <c r="C16" t="str">
         <v>000014</v>
       </c>
-      <c r="D16" s="185" t="str">
+      <c r="D16" s="184" t="str">
         <v>净卖: -962.87万</v>
       </c>
       <c r="E16">
@@ -5613,25 +5709,25 @@
       <c r="H16">
         <v>9.96</v>
       </c>
-      <c r="I16" s="186">
+      <c r="I16" s="188">
         <v>-12.33</v>
       </c>
-      <c r="J16" s="193">
+      <c r="J16" s="191">
         <v>-15.5</v>
       </c>
-      <c r="K16" s="187">
+      <c r="K16" s="189">
         <v>-14.75</v>
       </c>
-      <c r="L16" s="194">
+      <c r="L16" s="190">
         <v>-14.05</v>
       </c>
       <c r="M16" s="195">
         <v>-12.8</v>
       </c>
-      <c r="N16" s="188">
+      <c r="N16" s="185">
         <v>-18.7</v>
       </c>
-      <c r="O16" s="191">
+      <c r="O16" s="186">
         <v>-26.81</v>
       </c>
       <c r="P16" s="192">
@@ -5640,14 +5736,14 @@
       <c r="Q16" s="183">
         <v>-31.3</v>
       </c>
-      <c r="R16" s="189">
+      <c r="R16" s="193">
         <v>-29.12</v>
       </c>
-      <c r="S16" s="190">
+      <c r="S16" s="187">
         <v>-29.2</v>
       </c>
-      <c r="T16" s="184">
-        <v>-48.28</v>
+      <c r="T16" s="194">
+        <v>-48.79</v>
       </c>
     </row>
     <row r="17">
@@ -5660,7 +5756,7 @@
       <c r="C17" t="str">
         <v>688577</v>
       </c>
-      <c r="D17" s="198" t="str">
+      <c r="D17" s="199" t="str">
         <v>净卖: -1039.47万</v>
       </c>
       <c r="E17">
@@ -5675,25 +5771,25 @@
       <c r="H17">
         <v>-0.04</v>
       </c>
-      <c r="I17" s="199">
+      <c r="I17" s="200">
         <v>-19.96</v>
       </c>
-      <c r="J17" s="203">
+      <c r="J17" s="206">
         <v>-18.66</v>
       </c>
       <c r="K17" s="207">
         <v>-15.24</v>
       </c>
-      <c r="L17" s="200">
+      <c r="L17" s="208">
         <v>-16.26</v>
       </c>
       <c r="M17" s="201">
         <v>-17.76</v>
       </c>
-      <c r="N17" s="208">
+      <c r="N17" s="202">
         <v>-16.4</v>
       </c>
-      <c r="O17" s="202">
+      <c r="O17" s="203">
         <v>-18.64</v>
       </c>
       <c r="P17" s="196">
@@ -5702,14 +5798,14 @@
       <c r="Q17" s="204">
         <v>-10.36</v>
       </c>
-      <c r="R17" s="205">
+      <c r="R17" s="197">
         <v>-13.75</v>
       </c>
-      <c r="S17" s="206">
+      <c r="S17" s="205">
         <v>-14.11</v>
       </c>
-      <c r="T17" s="197">
-        <v>-38.38</v>
+      <c r="T17" s="198">
+        <v>-38.9</v>
       </c>
     </row>
     <row r="18">
@@ -5722,7 +5818,7 @@
       <c r="C18" t="str">
         <v>603757</v>
       </c>
-      <c r="D18" s="216" t="str">
+      <c r="D18" s="217" t="str">
         <v>净卖: -7133.87万</v>
       </c>
       <c r="E18">
@@ -5737,41 +5833,41 @@
       <c r="H18">
         <v>-1.84</v>
       </c>
-      <c r="I18" s="220">
+      <c r="I18" s="218">
         <v>12.06</v>
       </c>
       <c r="J18" s="221">
         <v>13.86</v>
       </c>
-      <c r="K18" s="209">
+      <c r="K18" s="212">
         <v>17.77</v>
       </c>
-      <c r="L18" s="217">
+      <c r="L18" s="213">
         <v>14.57</v>
       </c>
-      <c r="M18" s="218">
+      <c r="M18" s="209">
         <v>16.9</v>
       </c>
-      <c r="N18" s="210">
+      <c r="N18" s="214">
         <v>11.61</v>
       </c>
-      <c r="O18" s="212">
+      <c r="O18" s="215">
         <v>9.48</v>
       </c>
-      <c r="P18" s="211">
+      <c r="P18" s="216">
         <v>12.23</v>
       </c>
-      <c r="Q18" s="213">
+      <c r="Q18" s="219">
         <v>5.19</v>
       </c>
-      <c r="R18" s="219">
+      <c r="R18" s="220">
         <v>8.18</v>
       </c>
-      <c r="S18" s="214">
+      <c r="S18" s="210">
         <v>6.47</v>
       </c>
-      <c r="T18" s="215">
-        <v>28.74</v>
+      <c r="T18" s="211">
+        <v>20.43</v>
       </c>
     </row>
     <row r="19">
@@ -5799,41 +5895,41 @@
       <c r="H19">
         <v>0.29</v>
       </c>
-      <c r="I19" s="223">
+      <c r="I19" s="233">
         <v>-10.25</v>
       </c>
-      <c r="J19" s="224">
+      <c r="J19" s="232">
         <v>-10.69</v>
       </c>
-      <c r="K19" s="230">
+      <c r="K19" s="234">
         <v>-13.72</v>
       </c>
-      <c r="L19" s="233">
+      <c r="L19" s="223">
         <v>-12.78</v>
       </c>
-      <c r="M19" s="225">
+      <c r="M19" s="224">
         <v>-12.64</v>
       </c>
-      <c r="N19" s="234">
+      <c r="N19" s="225">
         <v>-8.52</v>
       </c>
-      <c r="O19" s="226">
+      <c r="O19" s="222">
         <v>-12.27</v>
       </c>
-      <c r="P19" s="231">
+      <c r="P19" s="226">
         <v>-11.26</v>
       </c>
-      <c r="Q19" s="222">
+      <c r="Q19" s="230">
         <v>-12.13</v>
       </c>
-      <c r="R19" s="228">
+      <c r="R19" s="227">
         <v>-12.78</v>
       </c>
-      <c r="S19" s="232">
+      <c r="S19" s="231">
         <v>-12.56</v>
       </c>
-      <c r="T19" s="227">
-        <v>-28.01</v>
+      <c r="T19" s="228">
+        <v>-27.22</v>
       </c>
     </row>
     <row r="20">
@@ -5846,7 +5942,7 @@
       <c r="C20" t="str">
         <v>600246</v>
       </c>
-      <c r="D20" s="243" t="str">
+      <c r="D20" s="246" t="str">
         <v>净买: 1107.56万</v>
       </c>
       <c r="E20">
@@ -5861,94 +5957,94 @@
       <c r="H20">
         <v>1.07</v>
       </c>
-      <c r="I20" s="246">
+      <c r="I20" s="236">
         <v>-10.98</v>
       </c>
       <c r="J20" s="239">
         <v>-11.79</v>
       </c>
-      <c r="K20" s="244">
+      <c r="K20" s="237">
         <v>-11.87</v>
       </c>
-      <c r="L20" s="247">
+      <c r="L20" s="238">
         <v>-11.54</v>
       </c>
-      <c r="M20" s="242">
+      <c r="M20" s="243">
         <v>-10.08</v>
       </c>
-      <c r="N20" s="245">
+      <c r="N20" s="244">
         <v>-10.08</v>
       </c>
-      <c r="O20" s="235">
+      <c r="O20" s="240">
         <v>-11.71</v>
       </c>
-      <c r="P20" s="236">
+      <c r="P20" s="247">
         <v>-12.52</v>
       </c>
-      <c r="Q20" s="237">
+      <c r="Q20" s="245">
         <v>-11.95</v>
       </c>
-      <c r="R20" s="240">
+      <c r="R20" s="235">
         <v>-12.44</v>
       </c>
       <c r="S20" s="241">
         <v>-14.15</v>
       </c>
-      <c r="T20" s="238">
-        <v>-21.3</v>
+      <c r="T20" s="242">
+        <v>-21.14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>纪录总数</v>
-      </c>
-      <c r="B21" t="str"/>
-      <c r="C21" t="str"/>
-      <c r="D21" t="str"/>
-      <c r="E21" t="str"/>
-      <c r="F21" t="str"/>
-      <c r="G21" t="str"/>
-      <c r="H21" t="str"/>
-      <c r="I21">
-        <v>19</v>
-      </c>
-      <c r="J21">
-        <v>19</v>
-      </c>
-      <c r="K21">
-        <v>19</v>
-      </c>
-      <c r="L21">
-        <v>19</v>
-      </c>
-      <c r="M21">
-        <v>19</v>
-      </c>
-      <c r="N21">
-        <v>19</v>
-      </c>
-      <c r="O21">
-        <v>19</v>
-      </c>
-      <c r="P21">
-        <v>19</v>
-      </c>
-      <c r="Q21">
-        <v>19</v>
-      </c>
-      <c r="R21">
-        <v>19</v>
-      </c>
-      <c r="S21">
-        <v>19</v>
-      </c>
-      <c r="T21">
-        <v>19</v>
+        <v>2026-04-21</v>
+      </c>
+      <c r="B21" t="str">
+        <v>时空科技</v>
+      </c>
+      <c r="C21" t="str">
+        <v>605178</v>
+      </c>
+      <c r="D21" s="253" t="str">
+        <v>净买: 140.70万</v>
+      </c>
+      <c r="E21">
+        <v>70.35</v>
+      </c>
+      <c r="F21">
+        <v>70.35</v>
+      </c>
+      <c r="G21">
+        <v>70.35</v>
+      </c>
+      <c r="H21">
+        <v>-10</v>
+      </c>
+      <c r="I21" s="248">
+        <v>0</v>
+      </c>
+      <c r="J21" s="249">
+        <v>-0.91</v>
+      </c>
+      <c r="K21" s="250">
+        <v>-4.48</v>
+      </c>
+      <c r="L21" s="251">
+        <v>-7.6</v>
+      </c>
+      <c r="M21" t="str"/>
+      <c r="N21" t="str"/>
+      <c r="O21" t="str"/>
+      <c r="P21" t="str"/>
+      <c r="Q21" t="str"/>
+      <c r="R21" t="str"/>
+      <c r="S21" t="str"/>
+      <c r="T21" s="252">
+        <v>-7.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>上涨比例</v>
+        <v>纪录总数</v>
       </c>
       <c r="B22" t="str"/>
       <c r="C22" t="str"/>
@@ -5957,46 +6053,46 @@
       <c r="F22" t="str"/>
       <c r="G22" t="str"/>
       <c r="H22" t="str"/>
-      <c r="I22" s="248">
-        <v>57.89</v>
-      </c>
-      <c r="J22" s="254">
-        <v>73.68</v>
-      </c>
-      <c r="K22" s="259">
-        <v>73.68</v>
-      </c>
-      <c r="L22" s="255">
-        <v>68.42</v>
-      </c>
-      <c r="M22" s="249">
-        <v>68.42</v>
-      </c>
-      <c r="N22" s="257">
-        <v>57.89</v>
-      </c>
-      <c r="O22" s="250">
-        <v>68.42</v>
-      </c>
-      <c r="P22" s="251">
-        <v>63.16</v>
-      </c>
-      <c r="Q22" s="258">
-        <v>63.16</v>
-      </c>
-      <c r="R22" s="256">
-        <v>63.16</v>
-      </c>
-      <c r="S22" s="252">
-        <v>63.16</v>
-      </c>
-      <c r="T22" s="253">
-        <v>47.37</v>
+      <c r="I22">
+        <v>20</v>
+      </c>
+      <c r="J22">
+        <v>20</v>
+      </c>
+      <c r="K22">
+        <v>20</v>
+      </c>
+      <c r="L22">
+        <v>20</v>
+      </c>
+      <c r="M22">
+        <v>19</v>
+      </c>
+      <c r="N22">
+        <v>19</v>
+      </c>
+      <c r="O22">
+        <v>19</v>
+      </c>
+      <c r="P22">
+        <v>19</v>
+      </c>
+      <c r="Q22">
+        <v>19</v>
+      </c>
+      <c r="R22">
+        <v>19</v>
+      </c>
+      <c r="S22">
+        <v>19</v>
+      </c>
+      <c r="T22">
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>平均涨幅</v>
+        <v>上涨比例</v>
       </c>
       <c r="B23" t="str"/>
       <c r="C23" t="str"/>
@@ -6005,41 +6101,89 @@
       <c r="F23" t="str"/>
       <c r="G23" t="str"/>
       <c r="H23" t="str"/>
-      <c r="I23" s="260">
-        <v>0.61</v>
-      </c>
-      <c r="J23" s="261">
-        <v>4.05</v>
-      </c>
-      <c r="K23" s="262">
-        <v>6.6</v>
-      </c>
-      <c r="L23" s="264">
-        <v>6.65</v>
-      </c>
-      <c r="M23" s="265">
+      <c r="I23" s="255">
+        <v>55</v>
+      </c>
+      <c r="J23" s="265">
+        <v>70</v>
+      </c>
+      <c r="K23" s="261">
+        <v>70</v>
+      </c>
+      <c r="L23" s="262">
+        <v>65</v>
+      </c>
+      <c r="M23" s="256">
+        <v>68.42</v>
+      </c>
+      <c r="N23" s="263">
+        <v>57.89</v>
+      </c>
+      <c r="O23" s="264">
+        <v>68.42</v>
+      </c>
+      <c r="P23" s="254">
+        <v>63.16</v>
+      </c>
+      <c r="Q23" s="257">
+        <v>63.16</v>
+      </c>
+      <c r="R23" s="258">
+        <v>63.16</v>
+      </c>
+      <c r="S23" s="259">
+        <v>63.16</v>
+      </c>
+      <c r="T23" s="260">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>平均涨幅</v>
+      </c>
+      <c r="B24" t="str"/>
+      <c r="C24" t="str"/>
+      <c r="D24" t="str"/>
+      <c r="E24" t="str"/>
+      <c r="F24" t="str"/>
+      <c r="G24" t="str"/>
+      <c r="H24" t="str"/>
+      <c r="I24" s="267">
+        <v>0.58</v>
+      </c>
+      <c r="J24" s="271">
+        <v>3.8</v>
+      </c>
+      <c r="K24" s="273">
+        <v>6.05</v>
+      </c>
+      <c r="L24" s="272">
+        <v>5.93</v>
+      </c>
+      <c r="M24" s="268">
         <v>7.77</v>
       </c>
-      <c r="N23" s="268">
+      <c r="N24" s="275">
         <v>9.94</v>
       </c>
-      <c r="O23" s="269">
+      <c r="O24" s="269">
         <v>11.31</v>
       </c>
-      <c r="P23" s="270">
+      <c r="P24" s="276">
         <v>13.62</v>
       </c>
-      <c r="Q23" s="263">
+      <c r="Q24" s="270">
         <v>14.92</v>
       </c>
-      <c r="R23" s="266">
+      <c r="R24" s="277">
         <v>16.06</v>
       </c>
-      <c r="S23" s="271">
+      <c r="S24" s="266">
         <v>15.55</v>
       </c>
-      <c r="T23" s="267">
-        <v>9.96</v>
+      <c r="T24" s="274">
+        <v>7.67</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/牛散唐汉若/index.xlsx
+++ b/youzi/牛散唐汉若/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="279">
+  <fills count="280">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,6 +39,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE0505E"/>
         <bgColor/>
       </patternFill>
@@ -51,55 +69,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF7AC88C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF249A40"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56BA6D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,31 +231,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,55 +291,361 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D5D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56974"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,19 +657,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -231,145 +807,799 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA4D9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD7EEDD"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF56BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0EBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D5D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FF3EB058"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -381,163 +1611,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -549,1075 +1653,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56974"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3EB058"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1651,56 +1705,15 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="278">
+  <borders count="279">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -3651,7 +3664,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="278">
+  <cellXfs count="279">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -4482,6 +4495,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="277" fillId="278" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="278" fillId="279" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -4826,7 +4842,7 @@
       <c r="C2" t="str">
         <v>603300</v>
       </c>
-      <c r="D2" s="13" t="str">
+      <c r="D2" s="8" t="str">
         <v>净买: 7263.08万</v>
       </c>
       <c r="E2">
@@ -4841,41 +4857,41 @@
       <c r="H2">
         <v>5.49</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="4">
         <v>4.31</v>
       </c>
       <c r="J2" s="9">
         <v>-6.1</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="5">
         <v>-0.65</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="2">
         <v>1.06</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="10">
         <v>-3.09</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="3">
         <v>-1.14</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="11">
         <v>-3.25</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="12">
         <v>-6.02</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="6">
         <v>-3.58</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="1">
         <v>-6.59</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="13">
         <v>-13.01</v>
       </c>
-      <c r="T2" s="6">
-        <v>-43.98</v>
+      <c r="T2" s="7">
+        <v>-45.2</v>
       </c>
     </row>
     <row r="3">
@@ -4888,7 +4904,7 @@
       <c r="C3" t="str">
         <v>002093</v>
       </c>
-      <c r="D3" s="18" t="str">
+      <c r="D3" s="14" t="str">
         <v>净卖: -871.26万</v>
       </c>
       <c r="E3">
@@ -4903,41 +4919,41 @@
       <c r="H3">
         <v>10.06</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="15">
         <v>0</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="24">
         <v>10.04</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="16">
         <v>14.06</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="17">
         <v>21.08</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="22">
         <v>33.23</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="18">
         <v>46.59</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="19">
         <v>41.16</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="25">
         <v>31.83</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="23">
         <v>44.98</v>
       </c>
-      <c r="R3" s="17">
+      <c r="R3" s="20">
         <v>59.44</v>
       </c>
       <c r="S3" s="21">
         <v>43.47</v>
       </c>
-      <c r="T3" s="25">
-        <v>-6.83</v>
+      <c r="T3" s="26">
+        <v>-5.82</v>
       </c>
     </row>
     <row r="4">
@@ -4950,7 +4966,7 @@
       <c r="C4" t="str">
         <v>603300</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="37" t="str">
         <v>净买: 227.62万</v>
       </c>
       <c r="E4">
@@ -4965,41 +4981,41 @@
       <c r="H4">
         <v>-6.24</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="30">
         <v>-3.99</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="38">
         <v>1.58</v>
       </c>
-      <c r="K4" s="39">
+      <c r="K4" s="34">
         <v>3.33</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="39">
         <v>-0.91</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="27">
         <v>1.08</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="28">
         <v>-1.08</v>
       </c>
-      <c r="O4" s="34">
+      <c r="O4" s="31">
         <v>-3.91</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="36">
         <v>-1.41</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="Q4" s="29">
         <v>-4.49</v>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="32">
         <v>-11.06</v>
       </c>
       <c r="S4" s="35">
         <v>-8.56</v>
       </c>
-      <c r="T4" s="28">
-        <v>-42.73</v>
+      <c r="T4" s="33">
+        <v>-43.97</v>
       </c>
     </row>
     <row r="5">
@@ -5012,7 +5028,7 @@
       <c r="C5" t="str">
         <v>603300</v>
       </c>
-      <c r="D5" s="48" t="str">
+      <c r="D5" s="42" t="str">
         <v>净卖: -6041.68万</v>
       </c>
       <c r="E5">
@@ -5027,41 +5043,41 @@
       <c r="H5">
         <v>2.16</v>
       </c>
-      <c r="I5" s="45">
+      <c r="I5" s="49">
         <v>3.56</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="43">
         <v>5.34</v>
       </c>
-      <c r="K5" s="46">
+      <c r="K5" s="44">
         <v>1.02</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="46">
         <v>3.05</v>
       </c>
-      <c r="M5" s="47">
+      <c r="M5" s="50">
         <v>0.85</v>
       </c>
-      <c r="N5" s="41">
+      <c r="N5" s="45">
         <v>-2.03</v>
       </c>
-      <c r="O5" s="50">
+      <c r="O5" s="51">
         <v>0.51</v>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="47">
         <v>-2.63</v>
       </c>
-      <c r="Q5" s="44">
+      <c r="Q5" s="52">
         <v>-9.32</v>
       </c>
-      <c r="R5" s="51">
+      <c r="R5" s="40">
         <v>-6.78</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="48">
         <v>-13.73</v>
       </c>
-      <c r="T5" s="40">
-        <v>-41.61</v>
+      <c r="T5" s="41">
+        <v>-42.88</v>
       </c>
     </row>
     <row r="6">
@@ -5074,7 +5090,7 @@
       <c r="C6" t="str">
         <v>603985</v>
       </c>
-      <c r="D6" s="56" t="str">
+      <c r="D6" s="63" t="str">
         <v>净卖: -484.50万</v>
       </c>
       <c r="E6">
@@ -5089,41 +5105,41 @@
       <c r="H6">
         <v>10.01</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="60">
         <v>0</v>
       </c>
-      <c r="J6" s="60">
+      <c r="J6" s="64">
         <v>10.01</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="57">
         <v>7.17</v>
       </c>
-      <c r="L6" s="54">
+      <c r="L6" s="55">
         <v>-3.55</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="56">
         <v>-10.59</v>
       </c>
-      <c r="N6" s="61">
+      <c r="N6" s="65">
         <v>-1.61</v>
       </c>
       <c r="O6" s="58">
         <v>2.32</v>
       </c>
-      <c r="P6" s="59">
+      <c r="P6" s="61">
         <v>3.87</v>
       </c>
-      <c r="Q6" s="64">
+      <c r="Q6" s="53">
         <v>6.33</v>
       </c>
-      <c r="R6" s="65">
+      <c r="R6" s="59">
         <v>4.33</v>
       </c>
       <c r="S6" s="62">
         <v>5.68</v>
       </c>
-      <c r="T6" s="63">
-        <v>63.65</v>
+      <c r="T6" s="54">
+        <v>70.37</v>
       </c>
     </row>
     <row r="7">
@@ -5136,7 +5152,7 @@
       <c r="C7" t="str">
         <v>600744</v>
       </c>
-      <c r="D7" s="67" t="str">
+      <c r="D7" s="74" t="str">
         <v>净卖: -165.95万</v>
       </c>
       <c r="E7">
@@ -5151,41 +5167,41 @@
       <c r="H7">
         <v>10.13</v>
       </c>
-      <c r="I7" s="72">
+      <c r="I7" s="66">
         <v>0</v>
       </c>
-      <c r="J7" s="73">
+      <c r="J7" s="70">
         <v>9.91</v>
       </c>
-      <c r="K7" s="74">
+      <c r="K7" s="71">
         <v>15.8</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="67">
         <v>4.25</v>
       </c>
-      <c r="M7" s="75">
+      <c r="M7" s="68">
         <v>14.62</v>
       </c>
-      <c r="N7" s="66">
+      <c r="N7" s="69">
         <v>19.34</v>
       </c>
-      <c r="O7" s="76">
+      <c r="O7" s="75">
         <v>27.36</v>
       </c>
-      <c r="P7" s="77">
+      <c r="P7" s="72">
         <v>27.36</v>
       </c>
-      <c r="Q7" s="69">
+      <c r="Q7" s="77">
         <v>25.24</v>
       </c>
-      <c r="R7" s="70">
+      <c r="R7" s="76">
         <v>24.53</v>
       </c>
-      <c r="S7" s="71">
+      <c r="S7" s="78">
         <v>22.88</v>
       </c>
-      <c r="T7" s="78">
-        <v>88.92</v>
+      <c r="T7" s="73">
+        <v>85.85</v>
       </c>
     </row>
     <row r="8">
@@ -5198,7 +5214,7 @@
       <c r="C8" t="str">
         <v>603042</v>
       </c>
-      <c r="D8" s="84" t="str">
+      <c r="D8" s="91" t="str">
         <v>净买: 1056.82万</v>
       </c>
       <c r="E8">
@@ -5216,38 +5232,38 @@
       <c r="I8" s="87">
         <v>6.28</v>
       </c>
-      <c r="J8" s="83">
+      <c r="J8" s="79">
         <v>7.66</v>
       </c>
-      <c r="K8" s="85">
+      <c r="K8" s="88">
         <v>9.48</v>
       </c>
-      <c r="L8" s="88">
+      <c r="L8" s="80">
         <v>12.44</v>
       </c>
-      <c r="M8" s="79">
+      <c r="M8" s="81">
         <v>11.93</v>
       </c>
-      <c r="N8" s="89">
+      <c r="N8" s="86">
         <v>9.99</v>
       </c>
-      <c r="O8" s="86">
+      <c r="O8" s="82">
         <v>8.73</v>
       </c>
-      <c r="P8" s="80">
+      <c r="P8" s="83">
         <v>12.5</v>
       </c>
-      <c r="Q8" s="81">
+      <c r="Q8" s="84">
         <v>9.86</v>
       </c>
-      <c r="R8" s="90">
+      <c r="R8" s="85">
         <v>3.71</v>
       </c>
-      <c r="S8" s="91">
+      <c r="S8" s="89">
         <v>5.21</v>
       </c>
-      <c r="T8" s="82">
-        <v>25.63</v>
+      <c r="T8" s="90">
+        <v>25.13</v>
       </c>
     </row>
     <row r="9">
@@ -5260,7 +5276,7 @@
       <c r="C9" t="str">
         <v>603300</v>
       </c>
-      <c r="D9" s="102" t="str">
+      <c r="D9" s="100" t="str">
         <v>净卖: -5853.95万</v>
       </c>
       <c r="E9">
@@ -5275,41 +5291,41 @@
       <c r="H9">
         <v>-0.29</v>
       </c>
-      <c r="I9" s="95">
+      <c r="I9" s="99">
         <v>7.44</v>
       </c>
-      <c r="J9" s="100">
+      <c r="J9" s="96">
         <v>8.23</v>
       </c>
-      <c r="K9" s="96">
+      <c r="K9" s="104">
         <v>9.21</v>
       </c>
-      <c r="L9" s="98">
+      <c r="L9" s="92">
         <v>4.8</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="101">
         <v>2.06</v>
       </c>
-      <c r="N9" s="104">
+      <c r="N9" s="97">
         <v>1.37</v>
       </c>
-      <c r="O9" s="92">
+      <c r="O9" s="93">
         <v>0.78</v>
       </c>
-      <c r="P9" s="97">
+      <c r="P9" s="94">
         <v>4.41</v>
       </c>
-      <c r="Q9" s="93">
+      <c r="Q9" s="102">
         <v>7.05</v>
       </c>
-      <c r="R9" s="94">
+      <c r="R9" s="98">
         <v>4.21</v>
       </c>
-      <c r="S9" s="99">
+      <c r="S9" s="95">
         <v>2.45</v>
       </c>
-      <c r="T9" s="101">
-        <v>-32.52</v>
+      <c r="T9" s="103">
+        <v>-33.99</v>
       </c>
     </row>
     <row r="10">
@@ -5322,7 +5338,7 @@
       <c r="C10" t="str">
         <v>002028</v>
       </c>
-      <c r="D10" s="114" t="str">
+      <c r="D10" s="111" t="str">
         <v>净卖: -3647.56万</v>
       </c>
       <c r="E10">
@@ -5337,41 +5353,41 @@
       <c r="H10">
         <v>7.27</v>
       </c>
-      <c r="I10" s="115">
+      <c r="I10" s="112">
         <v>2.54</v>
       </c>
-      <c r="J10" s="112">
+      <c r="J10" s="113">
         <v>9.99</v>
       </c>
-      <c r="K10" s="109">
+      <c r="K10" s="115">
         <v>6.69</v>
       </c>
-      <c r="L10" s="107">
+      <c r="L10" s="116">
         <v>5.58</v>
       </c>
-      <c r="M10" s="116">
+      <c r="M10" s="107">
         <v>1.57</v>
       </c>
-      <c r="N10" s="110">
+      <c r="N10" s="109">
         <v>3.49</v>
       </c>
-      <c r="O10" s="117">
+      <c r="O10" s="108">
         <v>5.22</v>
       </c>
-      <c r="P10" s="113">
+      <c r="P10" s="114">
         <v>4.9</v>
       </c>
-      <c r="Q10" s="111">
+      <c r="Q10" s="117">
         <v>3.53</v>
       </c>
       <c r="R10" s="105">
         <v>6.54</v>
       </c>
-      <c r="S10" s="106">
+      <c r="S10" s="110">
         <v>8.07</v>
       </c>
-      <c r="T10" s="108">
-        <v>195.86</v>
+      <c r="T10" s="106">
+        <v>176.35</v>
       </c>
     </row>
     <row r="11">
@@ -5384,7 +5400,7 @@
       <c r="C11" t="str">
         <v>603257</v>
       </c>
-      <c r="D11" s="121" t="str">
+      <c r="D11" s="124" t="str">
         <v>净卖: -308.53万</v>
       </c>
       <c r="E11">
@@ -5399,41 +5415,41 @@
       <c r="H11">
         <v>0.04</v>
       </c>
-      <c r="I11" s="122">
+      <c r="I11" s="118">
         <v>3.45</v>
       </c>
-      <c r="J11" s="123">
+      <c r="J11" s="125">
         <v>3.45</v>
       </c>
-      <c r="K11" s="124">
+      <c r="K11" s="128">
         <v>4.99</v>
       </c>
-      <c r="L11" s="125">
+      <c r="L11" s="119">
         <v>3.55</v>
       </c>
-      <c r="M11" s="128">
+      <c r="M11" s="129">
         <v>9.31</v>
       </c>
-      <c r="N11" s="130">
+      <c r="N11" s="126">
         <v>6.44</v>
       </c>
-      <c r="O11" s="118">
+      <c r="O11" s="120">
         <v>5.49</v>
       </c>
-      <c r="P11" s="126">
+      <c r="P11" s="121">
         <v>4.71</v>
       </c>
-      <c r="Q11" s="127">
+      <c r="Q11" s="130">
         <v>3.2</v>
       </c>
-      <c r="R11" s="129">
+      <c r="R11" s="127">
         <v>3.82</v>
       </c>
-      <c r="S11" s="119">
+      <c r="S11" s="122">
         <v>3.18</v>
       </c>
-      <c r="T11" s="120">
-        <v>10.94</v>
+      <c r="T11" s="123">
+        <v>10.2</v>
       </c>
     </row>
     <row r="12">
@@ -5446,7 +5462,7 @@
       <c r="C12" t="str">
         <v>603280</v>
       </c>
-      <c r="D12" s="135" t="str">
+      <c r="D12" s="143" t="str">
         <v>净卖: -740.40万</v>
       </c>
       <c r="E12">
@@ -5461,41 +5477,41 @@
       <c r="H12">
         <v>3.37</v>
       </c>
-      <c r="I12" s="136">
+      <c r="I12" s="133">
         <v>6.41</v>
       </c>
-      <c r="J12" s="131">
+      <c r="J12" s="134">
         <v>17.04</v>
       </c>
-      <c r="K12" s="132">
+      <c r="K12" s="139">
         <v>28.75</v>
       </c>
-      <c r="L12" s="133">
+      <c r="L12" s="135">
         <v>41.65</v>
       </c>
-      <c r="M12" s="137">
+      <c r="M12" s="131">
         <v>38.83</v>
       </c>
-      <c r="N12" s="134">
+      <c r="N12" s="132">
         <v>52.72</v>
       </c>
       <c r="O12" s="142">
         <v>67.99</v>
       </c>
-      <c r="P12" s="138">
+      <c r="P12" s="136">
         <v>84.77</v>
       </c>
-      <c r="Q12" s="143">
+      <c r="Q12" s="140">
         <v>103.26</v>
       </c>
-      <c r="R12" s="139">
+      <c r="R12" s="137">
         <v>112.93</v>
       </c>
-      <c r="S12" s="140">
+      <c r="S12" s="141">
         <v>122.68</v>
       </c>
-      <c r="T12" s="141">
-        <v>25.68</v>
+      <c r="T12" s="138">
+        <v>27.9</v>
       </c>
     </row>
     <row r="13">
@@ -5508,7 +5524,7 @@
       <c r="C13" t="str">
         <v>603280</v>
       </c>
-      <c r="D13" s="154" t="str">
+      <c r="D13" s="152" t="str">
         <v>净卖: -1064.89万</v>
       </c>
       <c r="E13">
@@ -5526,38 +5542,38 @@
       <c r="I13" s="149">
         <v>5.02</v>
       </c>
-      <c r="J13" s="150">
+      <c r="J13" s="153">
         <v>15.53</v>
       </c>
-      <c r="K13" s="151">
+      <c r="K13" s="150">
         <v>27.09</v>
       </c>
-      <c r="L13" s="146">
+      <c r="L13" s="147">
         <v>24.57</v>
       </c>
-      <c r="M13" s="155">
+      <c r="M13" s="156">
         <v>37.03</v>
       </c>
-      <c r="N13" s="156">
+      <c r="N13" s="154">
         <v>50.73</v>
       </c>
-      <c r="O13" s="147">
+      <c r="O13" s="144">
         <v>65.79</v>
       </c>
-      <c r="P13" s="153">
+      <c r="P13" s="148">
         <v>82.38</v>
       </c>
-      <c r="Q13" s="152">
+      <c r="Q13" s="155">
         <v>91.06</v>
       </c>
-      <c r="R13" s="144">
+      <c r="R13" s="151">
         <v>99.8</v>
       </c>
       <c r="S13" s="145">
         <v>90.16</v>
       </c>
-      <c r="T13" s="148">
-        <v>12.77</v>
+      <c r="T13" s="146">
+        <v>14.76</v>
       </c>
     </row>
     <row r="14">
@@ -5585,41 +5601,41 @@
       <c r="H14">
         <v>2.49</v>
       </c>
-      <c r="I14" s="168">
+      <c r="I14" s="161">
         <v>7.32</v>
       </c>
-      <c r="J14" s="161">
+      <c r="J14" s="168">
         <v>18.05</v>
       </c>
-      <c r="K14" s="165">
+      <c r="K14" s="162">
         <v>25.05</v>
       </c>
       <c r="L14" s="169">
         <v>37.57</v>
       </c>
-      <c r="M14" s="157">
+      <c r="M14" s="163">
         <v>35.41</v>
       </c>
-      <c r="N14" s="162">
+      <c r="N14" s="157">
         <v>38.35</v>
       </c>
-      <c r="O14" s="158">
+      <c r="O14" s="164">
         <v>38.24</v>
       </c>
-      <c r="P14" s="159">
+      <c r="P14" s="165">
         <v>39.05</v>
       </c>
-      <c r="Q14" s="163">
+      <c r="Q14" s="158">
         <v>33.92</v>
       </c>
-      <c r="R14" s="164">
+      <c r="R14" s="159">
         <v>47.32</v>
       </c>
       <c r="S14" s="160">
         <v>62.05</v>
       </c>
       <c r="T14" s="166">
-        <v>22.43</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="15">
@@ -5632,7 +5648,7 @@
       <c r="C15" t="str">
         <v>600113</v>
       </c>
-      <c r="D15" s="180" t="str">
+      <c r="D15" s="173" t="str">
         <v>净卖: -2870.19万</v>
       </c>
       <c r="E15">
@@ -5647,41 +5663,41 @@
       <c r="H15">
         <v>-0.58</v>
       </c>
-      <c r="I15" s="172">
+      <c r="I15" s="181">
         <v>10.65</v>
       </c>
-      <c r="J15" s="181">
+      <c r="J15" s="178">
         <v>8.91</v>
       </c>
-      <c r="K15" s="173">
+      <c r="K15" s="170">
         <v>11.28</v>
       </c>
-      <c r="L15" s="179">
+      <c r="L15" s="174">
         <v>11.2</v>
       </c>
-      <c r="M15" s="182">
+      <c r="M15" s="171">
         <v>11.85</v>
       </c>
-      <c r="N15" s="170">
+      <c r="N15" s="179">
         <v>7.72</v>
       </c>
-      <c r="O15" s="174">
+      <c r="O15" s="175">
         <v>18.5</v>
       </c>
-      <c r="P15" s="175">
+      <c r="P15" s="182">
         <v>30.35</v>
       </c>
       <c r="Q15" s="176">
         <v>33.04</v>
       </c>
-      <c r="R15" s="177">
+      <c r="R15" s="180">
         <v>22.78</v>
       </c>
-      <c r="S15" s="171">
+      <c r="S15" s="177">
         <v>28.54</v>
       </c>
-      <c r="T15" s="178">
-        <v>-1.52</v>
+      <c r="T15" s="172">
+        <v>-2.11</v>
       </c>
     </row>
     <row r="16">
@@ -5694,7 +5710,7 @@
       <c r="C16" t="str">
         <v>000014</v>
       </c>
-      <c r="D16" s="184" t="str">
+      <c r="D16" s="185" t="str">
         <v>净卖: -962.87万</v>
       </c>
       <c r="E16">
@@ -5709,41 +5725,41 @@
       <c r="H16">
         <v>9.96</v>
       </c>
-      <c r="I16" s="188">
+      <c r="I16" s="195">
         <v>-12.33</v>
       </c>
-      <c r="J16" s="191">
+      <c r="J16" s="192">
         <v>-15.5</v>
       </c>
-      <c r="K16" s="189">
+      <c r="K16" s="194">
         <v>-14.75</v>
       </c>
-      <c r="L16" s="190">
+      <c r="L16" s="183">
         <v>-14.05</v>
       </c>
-      <c r="M16" s="195">
+      <c r="M16" s="186">
         <v>-12.8</v>
       </c>
-      <c r="N16" s="185">
+      <c r="N16" s="187">
         <v>-18.7</v>
       </c>
-      <c r="O16" s="186">
+      <c r="O16" s="188">
         <v>-26.81</v>
       </c>
-      <c r="P16" s="192">
+      <c r="P16" s="189">
         <v>-26.39</v>
       </c>
-      <c r="Q16" s="183">
+      <c r="Q16" s="190">
         <v>-31.3</v>
       </c>
-      <c r="R16" s="193">
+      <c r="R16" s="191">
         <v>-29.12</v>
       </c>
-      <c r="S16" s="187">
+      <c r="S16" s="184">
         <v>-29.2</v>
       </c>
-      <c r="T16" s="194">
-        <v>-48.79</v>
+      <c r="T16" s="193">
+        <v>-48.44</v>
       </c>
     </row>
     <row r="17">
@@ -5756,7 +5772,7 @@
       <c r="C17" t="str">
         <v>688577</v>
       </c>
-      <c r="D17" s="199" t="str">
+      <c r="D17" s="202" t="str">
         <v>净卖: -1039.47万</v>
       </c>
       <c r="E17">
@@ -5771,41 +5787,41 @@
       <c r="H17">
         <v>-0.04</v>
       </c>
-      <c r="I17" s="200">
+      <c r="I17" s="207">
         <v>-19.96</v>
       </c>
-      <c r="J17" s="206">
+      <c r="J17" s="203">
         <v>-18.66</v>
       </c>
-      <c r="K17" s="207">
+      <c r="K17" s="208">
         <v>-15.24</v>
       </c>
-      <c r="L17" s="208">
+      <c r="L17" s="204">
         <v>-16.26</v>
       </c>
-      <c r="M17" s="201">
+      <c r="M17" s="198">
         <v>-17.76</v>
       </c>
-      <c r="N17" s="202">
+      <c r="N17" s="205">
         <v>-16.4</v>
       </c>
-      <c r="O17" s="203">
+      <c r="O17" s="199">
         <v>-18.64</v>
       </c>
-      <c r="P17" s="196">
+      <c r="P17" s="206">
         <v>-19.41</v>
       </c>
-      <c r="Q17" s="204">
+      <c r="Q17" s="196">
         <v>-10.36</v>
       </c>
       <c r="R17" s="197">
         <v>-13.75</v>
       </c>
-      <c r="S17" s="205">
+      <c r="S17" s="201">
         <v>-14.11</v>
       </c>
-      <c r="T17" s="198">
-        <v>-38.9</v>
+      <c r="T17" s="200">
+        <v>-38.33</v>
       </c>
     </row>
     <row r="18">
@@ -5818,7 +5834,7 @@
       <c r="C18" t="str">
         <v>603757</v>
       </c>
-      <c r="D18" s="217" t="str">
+      <c r="D18" s="209" t="str">
         <v>净卖: -7133.87万</v>
       </c>
       <c r="E18">
@@ -5833,41 +5849,41 @@
       <c r="H18">
         <v>-1.84</v>
       </c>
-      <c r="I18" s="218">
+      <c r="I18" s="214">
         <v>12.06</v>
       </c>
-      <c r="J18" s="221">
+      <c r="J18" s="220">
         <v>13.86</v>
       </c>
-      <c r="K18" s="212">
+      <c r="K18" s="210">
         <v>17.77</v>
       </c>
-      <c r="L18" s="213">
+      <c r="L18" s="216">
         <v>14.57</v>
       </c>
-      <c r="M18" s="209">
+      <c r="M18" s="217">
         <v>16.9</v>
       </c>
-      <c r="N18" s="214">
+      <c r="N18" s="218">
         <v>11.61</v>
       </c>
-      <c r="O18" s="215">
+      <c r="O18" s="221">
         <v>9.48</v>
       </c>
-      <c r="P18" s="216">
+      <c r="P18" s="219">
         <v>12.23</v>
       </c>
-      <c r="Q18" s="219">
+      <c r="Q18" s="211">
         <v>5.19</v>
       </c>
-      <c r="R18" s="220">
+      <c r="R18" s="215">
         <v>8.18</v>
       </c>
-      <c r="S18" s="210">
+      <c r="S18" s="212">
         <v>6.47</v>
       </c>
-      <c r="T18" s="211">
-        <v>20.43</v>
+      <c r="T18" s="213">
+        <v>20.97</v>
       </c>
     </row>
     <row r="19">
@@ -5880,7 +5896,7 @@
       <c r="C19" t="str">
         <v>002117</v>
       </c>
-      <c r="D19" s="229" t="str">
+      <c r="D19" s="227" t="str">
         <v>净卖: -1144.93万</v>
       </c>
       <c r="E19">
@@ -5895,41 +5911,41 @@
       <c r="H19">
         <v>0.29</v>
       </c>
-      <c r="I19" s="233">
+      <c r="I19" s="234">
         <v>-10.25</v>
       </c>
-      <c r="J19" s="232">
+      <c r="J19" s="228">
         <v>-10.69</v>
       </c>
-      <c r="K19" s="234">
+      <c r="K19" s="229">
         <v>-13.72</v>
       </c>
       <c r="L19" s="223">
         <v>-12.78</v>
       </c>
-      <c r="M19" s="224">
+      <c r="M19" s="230">
         <v>-12.64</v>
       </c>
       <c r="N19" s="225">
         <v>-8.52</v>
       </c>
-      <c r="O19" s="222">
+      <c r="O19" s="224">
         <v>-12.27</v>
       </c>
       <c r="P19" s="226">
         <v>-11.26</v>
       </c>
-      <c r="Q19" s="230">
+      <c r="Q19" s="231">
         <v>-12.13</v>
       </c>
-      <c r="R19" s="227">
+      <c r="R19" s="232">
         <v>-12.78</v>
       </c>
-      <c r="S19" s="231">
+      <c r="S19" s="233">
         <v>-12.56</v>
       </c>
-      <c r="T19" s="228">
-        <v>-27.22</v>
+      <c r="T19" s="222">
+        <v>-25.27</v>
       </c>
     </row>
     <row r="20">
@@ -5957,41 +5973,41 @@
       <c r="H20">
         <v>1.07</v>
       </c>
-      <c r="I20" s="236">
+      <c r="I20" s="237">
         <v>-10.98</v>
       </c>
-      <c r="J20" s="239">
+      <c r="J20" s="247">
         <v>-11.79</v>
       </c>
-      <c r="K20" s="237">
+      <c r="K20" s="243">
         <v>-11.87</v>
       </c>
-      <c r="L20" s="238">
+      <c r="L20" s="244">
         <v>-11.54</v>
       </c>
-      <c r="M20" s="243">
+      <c r="M20" s="235">
         <v>-10.08</v>
       </c>
-      <c r="N20" s="244">
+      <c r="N20" s="245">
         <v>-10.08</v>
       </c>
       <c r="O20" s="240">
         <v>-11.71</v>
       </c>
-      <c r="P20" s="247">
+      <c r="P20" s="238">
         <v>-12.52</v>
       </c>
-      <c r="Q20" s="245">
+      <c r="Q20" s="236">
         <v>-11.95</v>
       </c>
-      <c r="R20" s="235">
+      <c r="R20" s="241">
         <v>-12.44</v>
       </c>
-      <c r="S20" s="241">
+      <c r="S20" s="239">
         <v>-14.15</v>
       </c>
       <c r="T20" s="242">
-        <v>-21.14</v>
+        <v>-13.25</v>
       </c>
     </row>
     <row r="21">
@@ -6004,7 +6020,7 @@
       <c r="C21" t="str">
         <v>605178</v>
       </c>
-      <c r="D21" s="253" t="str">
+      <c r="D21" s="251" t="str">
         <v>净买: 140.70万</v>
       </c>
       <c r="E21">
@@ -6019,27 +6035,29 @@
       <c r="H21">
         <v>-10</v>
       </c>
-      <c r="I21" s="248">
+      <c r="I21" s="252">
         <v>0</v>
       </c>
-      <c r="J21" s="249">
+      <c r="J21" s="253">
         <v>-0.91</v>
       </c>
-      <c r="K21" s="250">
+      <c r="K21" s="254">
         <v>-4.48</v>
       </c>
-      <c r="L21" s="251">
+      <c r="L21" s="248">
         <v>-7.6</v>
       </c>
-      <c r="M21" t="str"/>
+      <c r="M21" s="249">
+        <v>0.85</v>
+      </c>
       <c r="N21" t="str"/>
       <c r="O21" t="str"/>
       <c r="P21" t="str"/>
       <c r="Q21" t="str"/>
       <c r="R21" t="str"/>
       <c r="S21" t="str"/>
-      <c r="T21" s="252">
-        <v>-7.6</v>
+      <c r="T21" s="250">
+        <v>0.85</v>
       </c>
     </row>
     <row r="22">
@@ -6066,7 +6084,7 @@
         <v>20</v>
       </c>
       <c r="M22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N22">
         <v>19</v>
@@ -6101,41 +6119,41 @@
       <c r="F23" t="str"/>
       <c r="G23" t="str"/>
       <c r="H23" t="str"/>
-      <c r="I23" s="255">
+      <c r="I23" s="257">
         <v>55</v>
       </c>
-      <c r="J23" s="265">
+      <c r="J23" s="263">
         <v>70</v>
       </c>
-      <c r="K23" s="261">
+      <c r="K23" s="264">
         <v>70</v>
       </c>
-      <c r="L23" s="262">
+      <c r="L23" s="255">
         <v>65</v>
       </c>
       <c r="M23" s="256">
+        <v>70</v>
+      </c>
+      <c r="N23" s="258">
+        <v>57.89</v>
+      </c>
+      <c r="O23" s="259">
         <v>68.42</v>
       </c>
-      <c r="N23" s="263">
-        <v>57.89</v>
-      </c>
-      <c r="O23" s="264">
-        <v>68.42</v>
-      </c>
-      <c r="P23" s="254">
+      <c r="P23" s="265">
         <v>63.16</v>
       </c>
-      <c r="Q23" s="257">
+      <c r="Q23" s="260">
         <v>63.16</v>
       </c>
-      <c r="R23" s="258">
+      <c r="R23" s="266">
         <v>63.16</v>
       </c>
-      <c r="S23" s="259">
+      <c r="S23" s="261">
         <v>63.16</v>
       </c>
-      <c r="T23" s="260">
-        <v>45</v>
+      <c r="T23" s="262">
+        <v>50</v>
       </c>
     </row>
     <row r="24">
@@ -6149,41 +6167,41 @@
       <c r="F24" t="str"/>
       <c r="G24" t="str"/>
       <c r="H24" t="str"/>
-      <c r="I24" s="267">
+      <c r="I24" s="276">
         <v>0.58</v>
       </c>
-      <c r="J24" s="271">
+      <c r="J24" s="269">
         <v>3.8</v>
       </c>
-      <c r="K24" s="273">
+      <c r="K24" s="277">
         <v>6.05</v>
       </c>
-      <c r="L24" s="272">
+      <c r="L24" s="278">
         <v>5.93</v>
       </c>
-      <c r="M24" s="268">
-        <v>7.77</v>
-      </c>
-      <c r="N24" s="275">
+      <c r="M24" s="274">
+        <v>7.43</v>
+      </c>
+      <c r="N24" s="270">
         <v>9.94</v>
       </c>
-      <c r="O24" s="269">
+      <c r="O24" s="275">
         <v>11.31</v>
       </c>
-      <c r="P24" s="276">
+      <c r="P24" s="267">
         <v>13.62</v>
       </c>
-      <c r="Q24" s="270">
+      <c r="Q24" s="268">
         <v>14.92</v>
       </c>
-      <c r="R24" s="277">
+      <c r="R24" s="271">
         <v>16.06</v>
       </c>
-      <c r="S24" s="266">
+      <c r="S24" s="272">
         <v>15.55</v>
       </c>
-      <c r="T24" s="274">
-        <v>7.67</v>
+      <c r="T24" s="273">
+        <v>7.74</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/牛散唐汉若/index.xlsx
+++ b/youzi/牛散唐汉若/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="280">
+  <fills count="281">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,19 +39,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF23943D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,13 +117,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,13 +261,799 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D5D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56974"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,13 +1065,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -117,445 +1137,517 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0EBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF56BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD7EEDD"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D5D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56974"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
+        <fgColor rgb="FF3EB058"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -567,1092 +1659,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA4D9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3EB058"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -1706,7 +1712,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="279">
+  <borders count="280">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -3664,7 +3677,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="279">
+  <cellXfs count="280">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -4498,6 +4511,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="278" fillId="279" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="279" fillId="280" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -4857,41 +4873,41 @@
       <c r="H2">
         <v>5.49</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="13">
         <v>4.31</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="11">
         <v>-6.1</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="9">
         <v>-0.65</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="1">
         <v>1.06</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="3">
         <v>-3.09</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="4">
         <v>-1.14</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="10">
         <v>-3.25</v>
       </c>
       <c r="P2" s="12">
         <v>-6.02</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="5">
         <v>-3.58</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="6">
         <v>-6.59</v>
       </c>
-      <c r="S2" s="13">
+      <c r="S2" s="2">
         <v>-13.01</v>
       </c>
       <c r="T2" s="7">
-        <v>-45.2</v>
+        <v>-45.69</v>
       </c>
     </row>
     <row r="3">
@@ -4904,7 +4920,7 @@
       <c r="C3" t="str">
         <v>002093</v>
       </c>
-      <c r="D3" s="14" t="str">
+      <c r="D3" s="17" t="str">
         <v>净卖: -871.26万</v>
       </c>
       <c r="E3">
@@ -4919,41 +4935,41 @@
       <c r="H3">
         <v>10.06</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="26">
         <v>0</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="14">
         <v>10.04</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="15">
         <v>14.06</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="22">
         <v>21.08</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="16">
         <v>33.23</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="19">
         <v>46.59</v>
       </c>
-      <c r="O3" s="19">
+      <c r="O3" s="20">
         <v>41.16</v>
       </c>
-      <c r="P3" s="25">
+      <c r="P3" s="23">
         <v>31.83</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="18">
         <v>44.98</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="21">
         <v>59.44</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="24">
         <v>43.47</v>
       </c>
-      <c r="T3" s="26">
-        <v>-5.82</v>
+      <c r="T3" s="25">
+        <v>-9.04</v>
       </c>
     </row>
     <row r="4">
@@ -4966,7 +4982,7 @@
       <c r="C4" t="str">
         <v>603300</v>
       </c>
-      <c r="D4" s="37" t="str">
+      <c r="D4" s="27" t="str">
         <v>净买: 227.62万</v>
       </c>
       <c r="E4">
@@ -4981,25 +4997,25 @@
       <c r="H4">
         <v>-6.24</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="34">
         <v>-3.99</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="31">
         <v>1.58</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="32">
         <v>3.33</v>
       </c>
-      <c r="L4" s="39">
+      <c r="L4" s="35">
         <v>-0.91</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="33">
         <v>1.08</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="39">
         <v>-1.08</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="28">
         <v>-3.91</v>
       </c>
       <c r="P4" s="36">
@@ -5008,14 +5024,14 @@
       <c r="Q4" s="29">
         <v>-4.49</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="37">
         <v>-11.06</v>
       </c>
-      <c r="S4" s="35">
+      <c r="S4" s="30">
         <v>-8.56</v>
       </c>
-      <c r="T4" s="33">
-        <v>-43.97</v>
+      <c r="T4" s="38">
+        <v>-44.47</v>
       </c>
     </row>
     <row r="5">
@@ -5028,7 +5044,7 @@
       <c r="C5" t="str">
         <v>603300</v>
       </c>
-      <c r="D5" s="42" t="str">
+      <c r="D5" s="49" t="str">
         <v>净卖: -6041.68万</v>
       </c>
       <c r="E5">
@@ -5043,7 +5059,7 @@
       <c r="H5">
         <v>2.16</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="42">
         <v>3.56</v>
       </c>
       <c r="J5" s="43">
@@ -5052,32 +5068,32 @@
       <c r="K5" s="44">
         <v>1.02</v>
       </c>
-      <c r="L5" s="46">
+      <c r="L5" s="50">
         <v>3.05</v>
       </c>
-      <c r="M5" s="50">
+      <c r="M5" s="45">
         <v>0.85</v>
       </c>
-      <c r="N5" s="45">
+      <c r="N5" s="51">
         <v>-2.03</v>
       </c>
-      <c r="O5" s="51">
+      <c r="O5" s="52">
         <v>0.51</v>
       </c>
-      <c r="P5" s="47">
+      <c r="P5" s="46">
         <v>-2.63</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="40">
         <v>-9.32</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="47">
         <v>-6.78</v>
       </c>
-      <c r="S5" s="48">
+      <c r="S5" s="41">
         <v>-13.73</v>
       </c>
-      <c r="T5" s="41">
-        <v>-42.88</v>
+      <c r="T5" s="48">
+        <v>-43.39</v>
       </c>
     </row>
     <row r="6">
@@ -5090,7 +5106,7 @@
       <c r="C6" t="str">
         <v>603985</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="62" t="str">
         <v>净卖: -484.50万</v>
       </c>
       <c r="E6">
@@ -5105,41 +5121,41 @@
       <c r="H6">
         <v>10.01</v>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="63">
         <v>0</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="57">
         <v>10.01</v>
       </c>
-      <c r="K6" s="57">
+      <c r="K6" s="58">
         <v>7.17</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="59">
         <v>-3.55</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="64">
         <v>-10.59</v>
       </c>
       <c r="N6" s="65">
         <v>-1.61</v>
       </c>
-      <c r="O6" s="58">
+      <c r="O6" s="60">
         <v>2.32</v>
       </c>
-      <c r="P6" s="61">
+      <c r="P6" s="53">
         <v>3.87</v>
       </c>
-      <c r="Q6" s="53">
+      <c r="Q6" s="54">
         <v>6.33</v>
       </c>
-      <c r="R6" s="59">
+      <c r="R6" s="55">
         <v>4.33</v>
       </c>
-      <c r="S6" s="62">
+      <c r="S6" s="61">
         <v>5.68</v>
       </c>
-      <c r="T6" s="54">
-        <v>70.37</v>
+      <c r="T6" s="56">
+        <v>77.66</v>
       </c>
     </row>
     <row r="7">
@@ -5152,7 +5168,7 @@
       <c r="C7" t="str">
         <v>600744</v>
       </c>
-      <c r="D7" s="74" t="str">
+      <c r="D7" s="66" t="str">
         <v>净卖: -165.95万</v>
       </c>
       <c r="E7">
@@ -5167,41 +5183,41 @@
       <c r="H7">
         <v>10.13</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="67">
         <v>0</v>
       </c>
       <c r="J7" s="70">
         <v>9.91</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="73">
         <v>15.8</v>
       </c>
-      <c r="L7" s="67">
+      <c r="L7" s="75">
         <v>4.25</v>
       </c>
-      <c r="M7" s="68">
+      <c r="M7" s="74">
         <v>14.62</v>
       </c>
-      <c r="N7" s="69">
+      <c r="N7" s="76">
         <v>19.34</v>
       </c>
-      <c r="O7" s="75">
+      <c r="O7" s="71">
         <v>27.36</v>
       </c>
-      <c r="P7" s="72">
+      <c r="P7" s="77">
         <v>27.36</v>
       </c>
-      <c r="Q7" s="77">
+      <c r="Q7" s="78">
         <v>25.24</v>
       </c>
-      <c r="R7" s="76">
+      <c r="R7" s="72">
         <v>24.53</v>
       </c>
-      <c r="S7" s="78">
+      <c r="S7" s="68">
         <v>22.88</v>
       </c>
-      <c r="T7" s="73">
-        <v>85.85</v>
+      <c r="T7" s="69">
+        <v>104.48</v>
       </c>
     </row>
     <row r="8">
@@ -5214,7 +5230,7 @@
       <c r="C8" t="str">
         <v>603042</v>
       </c>
-      <c r="D8" s="91" t="str">
+      <c r="D8" s="82" t="str">
         <v>净买: 1056.82万</v>
       </c>
       <c r="E8">
@@ -5229,41 +5245,41 @@
       <c r="H8">
         <v>-0.69</v>
       </c>
-      <c r="I8" s="87">
+      <c r="I8" s="84">
         <v>6.28</v>
       </c>
-      <c r="J8" s="79">
+      <c r="J8" s="85">
         <v>7.66</v>
       </c>
-      <c r="K8" s="88">
+      <c r="K8" s="86">
         <v>9.48</v>
       </c>
-      <c r="L8" s="80">
+      <c r="L8" s="87">
         <v>12.44</v>
       </c>
-      <c r="M8" s="81">
+      <c r="M8" s="89">
         <v>11.93</v>
       </c>
-      <c r="N8" s="86">
+      <c r="N8" s="90">
         <v>9.99</v>
       </c>
-      <c r="O8" s="82">
+      <c r="O8" s="80">
         <v>8.73</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8" s="91">
         <v>12.5</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="88">
         <v>9.86</v>
       </c>
-      <c r="R8" s="85">
+      <c r="R8" s="81">
         <v>3.71</v>
       </c>
-      <c r="S8" s="89">
+      <c r="S8" s="79">
         <v>5.21</v>
       </c>
-      <c r="T8" s="90">
-        <v>25.13</v>
+      <c r="T8" s="83">
+        <v>25.38</v>
       </c>
     </row>
     <row r="9">
@@ -5276,7 +5292,7 @@
       <c r="C9" t="str">
         <v>603300</v>
       </c>
-      <c r="D9" s="100" t="str">
+      <c r="D9" s="96" t="str">
         <v>净卖: -5853.95万</v>
       </c>
       <c r="E9">
@@ -5291,41 +5307,41 @@
       <c r="H9">
         <v>-0.29</v>
       </c>
-      <c r="I9" s="99">
+      <c r="I9" s="100">
         <v>7.44</v>
       </c>
-      <c r="J9" s="96">
+      <c r="J9" s="92">
         <v>8.23</v>
       </c>
-      <c r="K9" s="104">
+      <c r="K9" s="93">
         <v>9.21</v>
       </c>
-      <c r="L9" s="92">
+      <c r="L9" s="101">
         <v>4.8</v>
       </c>
-      <c r="M9" s="101">
+      <c r="M9" s="94">
         <v>2.06</v>
       </c>
-      <c r="N9" s="97">
+      <c r="N9" s="102">
         <v>1.37</v>
       </c>
-      <c r="O9" s="93">
+      <c r="O9" s="97">
         <v>0.78</v>
       </c>
-      <c r="P9" s="94">
+      <c r="P9" s="95">
         <v>4.41</v>
       </c>
-      <c r="Q9" s="102">
+      <c r="Q9" s="103">
         <v>7.05</v>
       </c>
       <c r="R9" s="98">
         <v>4.21</v>
       </c>
-      <c r="S9" s="95">
+      <c r="S9" s="99">
         <v>2.45</v>
       </c>
-      <c r="T9" s="103">
-        <v>-33.99</v>
+      <c r="T9" s="104">
+        <v>-34.57</v>
       </c>
     </row>
     <row r="10">
@@ -5338,7 +5354,7 @@
       <c r="C10" t="str">
         <v>002028</v>
       </c>
-      <c r="D10" s="111" t="str">
+      <c r="D10" s="117" t="str">
         <v>净卖: -3647.56万</v>
       </c>
       <c r="E10">
@@ -5353,41 +5369,41 @@
       <c r="H10">
         <v>7.27</v>
       </c>
-      <c r="I10" s="112">
+      <c r="I10" s="114">
         <v>2.54</v>
       </c>
-      <c r="J10" s="113">
+      <c r="J10" s="115">
         <v>9.99</v>
       </c>
-      <c r="K10" s="115">
+      <c r="K10" s="116">
         <v>6.69</v>
       </c>
-      <c r="L10" s="116">
+      <c r="L10" s="105">
         <v>5.58</v>
       </c>
-      <c r="M10" s="107">
+      <c r="M10" s="106">
         <v>1.57</v>
       </c>
-      <c r="N10" s="109">
+      <c r="N10" s="111">
         <v>3.49</v>
       </c>
-      <c r="O10" s="108">
+      <c r="O10" s="112">
         <v>5.22</v>
       </c>
-      <c r="P10" s="114">
+      <c r="P10" s="110">
         <v>4.9</v>
       </c>
-      <c r="Q10" s="117">
+      <c r="Q10" s="107">
         <v>3.53</v>
       </c>
-      <c r="R10" s="105">
+      <c r="R10" s="108">
         <v>6.54</v>
       </c>
-      <c r="S10" s="110">
+      <c r="S10" s="109">
         <v>8.07</v>
       </c>
-      <c r="T10" s="106">
-        <v>176.35</v>
+      <c r="T10" s="113">
+        <v>160.06</v>
       </c>
     </row>
     <row r="11">
@@ -5400,7 +5416,7 @@
       <c r="C11" t="str">
         <v>603257</v>
       </c>
-      <c r="D11" s="124" t="str">
+      <c r="D11" s="122" t="str">
         <v>净卖: -308.53万</v>
       </c>
       <c r="E11">
@@ -5415,41 +5431,41 @@
       <c r="H11">
         <v>0.04</v>
       </c>
-      <c r="I11" s="118">
+      <c r="I11" s="123">
         <v>3.45</v>
       </c>
-      <c r="J11" s="125">
+      <c r="J11" s="124">
         <v>3.45</v>
       </c>
-      <c r="K11" s="128">
+      <c r="K11" s="127">
         <v>4.99</v>
       </c>
-      <c r="L11" s="119">
+      <c r="L11" s="130">
         <v>3.55</v>
       </c>
-      <c r="M11" s="129">
+      <c r="M11" s="118">
         <v>9.31</v>
       </c>
-      <c r="N11" s="126">
+      <c r="N11" s="119">
         <v>6.44</v>
       </c>
-      <c r="O11" s="120">
+      <c r="O11" s="121">
         <v>5.49</v>
       </c>
-      <c r="P11" s="121">
+      <c r="P11" s="120">
         <v>4.71</v>
       </c>
-      <c r="Q11" s="130">
+      <c r="Q11" s="125">
         <v>3.2</v>
       </c>
-      <c r="R11" s="127">
+      <c r="R11" s="126">
         <v>3.82</v>
       </c>
-      <c r="S11" s="122">
+      <c r="S11" s="128">
         <v>3.18</v>
       </c>
-      <c r="T11" s="123">
-        <v>10.2</v>
+      <c r="T11" s="129">
+        <v>12.78</v>
       </c>
     </row>
     <row r="12">
@@ -5462,7 +5478,7 @@
       <c r="C12" t="str">
         <v>603280</v>
       </c>
-      <c r="D12" s="143" t="str">
+      <c r="D12" s="140" t="str">
         <v>净卖: -740.40万</v>
       </c>
       <c r="E12">
@@ -5477,41 +5493,41 @@
       <c r="H12">
         <v>3.37</v>
       </c>
-      <c r="I12" s="133">
+      <c r="I12" s="136">
         <v>6.41</v>
       </c>
-      <c r="J12" s="134">
+      <c r="J12" s="133">
         <v>17.04</v>
       </c>
-      <c r="K12" s="139">
+      <c r="K12" s="137">
         <v>28.75</v>
       </c>
-      <c r="L12" s="135">
+      <c r="L12" s="141">
         <v>41.65</v>
       </c>
-      <c r="M12" s="131">
+      <c r="M12" s="142">
         <v>38.83</v>
       </c>
-      <c r="N12" s="132">
+      <c r="N12" s="139">
         <v>52.72</v>
       </c>
-      <c r="O12" s="142">
+      <c r="O12" s="134">
         <v>67.99</v>
       </c>
-      <c r="P12" s="136">
+      <c r="P12" s="143">
         <v>84.77</v>
       </c>
-      <c r="Q12" s="140">
+      <c r="Q12" s="138">
         <v>103.26</v>
       </c>
-      <c r="R12" s="137">
+      <c r="R12" s="131">
         <v>112.93</v>
       </c>
-      <c r="S12" s="141">
+      <c r="S12" s="135">
         <v>122.68</v>
       </c>
-      <c r="T12" s="138">
-        <v>27.9</v>
+      <c r="T12" s="132">
+        <v>26.01</v>
       </c>
     </row>
     <row r="13">
@@ -5524,7 +5540,7 @@
       <c r="C13" t="str">
         <v>603280</v>
       </c>
-      <c r="D13" s="152" t="str">
+      <c r="D13" s="153" t="str">
         <v>净卖: -1064.89万</v>
       </c>
       <c r="E13">
@@ -5539,41 +5555,41 @@
       <c r="H13">
         <v>4.74</v>
       </c>
-      <c r="I13" s="149">
+      <c r="I13" s="156">
         <v>5.02</v>
       </c>
-      <c r="J13" s="153">
+      <c r="J13" s="154">
         <v>15.53</v>
       </c>
-      <c r="K13" s="150">
+      <c r="K13" s="148">
         <v>27.09</v>
       </c>
-      <c r="L13" s="147">
+      <c r="L13" s="149">
         <v>24.57</v>
       </c>
-      <c r="M13" s="156">
+      <c r="M13" s="155">
         <v>37.03</v>
       </c>
-      <c r="N13" s="154">
+      <c r="N13" s="150">
         <v>50.73</v>
       </c>
-      <c r="O13" s="144">
+      <c r="O13" s="151">
         <v>65.79</v>
       </c>
-      <c r="P13" s="148">
+      <c r="P13" s="152">
         <v>82.38</v>
       </c>
-      <c r="Q13" s="155">
+      <c r="Q13" s="145">
         <v>91.06</v>
       </c>
-      <c r="R13" s="151">
+      <c r="R13" s="146">
         <v>99.8</v>
       </c>
-      <c r="S13" s="145">
+      <c r="S13" s="144">
         <v>90.16</v>
       </c>
-      <c r="T13" s="146">
-        <v>14.76</v>
+      <c r="T13" s="147">
+        <v>13.07</v>
       </c>
     </row>
     <row r="14">
@@ -5586,7 +5602,7 @@
       <c r="C14" t="str">
         <v>600113</v>
       </c>
-      <c r="D14" s="167" t="str">
+      <c r="D14" s="165" t="str">
         <v>净卖: -1621.26万</v>
       </c>
       <c r="E14">
@@ -5601,41 +5617,41 @@
       <c r="H14">
         <v>2.49</v>
       </c>
-      <c r="I14" s="161">
+      <c r="I14" s="158">
         <v>7.32</v>
       </c>
       <c r="J14" s="168">
         <v>18.05</v>
       </c>
-      <c r="K14" s="162">
+      <c r="K14" s="169">
         <v>25.05</v>
       </c>
-      <c r="L14" s="169">
+      <c r="L14" s="166">
         <v>37.57</v>
       </c>
-      <c r="M14" s="163">
+      <c r="M14" s="159">
         <v>35.41</v>
       </c>
-      <c r="N14" s="157">
+      <c r="N14" s="163">
         <v>38.35</v>
       </c>
-      <c r="O14" s="164">
+      <c r="O14" s="157">
         <v>38.24</v>
       </c>
-      <c r="P14" s="165">
+      <c r="P14" s="160">
         <v>39.05</v>
       </c>
-      <c r="Q14" s="158">
+      <c r="Q14" s="161">
         <v>33.92</v>
       </c>
-      <c r="R14" s="159">
+      <c r="R14" s="167">
         <v>47.32</v>
       </c>
-      <c r="S14" s="160">
+      <c r="S14" s="164">
         <v>62.05</v>
       </c>
-      <c r="T14" s="166">
-        <v>21.7</v>
+      <c r="T14" s="162">
+        <v>20.49</v>
       </c>
     </row>
     <row r="15">
@@ -5648,7 +5664,7 @@
       <c r="C15" t="str">
         <v>600113</v>
       </c>
-      <c r="D15" s="173" t="str">
+      <c r="D15" s="176" t="str">
         <v>净卖: -2870.19万</v>
       </c>
       <c r="E15">
@@ -5663,41 +5679,41 @@
       <c r="H15">
         <v>-0.58</v>
       </c>
-      <c r="I15" s="181">
+      <c r="I15" s="180">
         <v>10.65</v>
       </c>
-      <c r="J15" s="178">
+      <c r="J15" s="181">
         <v>8.91</v>
       </c>
-      <c r="K15" s="170">
+      <c r="K15" s="182">
         <v>11.28</v>
       </c>
-      <c r="L15" s="174">
+      <c r="L15" s="177">
         <v>11.2</v>
       </c>
-      <c r="M15" s="171">
+      <c r="M15" s="178">
         <v>11.85</v>
       </c>
-      <c r="N15" s="179">
+      <c r="N15" s="172">
         <v>7.72</v>
       </c>
-      <c r="O15" s="175">
+      <c r="O15" s="179">
         <v>18.5</v>
       </c>
-      <c r="P15" s="182">
+      <c r="P15" s="173">
         <v>30.35</v>
       </c>
-      <c r="Q15" s="176">
+      <c r="Q15" s="174">
         <v>33.04</v>
       </c>
-      <c r="R15" s="180">
+      <c r="R15" s="175">
         <v>22.78</v>
       </c>
-      <c r="S15" s="177">
+      <c r="S15" s="170">
         <v>28.54</v>
       </c>
-      <c r="T15" s="172">
-        <v>-2.11</v>
+      <c r="T15" s="171">
+        <v>-3.09</v>
       </c>
     </row>
     <row r="16">
@@ -5710,7 +5726,7 @@
       <c r="C16" t="str">
         <v>000014</v>
       </c>
-      <c r="D16" s="185" t="str">
+      <c r="D16" s="194" t="str">
         <v>净卖: -962.87万</v>
       </c>
       <c r="E16">
@@ -5728,38 +5744,38 @@
       <c r="I16" s="195">
         <v>-12.33</v>
       </c>
-      <c r="J16" s="192">
+      <c r="J16" s="183">
         <v>-15.5</v>
       </c>
-      <c r="K16" s="194">
+      <c r="K16" s="184">
         <v>-14.75</v>
       </c>
-      <c r="L16" s="183">
+      <c r="L16" s="188">
         <v>-14.05</v>
       </c>
       <c r="M16" s="186">
         <v>-12.8</v>
       </c>
-      <c r="N16" s="187">
+      <c r="N16" s="189">
         <v>-18.7</v>
       </c>
-      <c r="O16" s="188">
+      <c r="O16" s="192">
         <v>-26.81</v>
       </c>
-      <c r="P16" s="189">
+      <c r="P16" s="193">
         <v>-26.39</v>
       </c>
       <c r="Q16" s="190">
         <v>-31.3</v>
       </c>
-      <c r="R16" s="191">
+      <c r="R16" s="187">
         <v>-29.12</v>
       </c>
-      <c r="S16" s="184">
+      <c r="S16" s="185">
         <v>-29.2</v>
       </c>
-      <c r="T16" s="193">
-        <v>-48.44</v>
+      <c r="T16" s="191">
+        <v>-49.1</v>
       </c>
     </row>
     <row r="17">
@@ -5787,41 +5803,41 @@
       <c r="H17">
         <v>-0.04</v>
       </c>
-      <c r="I17" s="207">
+      <c r="I17" s="199">
         <v>-19.96</v>
       </c>
-      <c r="J17" s="203">
+      <c r="J17" s="208">
         <v>-18.66</v>
       </c>
-      <c r="K17" s="208">
+      <c r="K17" s="203">
         <v>-15.24</v>
       </c>
       <c r="L17" s="204">
         <v>-16.26</v>
       </c>
-      <c r="M17" s="198">
+      <c r="M17" s="205">
         <v>-17.76</v>
       </c>
-      <c r="N17" s="205">
+      <c r="N17" s="200">
         <v>-16.4</v>
       </c>
-      <c r="O17" s="199">
+      <c r="O17" s="206">
         <v>-18.64</v>
       </c>
-      <c r="P17" s="206">
+      <c r="P17" s="196">
         <v>-19.41</v>
       </c>
-      <c r="Q17" s="196">
+      <c r="Q17" s="207">
         <v>-10.36</v>
       </c>
       <c r="R17" s="197">
         <v>-13.75</v>
       </c>
-      <c r="S17" s="201">
+      <c r="S17" s="198">
         <v>-14.11</v>
       </c>
-      <c r="T17" s="200">
-        <v>-38.33</v>
+      <c r="T17" s="201">
+        <v>-38.9</v>
       </c>
     </row>
     <row r="18">
@@ -5834,7 +5850,7 @@
       <c r="C18" t="str">
         <v>603757</v>
       </c>
-      <c r="D18" s="209" t="str">
+      <c r="D18" s="214" t="str">
         <v>净卖: -7133.87万</v>
       </c>
       <c r="E18">
@@ -5849,41 +5865,41 @@
       <c r="H18">
         <v>-1.84</v>
       </c>
-      <c r="I18" s="214">
+      <c r="I18" s="211">
         <v>12.06</v>
       </c>
-      <c r="J18" s="220">
+      <c r="J18" s="215">
         <v>13.86</v>
       </c>
-      <c r="K18" s="210">
+      <c r="K18" s="209">
         <v>17.77</v>
       </c>
-      <c r="L18" s="216">
+      <c r="L18" s="218">
         <v>14.57</v>
       </c>
-      <c r="M18" s="217">
+      <c r="M18" s="212">
         <v>16.9</v>
       </c>
-      <c r="N18" s="218">
+      <c r="N18" s="216">
         <v>11.61</v>
       </c>
-      <c r="O18" s="221">
+      <c r="O18" s="219">
         <v>9.48</v>
       </c>
-      <c r="P18" s="219">
+      <c r="P18" s="220">
         <v>12.23</v>
       </c>
-      <c r="Q18" s="211">
+      <c r="Q18" s="210">
         <v>5.19</v>
       </c>
-      <c r="R18" s="215">
+      <c r="R18" s="221">
         <v>8.18</v>
       </c>
-      <c r="S18" s="212">
+      <c r="S18" s="213">
         <v>6.47</v>
       </c>
-      <c r="T18" s="213">
-        <v>20.97</v>
+      <c r="T18" s="217">
+        <v>15.59</v>
       </c>
     </row>
     <row r="19">
@@ -5896,7 +5912,7 @@
       <c r="C19" t="str">
         <v>002117</v>
       </c>
-      <c r="D19" s="227" t="str">
+      <c r="D19" s="229" t="str">
         <v>净卖: -1144.93万</v>
       </c>
       <c r="E19">
@@ -5911,41 +5927,41 @@
       <c r="H19">
         <v>0.29</v>
       </c>
-      <c r="I19" s="234">
+      <c r="I19" s="230">
         <v>-10.25</v>
       </c>
-      <c r="J19" s="228">
+      <c r="J19" s="223">
         <v>-10.69</v>
       </c>
-      <c r="K19" s="229">
+      <c r="K19" s="224">
         <v>-13.72</v>
       </c>
-      <c r="L19" s="223">
+      <c r="L19" s="231">
         <v>-12.78</v>
       </c>
-      <c r="M19" s="230">
+      <c r="M19" s="225">
         <v>-12.64</v>
       </c>
-      <c r="N19" s="225">
+      <c r="N19" s="222">
         <v>-8.52</v>
       </c>
-      <c r="O19" s="224">
+      <c r="O19" s="226">
         <v>-12.27</v>
       </c>
-      <c r="P19" s="226">
+      <c r="P19" s="227">
         <v>-11.26</v>
       </c>
-      <c r="Q19" s="231">
+      <c r="Q19" s="232">
         <v>-12.13</v>
       </c>
-      <c r="R19" s="232">
+      <c r="R19" s="228">
         <v>-12.78</v>
       </c>
       <c r="S19" s="233">
         <v>-12.56</v>
       </c>
-      <c r="T19" s="222">
-        <v>-25.27</v>
+      <c r="T19" s="234">
+        <v>-28.09</v>
       </c>
     </row>
     <row r="20">
@@ -5958,7 +5974,7 @@
       <c r="C20" t="str">
         <v>600246</v>
       </c>
-      <c r="D20" s="246" t="str">
+      <c r="D20" s="243" t="str">
         <v>净买: 1107.56万</v>
       </c>
       <c r="E20">
@@ -5973,41 +5989,41 @@
       <c r="H20">
         <v>1.07</v>
       </c>
-      <c r="I20" s="237">
+      <c r="I20" s="244">
         <v>-10.98</v>
       </c>
-      <c r="J20" s="247">
+      <c r="J20" s="239">
         <v>-11.79</v>
       </c>
-      <c r="K20" s="243">
+      <c r="K20" s="245">
         <v>-11.87</v>
       </c>
-      <c r="L20" s="244">
+      <c r="L20" s="236">
         <v>-11.54</v>
       </c>
-      <c r="M20" s="235">
+      <c r="M20" s="240">
         <v>-10.08</v>
       </c>
-      <c r="N20" s="245">
+      <c r="N20" s="246">
         <v>-10.08</v>
       </c>
-      <c r="O20" s="240">
+      <c r="O20" s="242">
         <v>-11.71</v>
       </c>
-      <c r="P20" s="238">
+      <c r="P20" s="247">
         <v>-12.52</v>
       </c>
-      <c r="Q20" s="236">
+      <c r="Q20" s="237">
         <v>-11.95</v>
       </c>
-      <c r="R20" s="241">
+      <c r="R20" s="235">
         <v>-12.44</v>
       </c>
-      <c r="S20" s="239">
+      <c r="S20" s="238">
         <v>-14.15</v>
       </c>
-      <c r="T20" s="242">
-        <v>-13.25</v>
+      <c r="T20" s="241">
+        <v>-16.91</v>
       </c>
     </row>
     <row r="21">
@@ -6044,20 +6060,22 @@
       <c r="K21" s="254">
         <v>-4.48</v>
       </c>
-      <c r="L21" s="248">
+      <c r="L21" s="255">
         <v>-7.6</v>
       </c>
-      <c r="M21" s="249">
+      <c r="M21" s="248">
         <v>0.85</v>
       </c>
-      <c r="N21" t="str"/>
+      <c r="N21" s="249">
+        <v>-2.84</v>
+      </c>
       <c r="O21" t="str"/>
       <c r="P21" t="str"/>
       <c r="Q21" t="str"/>
       <c r="R21" t="str"/>
       <c r="S21" t="str"/>
       <c r="T21" s="250">
-        <v>0.85</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="22">
@@ -6087,7 +6105,7 @@
         <v>20</v>
       </c>
       <c r="N22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O22">
         <v>19</v>
@@ -6119,41 +6137,41 @@
       <c r="F23" t="str"/>
       <c r="G23" t="str"/>
       <c r="H23" t="str"/>
-      <c r="I23" s="257">
+      <c r="I23" s="266">
         <v>55</v>
       </c>
-      <c r="J23" s="263">
+      <c r="J23" s="260">
         <v>70</v>
       </c>
-      <c r="K23" s="264">
+      <c r="K23" s="263">
         <v>70</v>
       </c>
-      <c r="L23" s="255">
+      <c r="L23" s="264">
         <v>65</v>
       </c>
-      <c r="M23" s="256">
+      <c r="M23" s="261">
         <v>70</v>
       </c>
-      <c r="N23" s="258">
-        <v>57.89</v>
-      </c>
-      <c r="O23" s="259">
+      <c r="N23" s="267">
+        <v>55</v>
+      </c>
+      <c r="O23" s="256">
         <v>68.42</v>
       </c>
       <c r="P23" s="265">
         <v>63.16</v>
       </c>
-      <c r="Q23" s="260">
+      <c r="Q23" s="262">
         <v>63.16</v>
       </c>
-      <c r="R23" s="266">
+      <c r="R23" s="257">
         <v>63.16</v>
       </c>
-      <c r="S23" s="261">
+      <c r="S23" s="258">
         <v>63.16</v>
       </c>
-      <c r="T23" s="262">
-        <v>50</v>
+      <c r="T23" s="259">
+        <v>45</v>
       </c>
     </row>
     <row r="24">
@@ -6167,41 +6185,41 @@
       <c r="F24" t="str"/>
       <c r="G24" t="str"/>
       <c r="H24" t="str"/>
-      <c r="I24" s="276">
+      <c r="I24" s="277">
         <v>0.58</v>
       </c>
-      <c r="J24" s="269">
+      <c r="J24" s="270">
         <v>3.8</v>
       </c>
-      <c r="K24" s="277">
+      <c r="K24" s="271">
         <v>6.05</v>
       </c>
-      <c r="L24" s="278">
+      <c r="L24" s="275">
         <v>5.93</v>
       </c>
-      <c r="M24" s="274">
+      <c r="M24" s="278">
         <v>7.43</v>
       </c>
-      <c r="N24" s="270">
-        <v>9.94</v>
-      </c>
-      <c r="O24" s="275">
+      <c r="N24" s="279">
+        <v>9.3</v>
+      </c>
+      <c r="O24" s="276">
         <v>11.31</v>
       </c>
-      <c r="P24" s="267">
+      <c r="P24" s="268">
         <v>13.62</v>
       </c>
-      <c r="Q24" s="268">
+      <c r="Q24" s="272">
         <v>14.92</v>
       </c>
-      <c r="R24" s="271">
+      <c r="R24" s="273">
         <v>16.06</v>
       </c>
-      <c r="S24" s="272">
+      <c r="S24" s="269">
         <v>15.55</v>
       </c>
-      <c r="T24" s="273">
-        <v>7.74</v>
+      <c r="T24" s="274">
+        <v>6.97</v>
       </c>
     </row>
   </sheetData>
